--- a/ReportesUnificados/zamora_ReporteUnificado.xlsx
+++ b/ReportesUnificados/zamora_ReporteUnificado.xlsx
@@ -218,10 +218,10 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>2</row>
+      <row>3</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="3524250" cy="666750"/>
+    <ext cx="4762500" cy="952500"/>
     <pic>
       <nvPicPr>
         <cNvPr id="1" name="Image 1" descr="Picture"/>
@@ -243,10 +243,10 @@
     <from>
       <col>33</col>
       <colOff>0</colOff>
-      <row>1</row>
+      <row>2</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="2476500" cy="1333500"/>
+    <ext cx="2476500" cy="1143000"/>
     <pic>
       <nvPicPr>
         <cNvPr id="2" name="Image 2" descr="Picture"/>
@@ -268,10 +268,10 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>24</row>
+      <row>27</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="3524250" cy="666750"/>
+    <ext cx="4762500" cy="952500"/>
     <pic>
       <nvPicPr>
         <cNvPr id="3" name="Image 3" descr="Picture"/>
@@ -293,10 +293,10 @@
     <from>
       <col>33</col>
       <colOff>0</colOff>
-      <row>23</row>
+      <row>26</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="2476500" cy="1333500"/>
+    <ext cx="2476500" cy="1143000"/>
     <pic>
       <nvPicPr>
         <cNvPr id="4" name="Image 4" descr="Picture"/>
@@ -606,7 +606,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AK41"/>
+  <dimension ref="A1:AK43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="59" customWidth="1" min="1" max="1"/>
@@ -642,476 +642,212 @@
     <col width="8" customWidth="1" min="31" max="31"/>
     <col width="8" customWidth="1" min="32" max="32"/>
     <col width="8" customWidth="1" min="33" max="33"/>
-    <col width="19" customWidth="1" min="34" max="34"/>
-    <col width="22" customWidth="1" min="35" max="35"/>
-    <col width="42" customWidth="1" min="36" max="36"/>
+    <col width="15" customWidth="1" min="34" max="34"/>
+    <col width="23" customWidth="1" min="35" max="35"/>
+    <col width="23" customWidth="1" min="36" max="36"/>
     <col width="15" customWidth="1" min="37" max="37"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>AGENCIA DE REGULACIÓN Y CONTROL DE LAS TELECOMUNICACIONES</t>
+          <t>INFORME DE CONTROL TÉCNICO</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>COORDINACIÓN ZONAL 6</t>
+          <t>No. IT-CZ06-R-2025-00XX</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>ESTACIÓN DE COMPROBACIÓN TÉCNICA</t>
+          <t>AGENCIA DE REGULACIÓN Y CONTROL DE LAS TELECOMUNICACIONES</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>FORMULARIO DE CONTROL MENSUAL DE FM</t>
+          <t>COORDINACIÓN ZONAL 6</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>CIUDAD:ZAMORA</t>
+          <t>ESTACIÓN DE COMPROBACIÓN TÉCNICA</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>PERIODO: JULIO</t>
+          <t>FORMULARIO DE CONTROL MENSUAL DE FM</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
+          <t>CIUDAD:ZAMORA</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>PERIODO: JULIO</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
           <t>FECHA PRESENTACIÓN: 27/08/2025</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="45" customHeight="1">
-      <c r="A8" s="2" t="inlineStr">
+    <row r="10" ht="45" customHeight="1">
+      <c r="A10" s="2" t="inlineStr">
         <is>
           <t>ESTACION</t>
         </is>
       </c>
-      <c r="B8" s="3" t="inlineStr">
-        <is>
-          <t>FRECUENCIA (MHz)</t>
-        </is>
-      </c>
-      <c r="C8" s="3" t="n">
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>Frecuencia (MHz)</t>
+        </is>
+      </c>
+      <c r="C10" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="D8" s="3" t="n">
+      <c r="D10" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="E8" s="3" t="n">
+      <c r="E10" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="F8" s="3" t="n">
+      <c r="F10" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="G8" s="3" t="n">
+      <c r="G10" s="3" t="n">
         <v>5</v>
       </c>
-      <c r="H8" s="3" t="n">
+      <c r="H10" s="3" t="n">
         <v>6</v>
       </c>
-      <c r="I8" s="3" t="n">
+      <c r="I10" s="3" t="n">
         <v>7</v>
       </c>
-      <c r="J8" s="3" t="n">
+      <c r="J10" s="3" t="n">
         <v>8</v>
       </c>
-      <c r="K8" s="3" t="n">
+      <c r="K10" s="3" t="n">
         <v>9</v>
       </c>
-      <c r="L8" s="3" t="n">
+      <c r="L10" s="3" t="n">
         <v>10</v>
       </c>
-      <c r="M8" s="3" t="n">
+      <c r="M10" s="3" t="n">
         <v>11</v>
       </c>
-      <c r="N8" s="3" t="n">
+      <c r="N10" s="3" t="n">
         <v>12</v>
       </c>
-      <c r="O8" s="3" t="n">
+      <c r="O10" s="3" t="n">
         <v>13</v>
       </c>
-      <c r="P8" s="3" t="n">
+      <c r="P10" s="3" t="n">
         <v>14</v>
       </c>
-      <c r="Q8" s="3" t="n">
+      <c r="Q10" s="3" t="n">
         <v>15</v>
       </c>
-      <c r="R8" s="3" t="n">
+      <c r="R10" s="3" t="n">
         <v>16</v>
       </c>
-      <c r="S8" s="3" t="n">
+      <c r="S10" s="3" t="n">
         <v>17</v>
       </c>
-      <c r="T8" s="3" t="n">
+      <c r="T10" s="3" t="n">
         <v>18</v>
       </c>
-      <c r="U8" s="3" t="n">
+      <c r="U10" s="3" t="n">
         <v>19</v>
       </c>
-      <c r="V8" s="3" t="n">
+      <c r="V10" s="3" t="n">
         <v>20</v>
       </c>
-      <c r="W8" s="3" t="n">
+      <c r="W10" s="3" t="n">
         <v>21</v>
       </c>
-      <c r="X8" s="3" t="n">
+      <c r="X10" s="3" t="n">
         <v>22</v>
       </c>
-      <c r="Y8" s="3" t="n">
+      <c r="Y10" s="3" t="n">
         <v>23</v>
       </c>
-      <c r="Z8" s="3" t="n">
+      <c r="Z10" s="3" t="n">
         <v>24</v>
       </c>
-      <c r="AA8" s="3" t="n">
+      <c r="AA10" s="3" t="n">
         <v>25</v>
       </c>
-      <c r="AB8" s="3" t="n">
+      <c r="AB10" s="3" t="n">
         <v>26</v>
       </c>
-      <c r="AC8" s="3" t="n">
+      <c r="AC10" s="3" t="n">
         <v>27</v>
       </c>
-      <c r="AD8" s="3" t="n">
+      <c r="AD10" s="3" t="n">
         <v>28</v>
       </c>
-      <c r="AE8" s="3" t="n">
+      <c r="AE10" s="3" t="n">
         <v>29</v>
       </c>
-      <c r="AF8" s="3" t="n">
+      <c r="AF10" s="3" t="n">
         <v>30</v>
       </c>
-      <c r="AG8" s="3" t="n">
+      <c r="AG10" s="3" t="n">
         <v>31</v>
       </c>
-      <c r="AH8" s="3" t="inlineStr">
+      <c r="AH10" s="3" t="inlineStr">
         <is>
           <t>Promedio
 (dBuV/m)</t>
         </is>
       </c>
-      <c r="AI8" s="3" t="inlineStr">
+      <c r="AI10" s="3" t="inlineStr">
         <is>
           <t>Ancho de Banda
 (KHz)</t>
         </is>
       </c>
-      <c r="AJ8" s="3" t="inlineStr">
+      <c r="AJ10" s="3" t="inlineStr">
         <is>
           <t>Medición Manual
 AB(KHz) o NIVEL
 (dBµV/m)</t>
         </is>
       </c>
-      <c r="AK8" s="4" t="inlineStr">
+      <c r="AK10" s="4" t="inlineStr">
         <is>
           <t>OBSERVACIONES</t>
         </is>
       </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="5" t="inlineStr">
-        <is>
-          <t>RADIO SONORAMA FM</t>
-        </is>
-      </c>
-      <c r="B9" s="6" t="n">
-        <v>88.5</v>
-      </c>
-      <c r="C9" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D9" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E9" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F9" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G9" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H9" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I9" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J9" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K9" s="6" t="n">
-        <v>56.96</v>
-      </c>
-      <c r="L9" s="6" t="n">
-        <v>54.92</v>
-      </c>
-      <c r="M9" s="6" t="n">
-        <v>55.02</v>
-      </c>
-      <c r="N9" s="6" t="n">
-        <v>53.54</v>
-      </c>
-      <c r="O9" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P9" s="6" t="n">
-        <v>41.6</v>
-      </c>
-      <c r="Q9" s="6" t="n">
-        <v>40.72</v>
-      </c>
-      <c r="R9" s="6" t="n">
-        <v>39.48</v>
-      </c>
-      <c r="S9" s="6" t="n">
-        <v>39</v>
-      </c>
-      <c r="T9" s="6" t="n">
-        <v>39.18</v>
-      </c>
-      <c r="U9" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="V9" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="W9" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="X9" s="6" t="n">
-        <v>43.07</v>
-      </c>
-      <c r="Y9" s="6" t="n">
-        <v>38.32</v>
-      </c>
-      <c r="Z9" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AA9" s="6" t="n">
-        <v>46.74</v>
-      </c>
-      <c r="AB9" s="6" t="n">
-        <v>43.68</v>
-      </c>
-      <c r="AC9" s="6" t="n">
-        <v>40.17</v>
-      </c>
-      <c r="AD9" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AE9" s="6" t="n">
-        <v>42.11</v>
-      </c>
-      <c r="AF9" s="6" t="n">
-        <v>40.11</v>
-      </c>
-      <c r="AG9" s="6" t="n">
-        <v>41.92</v>
-      </c>
-      <c r="AH9" s="6" t="n">
-        <v>44.5</v>
-      </c>
-      <c r="AI9" s="6" t="n">
-        <v>485.74</v>
-      </c>
-      <c r="AJ9" s="6" t="inlineStr"/>
-      <c r="AK9" s="7" t="inlineStr"/>
-    </row>
-    <row r="10">
-      <c r="A10" s="5" t="inlineStr">
-        <is>
-          <t>LA RADIO DE LA ASAMBLEA NACIONA</t>
-        </is>
-      </c>
-      <c r="B10" s="6" t="n">
-        <v>88.90000000000001</v>
-      </c>
-      <c r="C10" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D10" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E10" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F10" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G10" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H10" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I10" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J10" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K10" s="6" t="n">
-        <v>75.64</v>
-      </c>
-      <c r="L10" s="6" t="n">
-        <v>76.81</v>
-      </c>
-      <c r="M10" s="6" t="n">
-        <v>79.76000000000001</v>
-      </c>
-      <c r="N10" s="6" t="n">
-        <v>81.90000000000001</v>
-      </c>
-      <c r="O10" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P10" s="6" t="n">
-        <v>82.14</v>
-      </c>
-      <c r="Q10" s="6" t="n">
-        <v>81.20999999999999</v>
-      </c>
-      <c r="R10" s="6" t="n">
-        <v>81.06</v>
-      </c>
-      <c r="S10" s="6" t="n">
-        <v>78.68000000000001</v>
-      </c>
-      <c r="T10" s="6" t="n">
-        <v>77.7</v>
-      </c>
-      <c r="U10" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="V10" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="W10" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="X10" s="6" t="n">
-        <v>81.20999999999999</v>
-      </c>
-      <c r="Y10" s="6" t="n">
-        <v>80.66</v>
-      </c>
-      <c r="Z10" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AA10" s="6" t="n">
-        <v>81.11</v>
-      </c>
-      <c r="AB10" s="6" t="n">
-        <v>79.63</v>
-      </c>
-      <c r="AC10" s="6" t="n">
-        <v>78.40000000000001</v>
-      </c>
-      <c r="AD10" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AE10" s="6" t="n">
-        <v>46.82</v>
-      </c>
-      <c r="AF10" s="6" t="n">
-        <v>40.81</v>
-      </c>
-      <c r="AG10" s="6" t="n">
-        <v>41.96</v>
-      </c>
-      <c r="AH10" s="6" t="n">
-        <v>73.26000000000001</v>
-      </c>
-      <c r="AI10" s="6" t="n">
-        <v>101.16</v>
-      </c>
-      <c r="AJ10" s="6" t="inlineStr"/>
-      <c r="AK10" s="7" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t>RADIO ONDA MUNICIPAL FM</t>
+          <t>RADIO SONORAMA FM</t>
         </is>
       </c>
       <c r="B11" s="6" t="n">
-        <v>90.09999999999999</v>
+        <v>88.5</v>
       </c>
       <c r="C11" s="6" t="inlineStr">
         <is>
@@ -1154,16 +890,16 @@
         </is>
       </c>
       <c r="K11" s="6" t="n">
-        <v>103.89</v>
+        <v>56.96</v>
       </c>
       <c r="L11" s="6" t="n">
-        <v>99.87</v>
+        <v>54.92</v>
       </c>
       <c r="M11" s="6" t="n">
-        <v>101.34</v>
+        <v>55.02</v>
       </c>
       <c r="N11" s="6" t="n">
-        <v>98.73999999999999</v>
+        <v>53.54</v>
       </c>
       <c r="O11" s="6" t="inlineStr">
         <is>
@@ -1171,19 +907,19 @@
         </is>
       </c>
       <c r="P11" s="6" t="n">
-        <v>102.67</v>
+        <v>41.6</v>
       </c>
       <c r="Q11" s="6" t="n">
-        <v>103.09</v>
+        <v>40.72</v>
       </c>
       <c r="R11" s="6" t="n">
-        <v>101.87</v>
+        <v>39.48</v>
       </c>
       <c r="S11" s="6" t="n">
-        <v>102.12</v>
+        <v>39</v>
       </c>
       <c r="T11" s="6" t="n">
-        <v>102.97</v>
+        <v>39.18</v>
       </c>
       <c r="U11" s="6" t="inlineStr">
         <is>
@@ -1201,10 +937,10 @@
         </is>
       </c>
       <c r="X11" s="6" t="n">
-        <v>102.96</v>
+        <v>43.07</v>
       </c>
       <c r="Y11" s="6" t="n">
-        <v>101.1</v>
+        <v>38.32</v>
       </c>
       <c r="Z11" s="6" t="inlineStr">
         <is>
@@ -1212,13 +948,13 @@
         </is>
       </c>
       <c r="AA11" s="6" t="n">
-        <v>102.83</v>
+        <v>46.74</v>
       </c>
       <c r="AB11" s="6" t="n">
-        <v>102.38</v>
+        <v>43.68</v>
       </c>
       <c r="AC11" s="6" t="n">
-        <v>101.42</v>
+        <v>40.17</v>
       </c>
       <c r="AD11" s="6" t="inlineStr">
         <is>
@@ -1226,19 +962,19 @@
         </is>
       </c>
       <c r="AE11" s="6" t="n">
-        <v>101.67</v>
+        <v>42.11</v>
       </c>
       <c r="AF11" s="6" t="n">
-        <v>102.23</v>
+        <v>40.11</v>
       </c>
       <c r="AG11" s="6" t="n">
-        <v>100.99</v>
+        <v>41.92</v>
       </c>
       <c r="AH11" s="6" t="n">
-        <v>101.89</v>
+        <v>44.5</v>
       </c>
       <c r="AI11" s="6" t="n">
-        <v>104.99</v>
+        <v>485.74</v>
       </c>
       <c r="AJ11" s="6" t="inlineStr"/>
       <c r="AK11" s="7" t="inlineStr"/>
@@ -1246,11 +982,11 @@
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>AMAZONAS FM</t>
+          <t>LA RADIO DE LA ASAMBLEA NACIONA</t>
         </is>
       </c>
       <c r="B12" s="6" t="n">
-        <v>92.09999999999999</v>
+        <v>88.90000000000001</v>
       </c>
       <c r="C12" s="6" t="inlineStr">
         <is>
@@ -1293,16 +1029,16 @@
         </is>
       </c>
       <c r="K12" s="6" t="n">
-        <v>89.91</v>
+        <v>75.64</v>
       </c>
       <c r="L12" s="6" t="n">
-        <v>89.05</v>
+        <v>76.81</v>
       </c>
       <c r="M12" s="6" t="n">
-        <v>89.79000000000001</v>
+        <v>79.76000000000001</v>
       </c>
       <c r="N12" s="6" t="n">
-        <v>90.05</v>
+        <v>81.90000000000001</v>
       </c>
       <c r="O12" s="6" t="inlineStr">
         <is>
@@ -1310,19 +1046,19 @@
         </is>
       </c>
       <c r="P12" s="6" t="n">
-        <v>91.48</v>
+        <v>82.14</v>
       </c>
       <c r="Q12" s="6" t="n">
-        <v>91.84</v>
+        <v>81.20999999999999</v>
       </c>
       <c r="R12" s="6" t="n">
-        <v>90.95999999999999</v>
+        <v>81.06</v>
       </c>
       <c r="S12" s="6" t="n">
-        <v>90.70999999999999</v>
+        <v>78.68000000000001</v>
       </c>
       <c r="T12" s="6" t="n">
-        <v>90.53</v>
+        <v>77.7</v>
       </c>
       <c r="U12" s="6" t="inlineStr">
         <is>
@@ -1340,10 +1076,10 @@
         </is>
       </c>
       <c r="X12" s="6" t="n">
-        <v>92.17</v>
+        <v>81.20999999999999</v>
       </c>
       <c r="Y12" s="6" t="n">
-        <v>89.58</v>
+        <v>80.66</v>
       </c>
       <c r="Z12" s="6" t="inlineStr">
         <is>
@@ -1351,13 +1087,13 @@
         </is>
       </c>
       <c r="AA12" s="6" t="n">
-        <v>92.22</v>
+        <v>81.11</v>
       </c>
       <c r="AB12" s="6" t="n">
-        <v>91.28</v>
+        <v>79.63</v>
       </c>
       <c r="AC12" s="6" t="n">
-        <v>91.42</v>
+        <v>78.40000000000001</v>
       </c>
       <c r="AD12" s="6" t="inlineStr">
         <is>
@@ -1365,19 +1101,19 @@
         </is>
       </c>
       <c r="AE12" s="6" t="n">
-        <v>92.08</v>
+        <v>46.82</v>
       </c>
       <c r="AF12" s="6" t="n">
-        <v>91.31999999999999</v>
+        <v>40.81</v>
       </c>
       <c r="AG12" s="6" t="n">
-        <v>90.73999999999999</v>
+        <v>41.96</v>
       </c>
       <c r="AH12" s="6" t="n">
-        <v>90.89</v>
+        <v>73.26000000000001</v>
       </c>
       <c r="AI12" s="6" t="n">
-        <v>119.83</v>
+        <v>101.16</v>
       </c>
       <c r="AJ12" s="6" t="inlineStr"/>
       <c r="AK12" s="7" t="inlineStr"/>
@@ -1385,11 +1121,11 @@
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>LA KARIBEÑA</t>
+          <t>RADIO ONDA MUNICIPAL FM</t>
         </is>
       </c>
       <c r="B13" s="6" t="n">
-        <v>94.5</v>
+        <v>90.09999999999999</v>
       </c>
       <c r="C13" s="6" t="inlineStr">
         <is>
@@ -1432,16 +1168,16 @@
         </is>
       </c>
       <c r="K13" s="6" t="n">
-        <v>73.76000000000001</v>
+        <v>103.89</v>
       </c>
       <c r="L13" s="6" t="n">
-        <v>72.86</v>
+        <v>99.87</v>
       </c>
       <c r="M13" s="6" t="n">
-        <v>73.77</v>
+        <v>101.34</v>
       </c>
       <c r="N13" s="6" t="n">
-        <v>73.42</v>
+        <v>98.73999999999999</v>
       </c>
       <c r="O13" s="6" t="inlineStr">
         <is>
@@ -1449,19 +1185,19 @@
         </is>
       </c>
       <c r="P13" s="6" t="n">
-        <v>74.97</v>
+        <v>102.67</v>
       </c>
       <c r="Q13" s="6" t="n">
-        <v>74.93000000000001</v>
+        <v>103.09</v>
       </c>
       <c r="R13" s="6" t="n">
-        <v>74.58</v>
+        <v>101.87</v>
       </c>
       <c r="S13" s="6" t="n">
-        <v>74.12</v>
+        <v>102.12</v>
       </c>
       <c r="T13" s="6" t="n">
-        <v>74.38</v>
+        <v>102.97</v>
       </c>
       <c r="U13" s="6" t="inlineStr">
         <is>
@@ -1479,10 +1215,10 @@
         </is>
       </c>
       <c r="X13" s="6" t="n">
-        <v>74.73999999999999</v>
+        <v>102.96</v>
       </c>
       <c r="Y13" s="6" t="n">
-        <v>74.34</v>
+        <v>101.1</v>
       </c>
       <c r="Z13" s="6" t="inlineStr">
         <is>
@@ -1490,13 +1226,13 @@
         </is>
       </c>
       <c r="AA13" s="6" t="n">
-        <v>74.92</v>
+        <v>102.83</v>
       </c>
       <c r="AB13" s="6" t="n">
-        <v>75.15000000000001</v>
+        <v>102.38</v>
       </c>
       <c r="AC13" s="6" t="n">
-        <v>75.31</v>
+        <v>101.42</v>
       </c>
       <c r="AD13" s="6" t="inlineStr">
         <is>
@@ -1504,19 +1240,19 @@
         </is>
       </c>
       <c r="AE13" s="6" t="n">
-        <v>74.61</v>
+        <v>101.67</v>
       </c>
       <c r="AF13" s="6" t="n">
-        <v>75.12</v>
+        <v>102.23</v>
       </c>
       <c r="AG13" s="6" t="n">
-        <v>74.22</v>
+        <v>100.99</v>
       </c>
       <c r="AH13" s="6" t="n">
-        <v>74.42</v>
+        <v>101.89</v>
       </c>
       <c r="AI13" s="6" t="n">
-        <v>156.6</v>
+        <v>104.99</v>
       </c>
       <c r="AJ13" s="6" t="inlineStr"/>
       <c r="AK13" s="7" t="inlineStr"/>
@@ -1524,11 +1260,11 @@
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
         <is>
-          <t>RADIO ROMÁNTICA FM</t>
+          <t>AMAZONAS FM</t>
         </is>
       </c>
       <c r="B14" s="6" t="n">
-        <v>95.7</v>
+        <v>92.09999999999999</v>
       </c>
       <c r="C14" s="6" t="inlineStr">
         <is>
@@ -1571,16 +1307,16 @@
         </is>
       </c>
       <c r="K14" s="6" t="n">
-        <v>90.2</v>
+        <v>89.91</v>
       </c>
       <c r="L14" s="6" t="n">
-        <v>87.67</v>
+        <v>89.05</v>
       </c>
       <c r="M14" s="6" t="n">
-        <v>89.05</v>
+        <v>89.79000000000001</v>
       </c>
       <c r="N14" s="6" t="n">
-        <v>88.61</v>
+        <v>90.05</v>
       </c>
       <c r="O14" s="6" t="inlineStr">
         <is>
@@ -1588,19 +1324,19 @@
         </is>
       </c>
       <c r="P14" s="6" t="n">
-        <v>90.01000000000001</v>
+        <v>91.48</v>
       </c>
       <c r="Q14" s="6" t="n">
-        <v>89.26000000000001</v>
+        <v>91.84</v>
       </c>
       <c r="R14" s="6" t="n">
-        <v>89.18000000000001</v>
+        <v>90.95999999999999</v>
       </c>
       <c r="S14" s="6" t="n">
-        <v>90.37</v>
+        <v>90.70999999999999</v>
       </c>
       <c r="T14" s="6" t="n">
-        <v>90.94</v>
+        <v>90.53</v>
       </c>
       <c r="U14" s="6" t="inlineStr">
         <is>
@@ -1618,10 +1354,10 @@
         </is>
       </c>
       <c r="X14" s="6" t="n">
-        <v>90.41</v>
+        <v>92.17</v>
       </c>
       <c r="Y14" s="6" t="n">
-        <v>88.64</v>
+        <v>89.58</v>
       </c>
       <c r="Z14" s="6" t="inlineStr">
         <is>
@@ -1629,13 +1365,13 @@
         </is>
       </c>
       <c r="AA14" s="6" t="n">
-        <v>90.01000000000001</v>
+        <v>92.22</v>
       </c>
       <c r="AB14" s="6" t="n">
-        <v>89.69</v>
+        <v>91.28</v>
       </c>
       <c r="AC14" s="6" t="n">
-        <v>89.87</v>
+        <v>91.42</v>
       </c>
       <c r="AD14" s="6" t="inlineStr">
         <is>
@@ -1643,19 +1379,19 @@
         </is>
       </c>
       <c r="AE14" s="6" t="n">
-        <v>89.26000000000001</v>
+        <v>92.08</v>
       </c>
       <c r="AF14" s="6" t="n">
-        <v>88.64</v>
+        <v>91.31999999999999</v>
       </c>
       <c r="AG14" s="6" t="n">
-        <v>88.94</v>
+        <v>90.73999999999999</v>
       </c>
       <c r="AH14" s="6" t="n">
-        <v>89.45999999999999</v>
+        <v>90.89</v>
       </c>
       <c r="AI14" s="6" t="n">
-        <v>138.26</v>
+        <v>119.83</v>
       </c>
       <c r="AJ14" s="6" t="inlineStr"/>
       <c r="AK14" s="7" t="inlineStr"/>
@@ -1663,11 +1399,11 @@
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
         <is>
-          <t>RADIO PODOCARPUS</t>
+          <t>LA KARIBEÑA</t>
         </is>
       </c>
       <c r="B15" s="6" t="n">
-        <v>98.09999999999999</v>
+        <v>94.5</v>
       </c>
       <c r="C15" s="6" t="inlineStr">
         <is>
@@ -1710,16 +1446,16 @@
         </is>
       </c>
       <c r="K15" s="6" t="n">
-        <v>103.71</v>
+        <v>73.76000000000001</v>
       </c>
       <c r="L15" s="6" t="n">
-        <v>102.89</v>
+        <v>72.86</v>
       </c>
       <c r="M15" s="6" t="n">
-        <v>104.26</v>
+        <v>73.77</v>
       </c>
       <c r="N15" s="6" t="n">
-        <v>103.16</v>
+        <v>73.42</v>
       </c>
       <c r="O15" s="6" t="inlineStr">
         <is>
@@ -1727,19 +1463,19 @@
         </is>
       </c>
       <c r="P15" s="6" t="n">
-        <v>105.67</v>
+        <v>74.97</v>
       </c>
       <c r="Q15" s="6" t="n">
-        <v>105.56</v>
+        <v>74.93000000000001</v>
       </c>
       <c r="R15" s="6" t="n">
-        <v>105</v>
+        <v>74.58</v>
       </c>
       <c r="S15" s="6" t="n">
-        <v>104.83</v>
+        <v>74.12</v>
       </c>
       <c r="T15" s="6" t="n">
-        <v>105.03</v>
+        <v>74.38</v>
       </c>
       <c r="U15" s="6" t="inlineStr">
         <is>
@@ -1757,10 +1493,10 @@
         </is>
       </c>
       <c r="X15" s="6" t="n">
-        <v>105.37</v>
+        <v>74.73999999999999</v>
       </c>
       <c r="Y15" s="6" t="n">
-        <v>104.17</v>
+        <v>74.34</v>
       </c>
       <c r="Z15" s="6" t="inlineStr">
         <is>
@@ -1768,13 +1504,13 @@
         </is>
       </c>
       <c r="AA15" s="6" t="n">
-        <v>105.66</v>
+        <v>74.92</v>
       </c>
       <c r="AB15" s="6" t="n">
-        <v>105.14</v>
+        <v>75.15000000000001</v>
       </c>
       <c r="AC15" s="6" t="n">
-        <v>104.84</v>
+        <v>75.31</v>
       </c>
       <c r="AD15" s="6" t="inlineStr">
         <is>
@@ -1782,19 +1518,19 @@
         </is>
       </c>
       <c r="AE15" s="6" t="n">
-        <v>105.13</v>
+        <v>74.61</v>
       </c>
       <c r="AF15" s="6" t="n">
-        <v>105.22</v>
+        <v>75.12</v>
       </c>
       <c r="AG15" s="6" t="n">
-        <v>104.76</v>
+        <v>74.22</v>
       </c>
       <c r="AH15" s="6" t="n">
-        <v>104.73</v>
+        <v>74.42</v>
       </c>
       <c r="AI15" s="6" t="n">
-        <v>246.97</v>
+        <v>156.6</v>
       </c>
       <c r="AJ15" s="6" t="inlineStr"/>
       <c r="AK15" s="7" t="inlineStr"/>
@@ -1802,11 +1538,11 @@
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
         <is>
-          <t>ZT RADIO LA RUMBERA</t>
+          <t>RADIO ROMÁNTICA FM</t>
         </is>
       </c>
       <c r="B16" s="6" t="n">
-        <v>100.9</v>
+        <v>95.7</v>
       </c>
       <c r="C16" s="6" t="inlineStr">
         <is>
@@ -1849,16 +1585,16 @@
         </is>
       </c>
       <c r="K16" s="6" t="n">
-        <v>66.56</v>
+        <v>90.2</v>
       </c>
       <c r="L16" s="6" t="n">
-        <v>70.83</v>
+        <v>87.67</v>
       </c>
       <c r="M16" s="6" t="n">
-        <v>71.56999999999999</v>
+        <v>89.05</v>
       </c>
       <c r="N16" s="6" t="n">
-        <v>70.55</v>
+        <v>88.61</v>
       </c>
       <c r="O16" s="6" t="inlineStr">
         <is>
@@ -1866,19 +1602,19 @@
         </is>
       </c>
       <c r="P16" s="6" t="n">
-        <v>73.66</v>
+        <v>90.01000000000001</v>
       </c>
       <c r="Q16" s="6" t="n">
-        <v>73.25</v>
+        <v>89.26000000000001</v>
       </c>
       <c r="R16" s="6" t="n">
-        <v>73.23</v>
+        <v>89.18000000000001</v>
       </c>
       <c r="S16" s="6" t="n">
-        <v>68.51000000000001</v>
+        <v>90.37</v>
       </c>
       <c r="T16" s="6" t="n">
-        <v>70.68000000000001</v>
+        <v>90.94</v>
       </c>
       <c r="U16" s="6" t="inlineStr">
         <is>
@@ -1896,10 +1632,10 @@
         </is>
       </c>
       <c r="X16" s="6" t="n">
-        <v>72.51000000000001</v>
+        <v>90.41</v>
       </c>
       <c r="Y16" s="6" t="n">
-        <v>66.12</v>
+        <v>88.64</v>
       </c>
       <c r="Z16" s="6" t="inlineStr">
         <is>
@@ -1907,13 +1643,13 @@
         </is>
       </c>
       <c r="AA16" s="6" t="n">
-        <v>71.5</v>
+        <v>90.01000000000001</v>
       </c>
       <c r="AB16" s="6" t="n">
-        <v>70.66</v>
+        <v>89.69</v>
       </c>
       <c r="AC16" s="6" t="n">
-        <v>70.8</v>
+        <v>89.87</v>
       </c>
       <c r="AD16" s="6" t="inlineStr">
         <is>
@@ -1921,19 +1657,19 @@
         </is>
       </c>
       <c r="AE16" s="6" t="n">
-        <v>71.98999999999999</v>
+        <v>89.26000000000001</v>
       </c>
       <c r="AF16" s="6" t="n">
-        <v>71.06999999999999</v>
+        <v>88.64</v>
       </c>
       <c r="AG16" s="6" t="n">
-        <v>71.56999999999999</v>
+        <v>88.94</v>
       </c>
       <c r="AH16" s="6" t="n">
-        <v>70.88</v>
+        <v>89.45999999999999</v>
       </c>
       <c r="AI16" s="6" t="n">
-        <v>52.8</v>
+        <v>138.26</v>
       </c>
       <c r="AJ16" s="6" t="inlineStr"/>
       <c r="AK16" s="7" t="inlineStr"/>
@@ -1941,11 +1677,11 @@
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
         <is>
-          <t>LUCA RADIO 101.3</t>
+          <t>RADIO PODOCARPUS</t>
         </is>
       </c>
       <c r="B17" s="6" t="n">
-        <v>101.3</v>
+        <v>98.09999999999999</v>
       </c>
       <c r="C17" s="6" t="inlineStr">
         <is>
@@ -1988,16 +1724,16 @@
         </is>
       </c>
       <c r="K17" s="6" t="n">
-        <v>46.03</v>
+        <v>103.71</v>
       </c>
       <c r="L17" s="6" t="n">
-        <v>43.57</v>
+        <v>102.89</v>
       </c>
       <c r="M17" s="6" t="n">
-        <v>45.68</v>
+        <v>104.26</v>
       </c>
       <c r="N17" s="6" t="n">
-        <v>44.8</v>
+        <v>103.16</v>
       </c>
       <c r="O17" s="6" t="inlineStr">
         <is>
@@ -2005,19 +1741,19 @@
         </is>
       </c>
       <c r="P17" s="6" t="n">
-        <v>47.17</v>
+        <v>105.67</v>
       </c>
       <c r="Q17" s="6" t="n">
-        <v>46.81</v>
+        <v>105.56</v>
       </c>
       <c r="R17" s="6" t="n">
-        <v>46.39</v>
+        <v>105</v>
       </c>
       <c r="S17" s="6" t="n">
-        <v>47.11</v>
+        <v>104.83</v>
       </c>
       <c r="T17" s="6" t="n">
-        <v>47</v>
+        <v>105.03</v>
       </c>
       <c r="U17" s="6" t="inlineStr">
         <is>
@@ -2035,10 +1771,10 @@
         </is>
       </c>
       <c r="X17" s="6" t="n">
-        <v>47.87</v>
+        <v>105.37</v>
       </c>
       <c r="Y17" s="6" t="n">
-        <v>45.81</v>
+        <v>104.17</v>
       </c>
       <c r="Z17" s="6" t="inlineStr">
         <is>
@@ -2046,13 +1782,13 @@
         </is>
       </c>
       <c r="AA17" s="6" t="n">
-        <v>47.24</v>
+        <v>105.66</v>
       </c>
       <c r="AB17" s="6" t="n">
-        <v>46.43</v>
+        <v>105.14</v>
       </c>
       <c r="AC17" s="6" t="n">
-        <v>46.17</v>
+        <v>104.84</v>
       </c>
       <c r="AD17" s="6" t="inlineStr">
         <is>
@@ -2060,19 +1796,19 @@
         </is>
       </c>
       <c r="AE17" s="6" t="n">
-        <v>46.36</v>
+        <v>105.13</v>
       </c>
       <c r="AF17" s="6" t="n">
-        <v>46.06</v>
+        <v>105.22</v>
       </c>
       <c r="AG17" s="6" t="n">
-        <v>45.74</v>
+        <v>104.76</v>
       </c>
       <c r="AH17" s="6" t="n">
-        <v>46.25</v>
+        <v>104.73</v>
       </c>
       <c r="AI17" s="6" t="n">
-        <v>477.49</v>
+        <v>246.97</v>
       </c>
       <c r="AJ17" s="6" t="inlineStr"/>
       <c r="AK17" s="7" t="inlineStr"/>
@@ -2080,11 +1816,11 @@
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
         <is>
-          <t>INTEGRACION FM</t>
+          <t>ZT RADIO LA RUMBERA</t>
         </is>
       </c>
       <c r="B18" s="6" t="n">
-        <v>104.1</v>
+        <v>100.9</v>
       </c>
       <c r="C18" s="6" t="inlineStr">
         <is>
@@ -2127,16 +1863,16 @@
         </is>
       </c>
       <c r="K18" s="6" t="n">
-        <v>82.23999999999999</v>
+        <v>66.56</v>
       </c>
       <c r="L18" s="6" t="n">
-        <v>83.69</v>
+        <v>70.83</v>
       </c>
       <c r="M18" s="6" t="n">
-        <v>81.95999999999999</v>
+        <v>71.56999999999999</v>
       </c>
       <c r="N18" s="6" t="n">
-        <v>82.68000000000001</v>
+        <v>70.55</v>
       </c>
       <c r="O18" s="6" t="inlineStr">
         <is>
@@ -2144,19 +1880,19 @@
         </is>
       </c>
       <c r="P18" s="6" t="n">
-        <v>81.26000000000001</v>
+        <v>73.66</v>
       </c>
       <c r="Q18" s="6" t="n">
-        <v>80.44</v>
+        <v>73.25</v>
       </c>
       <c r="R18" s="6" t="n">
-        <v>79.55</v>
+        <v>73.23</v>
       </c>
       <c r="S18" s="6" t="n">
-        <v>82.98</v>
+        <v>68.51000000000001</v>
       </c>
       <c r="T18" s="6" t="n">
-        <v>82.94</v>
+        <v>70.68000000000001</v>
       </c>
       <c r="U18" s="6" t="inlineStr">
         <is>
@@ -2174,10 +1910,10 @@
         </is>
       </c>
       <c r="X18" s="6" t="n">
-        <v>82.48999999999999</v>
+        <v>72.51000000000001</v>
       </c>
       <c r="Y18" s="6" t="n">
-        <v>81.39</v>
+        <v>66.12</v>
       </c>
       <c r="Z18" s="6" t="inlineStr">
         <is>
@@ -2185,13 +1921,13 @@
         </is>
       </c>
       <c r="AA18" s="6" t="n">
-        <v>80.79000000000001</v>
+        <v>71.5</v>
       </c>
       <c r="AB18" s="6" t="n">
-        <v>81.12</v>
+        <v>70.66</v>
       </c>
       <c r="AC18" s="6" t="n">
-        <v>78.63</v>
+        <v>70.8</v>
       </c>
       <c r="AD18" s="6" t="inlineStr">
         <is>
@@ -2199,19 +1935,19 @@
         </is>
       </c>
       <c r="AE18" s="6" t="n">
-        <v>80.22</v>
+        <v>71.98999999999999</v>
       </c>
       <c r="AF18" s="6" t="n">
-        <v>80.81</v>
+        <v>71.06999999999999</v>
       </c>
       <c r="AG18" s="6" t="n">
-        <v>80.31999999999999</v>
+        <v>71.56999999999999</v>
       </c>
       <c r="AH18" s="6" t="n">
-        <v>81.38</v>
+        <v>70.88</v>
       </c>
       <c r="AI18" s="6" t="n">
-        <v>149.08</v>
+        <v>52.8</v>
       </c>
       <c r="AJ18" s="6" t="inlineStr"/>
       <c r="AK18" s="7" t="inlineStr"/>
@@ -2219,11 +1955,11 @@
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
         <is>
-          <t>PUBLICA FM</t>
+          <t>LUCA RADIO 101.3</t>
         </is>
       </c>
       <c r="B19" s="6" t="n">
-        <v>105.3</v>
+        <v>101.3</v>
       </c>
       <c r="C19" s="6" t="inlineStr">
         <is>
@@ -2266,16 +2002,16 @@
         </is>
       </c>
       <c r="K19" s="6" t="n">
-        <v>55.96</v>
+        <v>46.03</v>
       </c>
       <c r="L19" s="6" t="n">
-        <v>57.99</v>
+        <v>43.57</v>
       </c>
       <c r="M19" s="6" t="n">
-        <v>56.92</v>
+        <v>45.68</v>
       </c>
       <c r="N19" s="6" t="n">
-        <v>59.21</v>
+        <v>44.8</v>
       </c>
       <c r="O19" s="6" t="inlineStr">
         <is>
@@ -2283,19 +2019,19 @@
         </is>
       </c>
       <c r="P19" s="6" t="n">
-        <v>55.46</v>
+        <v>47.17</v>
       </c>
       <c r="Q19" s="6" t="n">
-        <v>55.44</v>
+        <v>46.81</v>
       </c>
       <c r="R19" s="6" t="n">
-        <v>56.11</v>
+        <v>46.39</v>
       </c>
       <c r="S19" s="6" t="n">
-        <v>54.27</v>
+        <v>47.11</v>
       </c>
       <c r="T19" s="6" t="n">
-        <v>55.4</v>
+        <v>47</v>
       </c>
       <c r="U19" s="6" t="inlineStr">
         <is>
@@ -2313,10 +2049,10 @@
         </is>
       </c>
       <c r="X19" s="6" t="n">
-        <v>55.71</v>
+        <v>47.87</v>
       </c>
       <c r="Y19" s="6" t="n">
-        <v>57.52</v>
+        <v>45.81</v>
       </c>
       <c r="Z19" s="6" t="inlineStr">
         <is>
@@ -2324,13 +2060,13 @@
         </is>
       </c>
       <c r="AA19" s="6" t="n">
-        <v>55.4</v>
+        <v>47.24</v>
       </c>
       <c r="AB19" s="6" t="n">
-        <v>56.72</v>
+        <v>46.43</v>
       </c>
       <c r="AC19" s="6" t="n">
-        <v>56.56</v>
+        <v>46.17</v>
       </c>
       <c r="AD19" s="6" t="inlineStr">
         <is>
@@ -2338,619 +2074,623 @@
         </is>
       </c>
       <c r="AE19" s="6" t="n">
-        <v>55.47</v>
+        <v>46.36</v>
       </c>
       <c r="AF19" s="6" t="n">
-        <v>56.47</v>
+        <v>46.06</v>
       </c>
       <c r="AG19" s="6" t="n">
-        <v>57.08</v>
+        <v>45.74</v>
       </c>
       <c r="AH19" s="6" t="n">
-        <v>56.33</v>
+        <v>46.25</v>
       </c>
       <c r="AI19" s="6" t="n">
-        <v>157.64</v>
+        <v>477.49</v>
       </c>
       <c r="AJ19" s="6" t="inlineStr"/>
       <c r="AK19" s="7" t="inlineStr"/>
     </row>
     <row r="20">
-      <c r="A20" s="8" t="inlineStr">
+      <c r="A20" s="5" t="inlineStr">
+        <is>
+          <t>INTEGRACION FM</t>
+        </is>
+      </c>
+      <c r="B20" s="6" t="n">
+        <v>104.1</v>
+      </c>
+      <c r="C20" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D20" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E20" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F20" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G20" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H20" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I20" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J20" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K20" s="6" t="n">
+        <v>82.23999999999999</v>
+      </c>
+      <c r="L20" s="6" t="n">
+        <v>83.69</v>
+      </c>
+      <c r="M20" s="6" t="n">
+        <v>81.95999999999999</v>
+      </c>
+      <c r="N20" s="6" t="n">
+        <v>82.68000000000001</v>
+      </c>
+      <c r="O20" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P20" s="6" t="n">
+        <v>81.26000000000001</v>
+      </c>
+      <c r="Q20" s="6" t="n">
+        <v>80.44</v>
+      </c>
+      <c r="R20" s="6" t="n">
+        <v>79.55</v>
+      </c>
+      <c r="S20" s="6" t="n">
+        <v>82.98</v>
+      </c>
+      <c r="T20" s="6" t="n">
+        <v>82.94</v>
+      </c>
+      <c r="U20" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="V20" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="W20" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="X20" s="6" t="n">
+        <v>82.48999999999999</v>
+      </c>
+      <c r="Y20" s="6" t="n">
+        <v>81.39</v>
+      </c>
+      <c r="Z20" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AA20" s="6" t="n">
+        <v>80.79000000000001</v>
+      </c>
+      <c r="AB20" s="6" t="n">
+        <v>81.12</v>
+      </c>
+      <c r="AC20" s="6" t="n">
+        <v>78.63</v>
+      </c>
+      <c r="AD20" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AE20" s="6" t="n">
+        <v>80.22</v>
+      </c>
+      <c r="AF20" s="6" t="n">
+        <v>80.81</v>
+      </c>
+      <c r="AG20" s="6" t="n">
+        <v>80.31999999999999</v>
+      </c>
+      <c r="AH20" s="6" t="n">
+        <v>81.38</v>
+      </c>
+      <c r="AI20" s="6" t="n">
+        <v>149.08</v>
+      </c>
+      <c r="AJ20" s="6" t="inlineStr"/>
+      <c r="AK20" s="7" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="5" t="inlineStr">
+        <is>
+          <t>PUBLICA FM</t>
+        </is>
+      </c>
+      <c r="B21" s="6" t="n">
+        <v>105.3</v>
+      </c>
+      <c r="C21" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D21" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E21" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F21" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G21" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H21" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I21" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J21" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K21" s="6" t="n">
+        <v>55.96</v>
+      </c>
+      <c r="L21" s="6" t="n">
+        <v>57.99</v>
+      </c>
+      <c r="M21" s="6" t="n">
+        <v>56.92</v>
+      </c>
+      <c r="N21" s="6" t="n">
+        <v>59.21</v>
+      </c>
+      <c r="O21" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P21" s="6" t="n">
+        <v>55.46</v>
+      </c>
+      <c r="Q21" s="6" t="n">
+        <v>55.44</v>
+      </c>
+      <c r="R21" s="6" t="n">
+        <v>56.11</v>
+      </c>
+      <c r="S21" s="6" t="n">
+        <v>54.27</v>
+      </c>
+      <c r="T21" s="6" t="n">
+        <v>55.4</v>
+      </c>
+      <c r="U21" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="V21" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="W21" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="X21" s="6" t="n">
+        <v>55.71</v>
+      </c>
+      <c r="Y21" s="6" t="n">
+        <v>57.52</v>
+      </c>
+      <c r="Z21" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AA21" s="6" t="n">
+        <v>55.4</v>
+      </c>
+      <c r="AB21" s="6" t="n">
+        <v>56.72</v>
+      </c>
+      <c r="AC21" s="6" t="n">
+        <v>56.56</v>
+      </c>
+      <c r="AD21" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AE21" s="6" t="n">
+        <v>55.47</v>
+      </c>
+      <c r="AF21" s="6" t="n">
+        <v>56.47</v>
+      </c>
+      <c r="AG21" s="6" t="n">
+        <v>57.08</v>
+      </c>
+      <c r="AH21" s="6" t="n">
+        <v>56.33</v>
+      </c>
+      <c r="AI21" s="6" t="n">
+        <v>157.64</v>
+      </c>
+      <c r="AJ21" s="6" t="inlineStr"/>
+      <c r="AK21" s="7" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="8" t="inlineStr">
         <is>
           <t>ZETA</t>
         </is>
       </c>
-      <c r="B20" s="9" t="n">
+      <c r="B22" s="9" t="n">
         <v>106.9</v>
       </c>
-      <c r="C20" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D20" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E20" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F20" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G20" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H20" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I20" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J20" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K20" s="9" t="n">
+      <c r="C22" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D22" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E22" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F22" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G22" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H22" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I22" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J22" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K22" s="9" t="n">
         <v>94.18000000000001</v>
       </c>
-      <c r="L20" s="9" t="n">
+      <c r="L22" s="9" t="n">
         <v>93.93000000000001</v>
       </c>
-      <c r="M20" s="9" t="n">
+      <c r="M22" s="9" t="n">
         <v>95.51000000000001</v>
       </c>
-      <c r="N20" s="9" t="n">
+      <c r="N22" s="9" t="n">
         <v>94.7</v>
       </c>
-      <c r="O20" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P20" s="9" t="n">
+      <c r="O22" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P22" s="9" t="n">
         <v>96.44</v>
       </c>
-      <c r="Q20" s="9" t="n">
+      <c r="Q22" s="9" t="n">
         <v>96.55</v>
       </c>
-      <c r="R20" s="9" t="n">
+      <c r="R22" s="9" t="n">
         <v>96.68000000000001</v>
       </c>
-      <c r="S20" s="9" t="n">
+      <c r="S22" s="9" t="n">
         <v>95.59</v>
       </c>
-      <c r="T20" s="9" t="n">
+      <c r="T22" s="9" t="n">
         <v>95.16</v>
       </c>
-      <c r="U20" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="V20" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="W20" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="X20" s="9" t="n">
+      <c r="U22" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="V22" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="W22" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="X22" s="9" t="n">
         <v>96.52</v>
       </c>
-      <c r="Y20" s="9" t="n">
+      <c r="Y22" s="9" t="n">
         <v>96.81</v>
       </c>
-      <c r="Z20" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AA20" s="9" t="n">
+      <c r="Z22" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AA22" s="9" t="n">
         <v>96.84</v>
       </c>
-      <c r="AB20" s="9" t="n">
+      <c r="AB22" s="9" t="n">
         <v>97.22</v>
       </c>
-      <c r="AC20" s="9" t="n">
+      <c r="AC22" s="9" t="n">
         <v>96.81</v>
       </c>
-      <c r="AD20" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AE20" s="9" t="n">
+      <c r="AD22" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AE22" s="9" t="n">
         <v>96.48</v>
       </c>
-      <c r="AF20" s="9" t="n">
+      <c r="AF22" s="9" t="n">
         <v>97.16</v>
       </c>
-      <c r="AG20" s="9" t="n">
+      <c r="AG22" s="9" t="n">
         <v>96.37</v>
       </c>
-      <c r="AH20" s="9" t="n">
+      <c r="AH22" s="9" t="n">
         <v>96.06</v>
       </c>
-      <c r="AI20" s="9" t="n">
+      <c r="AI22" s="9" t="n">
         <v>127.1</v>
       </c>
-      <c r="AJ20" s="9" t="inlineStr"/>
-      <c r="AK20" s="10" t="inlineStr"/>
+      <c r="AJ22" s="9" t="inlineStr"/>
+      <c r="AK22" s="10" t="inlineStr"/>
     </row>
-    <row r="21"/>
-    <row r="22"/>
-    <row r="23">
-      <c r="A23" s="1" t="inlineStr">
-        <is>
-          <t>AGENCIA DE REGULACIÓN Y CONTROL DE LAS TELECOMUNICACIONES</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="1" t="inlineStr">
-        <is>
-          <t>COORDINACIÓN ZONAL 6</t>
-        </is>
-      </c>
-    </row>
+    <row r="23"/>
+    <row r="24"/>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>ESTACIÓN DE COMPROBACIÓN TÉCNICA</t>
+          <t>AGENCIA DE REGULACIÓN Y CONTROL DE LAS TELECOMUNICACIONES</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
         <is>
-          <t>FORMULARIO DE CONTROL MENSUAL DE TV</t>
+          <t>COORDINACIÓN ZONAL 6</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="inlineStr">
         <is>
-          <t>CIUDAD:ZAMORA</t>
+          <t>ESTACIÓN DE COMPROBACIÓN TÉCNICA</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>PERIODO: JULIO</t>
+          <t>FORMULARIO DE CONTROL MENSUAL DE TV</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
         <is>
+          <t>CIUDAD:ZAMORA</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="1" t="inlineStr">
+        <is>
+          <t>PERIODO: JULIO</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="1" t="inlineStr">
+        <is>
           <t>FECHA PRESENTACIÓN: 27/08/2025</t>
         </is>
       </c>
     </row>
-    <row r="30" ht="45" customHeight="1">
-      <c r="A30" s="2" t="inlineStr">
+    <row r="32" ht="45" customHeight="1">
+      <c r="A32" s="2" t="inlineStr">
         <is>
           <t>ESTACION</t>
         </is>
       </c>
-      <c r="B30" s="3" t="inlineStr">
+      <c r="B32" s="3" t="inlineStr">
         <is>
           <t>Frecuencia (MHz)</t>
         </is>
       </c>
-      <c r="C30" s="3" t="n">
+      <c r="C32" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="D30" s="3" t="n">
+      <c r="D32" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="E30" s="3" t="n">
+      <c r="E32" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="F30" s="3" t="n">
+      <c r="F32" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="G30" s="3" t="n">
+      <c r="G32" s="3" t="n">
         <v>5</v>
       </c>
-      <c r="H30" s="3" t="n">
+      <c r="H32" s="3" t="n">
         <v>6</v>
       </c>
-      <c r="I30" s="3" t="n">
+      <c r="I32" s="3" t="n">
         <v>7</v>
       </c>
-      <c r="J30" s="3" t="n">
+      <c r="J32" s="3" t="n">
         <v>8</v>
       </c>
-      <c r="K30" s="3" t="n">
+      <c r="K32" s="3" t="n">
         <v>9</v>
       </c>
-      <c r="L30" s="3" t="n">
+      <c r="L32" s="3" t="n">
         <v>10</v>
       </c>
-      <c r="M30" s="3" t="n">
+      <c r="M32" s="3" t="n">
         <v>11</v>
       </c>
-      <c r="N30" s="3" t="n">
+      <c r="N32" s="3" t="n">
         <v>12</v>
       </c>
-      <c r="O30" s="3" t="n">
+      <c r="O32" s="3" t="n">
         <v>13</v>
       </c>
-      <c r="P30" s="3" t="n">
+      <c r="P32" s="3" t="n">
         <v>14</v>
       </c>
-      <c r="Q30" s="3" t="n">
+      <c r="Q32" s="3" t="n">
         <v>15</v>
       </c>
-      <c r="R30" s="3" t="n">
+      <c r="R32" s="3" t="n">
         <v>16</v>
       </c>
-      <c r="S30" s="3" t="n">
+      <c r="S32" s="3" t="n">
         <v>17</v>
       </c>
-      <c r="T30" s="3" t="n">
+      <c r="T32" s="3" t="n">
         <v>18</v>
       </c>
-      <c r="U30" s="3" t="n">
+      <c r="U32" s="3" t="n">
         <v>19</v>
       </c>
-      <c r="V30" s="3" t="n">
+      <c r="V32" s="3" t="n">
         <v>20</v>
       </c>
-      <c r="W30" s="3" t="n">
+      <c r="W32" s="3" t="n">
         <v>21</v>
       </c>
-      <c r="X30" s="3" t="n">
+      <c r="X32" s="3" t="n">
         <v>22</v>
       </c>
-      <c r="Y30" s="3" t="n">
+      <c r="Y32" s="3" t="n">
         <v>23</v>
       </c>
-      <c r="Z30" s="3" t="n">
+      <c r="Z32" s="3" t="n">
         <v>24</v>
       </c>
-      <c r="AA30" s="3" t="n">
+      <c r="AA32" s="3" t="n">
         <v>25</v>
       </c>
-      <c r="AB30" s="3" t="n">
+      <c r="AB32" s="3" t="n">
         <v>26</v>
       </c>
-      <c r="AC30" s="3" t="n">
+      <c r="AC32" s="3" t="n">
         <v>27</v>
       </c>
-      <c r="AD30" s="3" t="n">
+      <c r="AD32" s="3" t="n">
         <v>28</v>
       </c>
-      <c r="AE30" s="3" t="n">
+      <c r="AE32" s="3" t="n">
         <v>29</v>
       </c>
-      <c r="AF30" s="3" t="n">
+      <c r="AF32" s="3" t="n">
         <v>30</v>
       </c>
-      <c r="AG30" s="3" t="n">
+      <c r="AG32" s="3" t="n">
         <v>31</v>
       </c>
-      <c r="AH30" s="3" t="inlineStr">
+      <c r="AH32" s="3" t="inlineStr">
         <is>
           <t>Promedio
 (dBuV/m)</t>
         </is>
       </c>
-      <c r="AI30" s="3" t="inlineStr">
+      <c r="AI32" s="3" t="inlineStr">
         <is>
           <t>Medición Manual
 AB(KHz) o NIVEL
 (dBµV/m)</t>
         </is>
       </c>
-      <c r="AJ30" s="3" t="inlineStr">
+      <c r="AJ32" s="3" t="inlineStr">
         <is>
           <t>OBSERVACIONES</t>
         </is>
       </c>
-      <c r="AK30" s="4" t="n"/>
-    </row>
-    <row r="31">
-      <c r="A31" s="5" t="inlineStr">
-        <is>
-          <t>RED TELESISTEMA (R.T.S)</t>
-        </is>
-      </c>
-      <c r="B31" s="6" t="n">
-        <v>55.25</v>
-      </c>
-      <c r="C31" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D31" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E31" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F31" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G31" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H31" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I31" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J31" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K31" s="6" t="n">
-        <v>57.55</v>
-      </c>
-      <c r="L31" s="6" t="n">
-        <v>57.75</v>
-      </c>
-      <c r="M31" s="6" t="n">
-        <v>57.28</v>
-      </c>
-      <c r="N31" s="6" t="n">
-        <v>57.49</v>
-      </c>
-      <c r="O31" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P31" s="6" t="n">
-        <v>56.76</v>
-      </c>
-      <c r="Q31" s="6" t="n">
-        <v>55.79</v>
-      </c>
-      <c r="R31" s="6" t="n">
-        <v>54.35</v>
-      </c>
-      <c r="S31" s="6" t="n">
-        <v>56.31</v>
-      </c>
-      <c r="T31" s="6" t="n">
-        <v>55.88</v>
-      </c>
-      <c r="U31" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="V31" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="W31" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="X31" s="6" t="n">
-        <v>55.13</v>
-      </c>
-      <c r="Y31" s="6" t="n">
-        <v>54.41</v>
-      </c>
-      <c r="Z31" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AA31" s="6" t="n">
-        <v>55</v>
-      </c>
-      <c r="AB31" s="6" t="n">
-        <v>55.06</v>
-      </c>
-      <c r="AC31" s="6" t="n">
-        <v>54.2</v>
-      </c>
-      <c r="AD31" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AE31" s="6" t="n">
-        <v>54.14</v>
-      </c>
-      <c r="AF31" s="6" t="n">
-        <v>54.39</v>
-      </c>
-      <c r="AG31" s="6" t="n">
-        <v>54.92</v>
-      </c>
-      <c r="AH31" s="6" t="n">
-        <v>55.67</v>
-      </c>
-      <c r="AI31" s="6" t="inlineStr"/>
-      <c r="AJ31" s="6" t="inlineStr"/>
-      <c r="AK31" s="7" t="n"/>
-    </row>
-    <row r="32">
-      <c r="A32" s="5" t="inlineStr">
-        <is>
-          <t>TELEVISION DEL PACIFICO</t>
-        </is>
-      </c>
-      <c r="B32" s="6" t="n">
-        <v>67.25</v>
-      </c>
-      <c r="C32" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D32" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E32" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F32" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G32" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H32" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I32" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J32" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K32" s="6" t="n">
-        <v>38.7</v>
-      </c>
-      <c r="L32" s="6" t="n">
-        <v>40.12</v>
-      </c>
-      <c r="M32" s="6" t="n">
-        <v>39.56</v>
-      </c>
-      <c r="N32" s="6" t="n">
-        <v>38.39</v>
-      </c>
-      <c r="O32" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P32" s="6" t="n">
-        <v>39.4</v>
-      </c>
-      <c r="Q32" s="6" t="n">
-        <v>38.11</v>
-      </c>
-      <c r="R32" s="6" t="n">
-        <v>39.07</v>
-      </c>
-      <c r="S32" s="6" t="n">
-        <v>38.31</v>
-      </c>
-      <c r="T32" s="6" t="n">
-        <v>38.94</v>
-      </c>
-      <c r="U32" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="V32" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="W32" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="X32" s="6" t="n">
-        <v>39.57</v>
-      </c>
-      <c r="Y32" s="6" t="n">
-        <v>38.75</v>
-      </c>
-      <c r="Z32" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AA32" s="6" t="n">
-        <v>39.83</v>
-      </c>
-      <c r="AB32" s="6" t="n">
-        <v>39.13</v>
-      </c>
-      <c r="AC32" s="6" t="n">
-        <v>38.66</v>
-      </c>
-      <c r="AD32" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AE32" s="6" t="n">
-        <v>40.58</v>
-      </c>
-      <c r="AF32" s="6" t="n">
-        <v>40.04</v>
-      </c>
-      <c r="AG32" s="6" t="n">
-        <v>39.34</v>
-      </c>
-      <c r="AH32" s="6" t="n">
-        <v>39.21</v>
-      </c>
-      <c r="AI32" s="6" t="inlineStr"/>
-      <c r="AJ32" s="6" t="inlineStr"/>
-      <c r="AK32" s="7" t="n"/>
+      <c r="AK32" s="4" t="n"/>
     </row>
     <row r="33">
       <c r="A33" s="5" t="inlineStr">
         <is>
-          <t>TV CATOLICA LOS ENCUENTROS</t>
+          <t>RED TELESISTEMA (R.T.S)</t>
         </is>
       </c>
       <c r="B33" s="6" t="n">
-        <v>77.25</v>
+        <v>55.25</v>
       </c>
       <c r="C33" s="6" t="inlineStr">
         <is>
@@ -2993,16 +2733,16 @@
         </is>
       </c>
       <c r="K33" s="6" t="n">
-        <v>42.34</v>
+        <v>57.55</v>
       </c>
       <c r="L33" s="6" t="n">
-        <v>40.07</v>
+        <v>57.75</v>
       </c>
       <c r="M33" s="6" t="n">
-        <v>41.68</v>
+        <v>57.28</v>
       </c>
       <c r="N33" s="6" t="n">
-        <v>39.71</v>
+        <v>57.49</v>
       </c>
       <c r="O33" s="6" t="inlineStr">
         <is>
@@ -3010,19 +2750,19 @@
         </is>
       </c>
       <c r="P33" s="6" t="n">
-        <v>42.02</v>
+        <v>56.76</v>
       </c>
       <c r="Q33" s="6" t="n">
-        <v>40.85</v>
+        <v>55.79</v>
       </c>
       <c r="R33" s="6" t="n">
-        <v>42.52</v>
+        <v>54.35</v>
       </c>
       <c r="S33" s="6" t="n">
-        <v>40.18</v>
+        <v>56.31</v>
       </c>
       <c r="T33" s="6" t="n">
-        <v>42.59</v>
+        <v>55.88</v>
       </c>
       <c r="U33" s="6" t="inlineStr">
         <is>
@@ -3040,10 +2780,10 @@
         </is>
       </c>
       <c r="X33" s="6" t="n">
-        <v>40.06</v>
+        <v>55.13</v>
       </c>
       <c r="Y33" s="6" t="n">
-        <v>37.89</v>
+        <v>54.41</v>
       </c>
       <c r="Z33" s="6" t="inlineStr">
         <is>
@@ -3051,13 +2791,13 @@
         </is>
       </c>
       <c r="AA33" s="6" t="n">
-        <v>41.15</v>
+        <v>55</v>
       </c>
       <c r="AB33" s="6" t="n">
-        <v>38.92</v>
+        <v>55.06</v>
       </c>
       <c r="AC33" s="6" t="n">
-        <v>39.38</v>
+        <v>54.2</v>
       </c>
       <c r="AD33" s="6" t="inlineStr">
         <is>
@@ -3065,16 +2805,16 @@
         </is>
       </c>
       <c r="AE33" s="6" t="n">
-        <v>40.89</v>
+        <v>54.14</v>
       </c>
       <c r="AF33" s="6" t="n">
-        <v>41.14</v>
+        <v>54.39</v>
       </c>
       <c r="AG33" s="6" t="n">
-        <v>41.74</v>
+        <v>54.92</v>
       </c>
       <c r="AH33" s="6" t="n">
-        <v>40.77</v>
+        <v>55.67</v>
       </c>
       <c r="AI33" s="6" t="inlineStr"/>
       <c r="AJ33" s="6" t="inlineStr"/>
@@ -3083,11 +2823,11 @@
     <row r="34">
       <c r="A34" s="5" t="inlineStr">
         <is>
-          <t>ECUADOR TV</t>
+          <t>TELEVISION DEL PACIFICO</t>
         </is>
       </c>
       <c r="B34" s="6" t="n">
-        <v>175.25</v>
+        <v>67.25</v>
       </c>
       <c r="C34" s="6" t="inlineStr">
         <is>
@@ -3130,16 +2870,16 @@
         </is>
       </c>
       <c r="K34" s="6" t="n">
-        <v>32.85</v>
+        <v>38.7</v>
       </c>
       <c r="L34" s="6" t="n">
-        <v>34.68</v>
+        <v>40.12</v>
       </c>
       <c r="M34" s="6" t="n">
-        <v>34.93</v>
+        <v>39.56</v>
       </c>
       <c r="N34" s="6" t="n">
-        <v>32.62</v>
+        <v>38.39</v>
       </c>
       <c r="O34" s="6" t="inlineStr">
         <is>
@@ -3147,19 +2887,19 @@
         </is>
       </c>
       <c r="P34" s="6" t="n">
-        <v>35.57</v>
+        <v>39.4</v>
       </c>
       <c r="Q34" s="6" t="n">
-        <v>33.22</v>
+        <v>38.11</v>
       </c>
       <c r="R34" s="6" t="n">
-        <v>33.28</v>
+        <v>39.07</v>
       </c>
       <c r="S34" s="6" t="n">
-        <v>33.37</v>
+        <v>38.31</v>
       </c>
       <c r="T34" s="6" t="n">
-        <v>33.94</v>
+        <v>38.94</v>
       </c>
       <c r="U34" s="6" t="inlineStr">
         <is>
@@ -3177,10 +2917,10 @@
         </is>
       </c>
       <c r="X34" s="6" t="n">
-        <v>33.7</v>
+        <v>39.57</v>
       </c>
       <c r="Y34" s="6" t="n">
-        <v>32.97</v>
+        <v>38.75</v>
       </c>
       <c r="Z34" s="6" t="inlineStr">
         <is>
@@ -3188,13 +2928,13 @@
         </is>
       </c>
       <c r="AA34" s="6" t="n">
-        <v>33.07</v>
+        <v>39.83</v>
       </c>
       <c r="AB34" s="6" t="n">
-        <v>33.43</v>
+        <v>39.13</v>
       </c>
       <c r="AC34" s="6" t="n">
-        <v>33.04</v>
+        <v>38.66</v>
       </c>
       <c r="AD34" s="6" t="inlineStr">
         <is>
@@ -3202,16 +2942,16 @@
         </is>
       </c>
       <c r="AE34" s="6" t="n">
-        <v>33.12</v>
+        <v>40.58</v>
       </c>
       <c r="AF34" s="6" t="n">
-        <v>35.94</v>
+        <v>40.04</v>
       </c>
       <c r="AG34" s="6" t="n">
-        <v>33.06</v>
+        <v>39.34</v>
       </c>
       <c r="AH34" s="6" t="n">
-        <v>33.69</v>
+        <v>39.21</v>
       </c>
       <c r="AI34" s="6" t="inlineStr"/>
       <c r="AJ34" s="6" t="inlineStr"/>
@@ -3220,11 +2960,11 @@
     <row r="35">
       <c r="A35" s="5" t="inlineStr">
         <is>
-          <t>UV TELEVISION</t>
+          <t>TV CATOLICA LOS ENCUENTROS</t>
         </is>
       </c>
       <c r="B35" s="6" t="n">
-        <v>187.25</v>
+        <v>77.25</v>
       </c>
       <c r="C35" s="6" t="inlineStr">
         <is>
@@ -3267,16 +3007,16 @@
         </is>
       </c>
       <c r="K35" s="6" t="n">
-        <v>31.68</v>
+        <v>42.34</v>
       </c>
       <c r="L35" s="6" t="n">
-        <v>34.34</v>
+        <v>40.07</v>
       </c>
       <c r="M35" s="6" t="n">
-        <v>34.12</v>
+        <v>41.68</v>
       </c>
       <c r="N35" s="6" t="n">
-        <v>31.96</v>
+        <v>39.71</v>
       </c>
       <c r="O35" s="6" t="inlineStr">
         <is>
@@ -3284,19 +3024,19 @@
         </is>
       </c>
       <c r="P35" s="6" t="n">
-        <v>32.38</v>
+        <v>42.02</v>
       </c>
       <c r="Q35" s="6" t="n">
-        <v>33.12</v>
+        <v>40.85</v>
       </c>
       <c r="R35" s="6" t="n">
-        <v>33.15</v>
+        <v>42.52</v>
       </c>
       <c r="S35" s="6" t="n">
-        <v>31.32</v>
+        <v>40.18</v>
       </c>
       <c r="T35" s="6" t="n">
-        <v>31.71</v>
+        <v>42.59</v>
       </c>
       <c r="U35" s="6" t="inlineStr">
         <is>
@@ -3314,10 +3054,10 @@
         </is>
       </c>
       <c r="X35" s="6" t="n">
-        <v>32.34</v>
+        <v>40.06</v>
       </c>
       <c r="Y35" s="6" t="n">
-        <v>32.37</v>
+        <v>37.89</v>
       </c>
       <c r="Z35" s="6" t="inlineStr">
         <is>
@@ -3325,13 +3065,13 @@
         </is>
       </c>
       <c r="AA35" s="6" t="n">
-        <v>32.65</v>
+        <v>41.15</v>
       </c>
       <c r="AB35" s="6" t="n">
-        <v>33.45</v>
+        <v>38.92</v>
       </c>
       <c r="AC35" s="6" t="n">
-        <v>31.78</v>
+        <v>39.38</v>
       </c>
       <c r="AD35" s="6" t="inlineStr">
         <is>
@@ -3339,16 +3079,16 @@
         </is>
       </c>
       <c r="AE35" s="6" t="n">
-        <v>31.59</v>
+        <v>40.89</v>
       </c>
       <c r="AF35" s="6" t="n">
-        <v>33.82</v>
+        <v>41.14</v>
       </c>
       <c r="AG35" s="6" t="n">
-        <v>31.83</v>
+        <v>41.74</v>
       </c>
       <c r="AH35" s="6" t="n">
-        <v>32.57</v>
+        <v>40.77</v>
       </c>
       <c r="AI35" s="6" t="inlineStr"/>
       <c r="AJ35" s="6" t="inlineStr"/>
@@ -3357,11 +3097,11 @@
     <row r="36">
       <c r="A36" s="5" t="inlineStr">
         <is>
-          <t>TELEAMAZONAS</t>
+          <t>ECUADOR TV</t>
         </is>
       </c>
       <c r="B36" s="6" t="n">
-        <v>199.25</v>
+        <v>175.25</v>
       </c>
       <c r="C36" s="6" t="inlineStr">
         <is>
@@ -3404,16 +3144,16 @@
         </is>
       </c>
       <c r="K36" s="6" t="n">
-        <v>30.38</v>
+        <v>32.85</v>
       </c>
       <c r="L36" s="6" t="n">
-        <v>33.09</v>
+        <v>34.68</v>
       </c>
       <c r="M36" s="6" t="n">
-        <v>32.21</v>
+        <v>34.93</v>
       </c>
       <c r="N36" s="6" t="n">
-        <v>30.17</v>
+        <v>32.62</v>
       </c>
       <c r="O36" s="6" t="inlineStr">
         <is>
@@ -3421,19 +3161,19 @@
         </is>
       </c>
       <c r="P36" s="6" t="n">
-        <v>32.04</v>
+        <v>35.57</v>
       </c>
       <c r="Q36" s="6" t="n">
-        <v>30.86</v>
+        <v>33.22</v>
       </c>
       <c r="R36" s="6" t="n">
-        <v>30.69</v>
+        <v>33.28</v>
       </c>
       <c r="S36" s="6" t="n">
-        <v>30.45</v>
+        <v>33.37</v>
       </c>
       <c r="T36" s="6" t="n">
-        <v>30.94</v>
+        <v>33.94</v>
       </c>
       <c r="U36" s="6" t="inlineStr">
         <is>
@@ -3451,10 +3191,10 @@
         </is>
       </c>
       <c r="X36" s="6" t="n">
-        <v>31.18</v>
+        <v>33.7</v>
       </c>
       <c r="Y36" s="6" t="n">
-        <v>30.95</v>
+        <v>32.97</v>
       </c>
       <c r="Z36" s="6" t="inlineStr">
         <is>
@@ -3462,13 +3202,13 @@
         </is>
       </c>
       <c r="AA36" s="6" t="n">
-        <v>30.83</v>
+        <v>33.07</v>
       </c>
       <c r="AB36" s="6" t="n">
-        <v>31.03</v>
+        <v>33.43</v>
       </c>
       <c r="AC36" s="6" t="n">
-        <v>30.71</v>
+        <v>33.04</v>
       </c>
       <c r="AD36" s="6" t="inlineStr">
         <is>
@@ -3476,16 +3216,16 @@
         </is>
       </c>
       <c r="AE36" s="6" t="n">
-        <v>30.44</v>
+        <v>33.12</v>
       </c>
       <c r="AF36" s="6" t="n">
-        <v>33.05</v>
+        <v>35.94</v>
       </c>
       <c r="AG36" s="6" t="n">
-        <v>30.7</v>
+        <v>33.06</v>
       </c>
       <c r="AH36" s="6" t="n">
-        <v>31.16</v>
+        <v>33.69</v>
       </c>
       <c r="AI36" s="6" t="inlineStr"/>
       <c r="AJ36" s="6" t="inlineStr"/>
@@ -3494,11 +3234,11 @@
     <row r="37">
       <c r="A37" s="5" t="inlineStr">
         <is>
-          <t>CADENA ECUATORIANA DE TELE</t>
+          <t>UV TELEVISION</t>
         </is>
       </c>
       <c r="B37" s="6" t="n">
-        <v>211.25</v>
+        <v>187.25</v>
       </c>
       <c r="C37" s="6" t="inlineStr">
         <is>
@@ -3541,16 +3281,16 @@
         </is>
       </c>
       <c r="K37" s="6" t="n">
-        <v>29.23</v>
+        <v>31.68</v>
       </c>
       <c r="L37" s="6" t="n">
-        <v>29.27</v>
+        <v>34.34</v>
       </c>
       <c r="M37" s="6" t="n">
-        <v>29.72</v>
+        <v>34.12</v>
       </c>
       <c r="N37" s="6" t="n">
-        <v>28.44</v>
+        <v>31.96</v>
       </c>
       <c r="O37" s="6" t="inlineStr">
         <is>
@@ -3558,19 +3298,19 @@
         </is>
       </c>
       <c r="P37" s="6" t="n">
-        <v>29.66</v>
+        <v>32.38</v>
       </c>
       <c r="Q37" s="6" t="n">
-        <v>28.68</v>
+        <v>33.12</v>
       </c>
       <c r="R37" s="6" t="n">
-        <v>29.01</v>
+        <v>33.15</v>
       </c>
       <c r="S37" s="6" t="n">
-        <v>28.72</v>
+        <v>31.32</v>
       </c>
       <c r="T37" s="6" t="n">
-        <v>29.25</v>
+        <v>31.71</v>
       </c>
       <c r="U37" s="6" t="inlineStr">
         <is>
@@ -3588,10 +3328,10 @@
         </is>
       </c>
       <c r="X37" s="6" t="n">
-        <v>29.75</v>
+        <v>32.34</v>
       </c>
       <c r="Y37" s="6" t="n">
-        <v>29.47</v>
+        <v>32.37</v>
       </c>
       <c r="Z37" s="6" t="inlineStr">
         <is>
@@ -3599,13 +3339,13 @@
         </is>
       </c>
       <c r="AA37" s="6" t="n">
-        <v>29.05</v>
+        <v>32.65</v>
       </c>
       <c r="AB37" s="6" t="n">
-        <v>29.35</v>
+        <v>33.45</v>
       </c>
       <c r="AC37" s="6" t="n">
-        <v>28.38</v>
+        <v>31.78</v>
       </c>
       <c r="AD37" s="6" t="inlineStr">
         <is>
@@ -3613,16 +3353,16 @@
         </is>
       </c>
       <c r="AE37" s="6" t="n">
-        <v>29.33</v>
+        <v>31.59</v>
       </c>
       <c r="AF37" s="6" t="n">
-        <v>29.64</v>
+        <v>33.82</v>
       </c>
       <c r="AG37" s="6" t="n">
-        <v>29.19</v>
+        <v>31.83</v>
       </c>
       <c r="AH37" s="6" t="n">
-        <v>29.19</v>
+        <v>32.57</v>
       </c>
       <c r="AI37" s="6" t="inlineStr"/>
       <c r="AJ37" s="6" t="inlineStr"/>
@@ -3631,11 +3371,11 @@
     <row r="38">
       <c r="A38" s="5" t="inlineStr">
         <is>
-          <t>UCSG TELEVISION</t>
+          <t>TELEAMAZONAS</t>
         </is>
       </c>
       <c r="B38" s="6" t="n">
-        <v>525.25</v>
+        <v>199.25</v>
       </c>
       <c r="C38" s="6" t="inlineStr">
         <is>
@@ -3678,16 +3418,16 @@
         </is>
       </c>
       <c r="K38" s="6" t="n">
-        <v>26.49</v>
+        <v>30.38</v>
       </c>
       <c r="L38" s="6" t="n">
-        <v>26.61</v>
+        <v>33.09</v>
       </c>
       <c r="M38" s="6" t="n">
-        <v>26.76</v>
+        <v>32.21</v>
       </c>
       <c r="N38" s="6" t="n">
-        <v>26.86</v>
+        <v>30.17</v>
       </c>
       <c r="O38" s="6" t="inlineStr">
         <is>
@@ -3695,19 +3435,19 @@
         </is>
       </c>
       <c r="P38" s="6" t="n">
-        <v>26.77</v>
+        <v>32.04</v>
       </c>
       <c r="Q38" s="6" t="n">
-        <v>26.84</v>
+        <v>30.86</v>
       </c>
       <c r="R38" s="6" t="n">
-        <v>27.65</v>
+        <v>30.69</v>
       </c>
       <c r="S38" s="6" t="n">
-        <v>26.75</v>
+        <v>30.45</v>
       </c>
       <c r="T38" s="6" t="n">
-        <v>26.91</v>
+        <v>30.94</v>
       </c>
       <c r="U38" s="6" t="inlineStr">
         <is>
@@ -3725,10 +3465,10 @@
         </is>
       </c>
       <c r="X38" s="6" t="n">
-        <v>26.82</v>
+        <v>31.18</v>
       </c>
       <c r="Y38" s="6" t="n">
-        <v>26.87</v>
+        <v>30.95</v>
       </c>
       <c r="Z38" s="6" t="inlineStr">
         <is>
@@ -3736,13 +3476,13 @@
         </is>
       </c>
       <c r="AA38" s="6" t="n">
-        <v>26.65</v>
+        <v>30.83</v>
       </c>
       <c r="AB38" s="6" t="n">
-        <v>26.82</v>
+        <v>31.03</v>
       </c>
       <c r="AC38" s="6" t="n">
-        <v>26.56</v>
+        <v>30.71</v>
       </c>
       <c r="AD38" s="6" t="inlineStr">
         <is>
@@ -3750,16 +3490,16 @@
         </is>
       </c>
       <c r="AE38" s="6" t="n">
-        <v>26.93</v>
+        <v>30.44</v>
       </c>
       <c r="AF38" s="6" t="n">
-        <v>26.84</v>
+        <v>33.05</v>
       </c>
       <c r="AG38" s="6" t="n">
-        <v>26.69</v>
+        <v>30.7</v>
       </c>
       <c r="AH38" s="6" t="n">
-        <v>26.81</v>
+        <v>31.16</v>
       </c>
       <c r="AI38" s="6" t="inlineStr"/>
       <c r="AJ38" s="6" t="inlineStr"/>
@@ -3768,11 +3508,11 @@
     <row r="39">
       <c r="A39" s="5" t="inlineStr">
         <is>
-          <t>OROMAR</t>
+          <t>CADENA ECUATORIANA DE TELE</t>
         </is>
       </c>
       <c r="B39" s="6" t="n">
-        <v>537.25</v>
+        <v>211.25</v>
       </c>
       <c r="C39" s="6" t="inlineStr">
         <is>
@@ -3815,16 +3555,16 @@
         </is>
       </c>
       <c r="K39" s="6" t="n">
-        <v>26.63</v>
+        <v>29.23</v>
       </c>
       <c r="L39" s="6" t="n">
-        <v>26.96</v>
+        <v>29.27</v>
       </c>
       <c r="M39" s="6" t="n">
-        <v>26.84</v>
+        <v>29.72</v>
       </c>
       <c r="N39" s="6" t="n">
-        <v>26.93</v>
+        <v>28.44</v>
       </c>
       <c r="O39" s="6" t="inlineStr">
         <is>
@@ -3832,19 +3572,19 @@
         </is>
       </c>
       <c r="P39" s="6" t="n">
-        <v>27.04</v>
+        <v>29.66</v>
       </c>
       <c r="Q39" s="6" t="n">
-        <v>26.67</v>
+        <v>28.68</v>
       </c>
       <c r="R39" s="6" t="n">
-        <v>26.77</v>
+        <v>29.01</v>
       </c>
       <c r="S39" s="6" t="n">
-        <v>26.6</v>
+        <v>28.72</v>
       </c>
       <c r="T39" s="6" t="n">
-        <v>27.2</v>
+        <v>29.25</v>
       </c>
       <c r="U39" s="6" t="inlineStr">
         <is>
@@ -3862,10 +3602,10 @@
         </is>
       </c>
       <c r="X39" s="6" t="n">
-        <v>26.92</v>
+        <v>29.75</v>
       </c>
       <c r="Y39" s="6" t="n">
-        <v>27.06</v>
+        <v>29.47</v>
       </c>
       <c r="Z39" s="6" t="inlineStr">
         <is>
@@ -3873,13 +3613,13 @@
         </is>
       </c>
       <c r="AA39" s="6" t="n">
-        <v>26.83</v>
+        <v>29.05</v>
       </c>
       <c r="AB39" s="6" t="n">
-        <v>26.85</v>
+        <v>29.35</v>
       </c>
       <c r="AC39" s="6" t="n">
-        <v>26.68</v>
+        <v>28.38</v>
       </c>
       <c r="AD39" s="6" t="inlineStr">
         <is>
@@ -3887,16 +3627,16 @@
         </is>
       </c>
       <c r="AE39" s="6" t="n">
-        <v>27.21</v>
+        <v>29.33</v>
       </c>
       <c r="AF39" s="6" t="n">
-        <v>27.19</v>
+        <v>29.64</v>
       </c>
       <c r="AG39" s="6" t="n">
-        <v>26.73</v>
+        <v>29.19</v>
       </c>
       <c r="AH39" s="6" t="n">
-        <v>26.89</v>
+        <v>29.19</v>
       </c>
       <c r="AI39" s="6" t="inlineStr"/>
       <c r="AJ39" s="6" t="inlineStr"/>
@@ -3905,11 +3645,11 @@
     <row r="40">
       <c r="A40" s="5" t="inlineStr">
         <is>
-          <t>TV LEGISLATIVA</t>
+          <t>UCSG TELEVISION</t>
         </is>
       </c>
       <c r="B40" s="6" t="n">
-        <v>549.25</v>
+        <v>525.25</v>
       </c>
       <c r="C40" s="6" t="inlineStr">
         <is>
@@ -3952,16 +3692,16 @@
         </is>
       </c>
       <c r="K40" s="6" t="n">
-        <v>27.35</v>
+        <v>26.49</v>
       </c>
       <c r="L40" s="6" t="n">
-        <v>27.68</v>
+        <v>26.61</v>
       </c>
       <c r="M40" s="6" t="n">
-        <v>26.97</v>
+        <v>26.76</v>
       </c>
       <c r="N40" s="6" t="n">
-        <v>27.55</v>
+        <v>26.86</v>
       </c>
       <c r="O40" s="6" t="inlineStr">
         <is>
@@ -3969,19 +3709,19 @@
         </is>
       </c>
       <c r="P40" s="6" t="n">
-        <v>28.86</v>
+        <v>26.77</v>
       </c>
       <c r="Q40" s="6" t="n">
-        <v>27.39</v>
+        <v>26.84</v>
       </c>
       <c r="R40" s="6" t="n">
-        <v>29.27</v>
+        <v>27.65</v>
       </c>
       <c r="S40" s="6" t="n">
-        <v>27.56</v>
+        <v>26.75</v>
       </c>
       <c r="T40" s="6" t="n">
-        <v>28.35</v>
+        <v>26.91</v>
       </c>
       <c r="U40" s="6" t="inlineStr">
         <is>
@@ -3999,10 +3739,10 @@
         </is>
       </c>
       <c r="X40" s="6" t="n">
-        <v>27.35</v>
+        <v>26.82</v>
       </c>
       <c r="Y40" s="6" t="n">
-        <v>27.39</v>
+        <v>26.87</v>
       </c>
       <c r="Z40" s="6" t="inlineStr">
         <is>
@@ -4010,13 +3750,13 @@
         </is>
       </c>
       <c r="AA40" s="6" t="n">
-        <v>27.07</v>
+        <v>26.65</v>
       </c>
       <c r="AB40" s="6" t="n">
-        <v>27.45</v>
+        <v>26.82</v>
       </c>
       <c r="AC40" s="6" t="n">
-        <v>27.13</v>
+        <v>26.56</v>
       </c>
       <c r="AD40" s="6" t="inlineStr">
         <is>
@@ -4024,173 +3764,449 @@
         </is>
       </c>
       <c r="AE40" s="6" t="n">
-        <v>27.25</v>
+        <v>26.93</v>
       </c>
       <c r="AF40" s="6" t="n">
-        <v>27.71</v>
+        <v>26.84</v>
       </c>
       <c r="AG40" s="6" t="n">
-        <v>27.53</v>
+        <v>26.69</v>
       </c>
       <c r="AH40" s="6" t="n">
-        <v>27.64</v>
+        <v>26.81</v>
       </c>
       <c r="AI40" s="6" t="inlineStr"/>
       <c r="AJ40" s="6" t="inlineStr"/>
       <c r="AK40" s="7" t="n"/>
     </row>
     <row r="41">
-      <c r="A41" s="8" t="inlineStr">
+      <c r="A41" s="5" t="inlineStr">
+        <is>
+          <t>OROMAR</t>
+        </is>
+      </c>
+      <c r="B41" s="6" t="n">
+        <v>537.25</v>
+      </c>
+      <c r="C41" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D41" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E41" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F41" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G41" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H41" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I41" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J41" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K41" s="6" t="n">
+        <v>26.63</v>
+      </c>
+      <c r="L41" s="6" t="n">
+        <v>26.96</v>
+      </c>
+      <c r="M41" s="6" t="n">
+        <v>26.84</v>
+      </c>
+      <c r="N41" s="6" t="n">
+        <v>26.93</v>
+      </c>
+      <c r="O41" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P41" s="6" t="n">
+        <v>27.04</v>
+      </c>
+      <c r="Q41" s="6" t="n">
+        <v>26.67</v>
+      </c>
+      <c r="R41" s="6" t="n">
+        <v>26.77</v>
+      </c>
+      <c r="S41" s="6" t="n">
+        <v>26.6</v>
+      </c>
+      <c r="T41" s="6" t="n">
+        <v>27.2</v>
+      </c>
+      <c r="U41" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="V41" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="W41" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="X41" s="6" t="n">
+        <v>26.92</v>
+      </c>
+      <c r="Y41" s="6" t="n">
+        <v>27.06</v>
+      </c>
+      <c r="Z41" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AA41" s="6" t="n">
+        <v>26.83</v>
+      </c>
+      <c r="AB41" s="6" t="n">
+        <v>26.85</v>
+      </c>
+      <c r="AC41" s="6" t="n">
+        <v>26.68</v>
+      </c>
+      <c r="AD41" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AE41" s="6" t="n">
+        <v>27.21</v>
+      </c>
+      <c r="AF41" s="6" t="n">
+        <v>27.19</v>
+      </c>
+      <c r="AG41" s="6" t="n">
+        <v>26.73</v>
+      </c>
+      <c r="AH41" s="6" t="n">
+        <v>26.89</v>
+      </c>
+      <c r="AI41" s="6" t="inlineStr"/>
+      <c r="AJ41" s="6" t="inlineStr"/>
+      <c r="AK41" s="7" t="n"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="5" t="inlineStr">
+        <is>
+          <t>TV LEGISLATIVA</t>
+        </is>
+      </c>
+      <c r="B42" s="6" t="n">
+        <v>549.25</v>
+      </c>
+      <c r="C42" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D42" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E42" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F42" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G42" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H42" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I42" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J42" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K42" s="6" t="n">
+        <v>27.35</v>
+      </c>
+      <c r="L42" s="6" t="n">
+        <v>27.68</v>
+      </c>
+      <c r="M42" s="6" t="n">
+        <v>26.97</v>
+      </c>
+      <c r="N42" s="6" t="n">
+        <v>27.55</v>
+      </c>
+      <c r="O42" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P42" s="6" t="n">
+        <v>28.86</v>
+      </c>
+      <c r="Q42" s="6" t="n">
+        <v>27.39</v>
+      </c>
+      <c r="R42" s="6" t="n">
+        <v>29.27</v>
+      </c>
+      <c r="S42" s="6" t="n">
+        <v>27.56</v>
+      </c>
+      <c r="T42" s="6" t="n">
+        <v>28.35</v>
+      </c>
+      <c r="U42" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="V42" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="W42" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="X42" s="6" t="n">
+        <v>27.35</v>
+      </c>
+      <c r="Y42" s="6" t="n">
+        <v>27.39</v>
+      </c>
+      <c r="Z42" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AA42" s="6" t="n">
+        <v>27.07</v>
+      </c>
+      <c r="AB42" s="6" t="n">
+        <v>27.45</v>
+      </c>
+      <c r="AC42" s="6" t="n">
+        <v>27.13</v>
+      </c>
+      <c r="AD42" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AE42" s="6" t="n">
+        <v>27.25</v>
+      </c>
+      <c r="AF42" s="6" t="n">
+        <v>27.71</v>
+      </c>
+      <c r="AG42" s="6" t="n">
+        <v>27.53</v>
+      </c>
+      <c r="AH42" s="6" t="n">
+        <v>27.64</v>
+      </c>
+      <c r="AI42" s="6" t="inlineStr"/>
+      <c r="AJ42" s="6" t="inlineStr"/>
+      <c r="AK42" s="7" t="n"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="8" t="inlineStr">
         <is>
           <t>TELECIUDADANA</t>
         </is>
       </c>
-      <c r="B41" s="9" t="n">
+      <c r="B43" s="9" t="n">
         <v>681.25</v>
       </c>
-      <c r="C41" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D41" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E41" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F41" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G41" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H41" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I41" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J41" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K41" s="9" t="n">
+      <c r="C43" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D43" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E43" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F43" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G43" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H43" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I43" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J43" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K43" s="9" t="n">
         <v>27.51</v>
       </c>
-      <c r="L41" s="9" t="n">
+      <c r="L43" s="9" t="n">
         <v>27.51</v>
       </c>
-      <c r="M41" s="9" t="n">
+      <c r="M43" s="9" t="n">
         <v>27.42</v>
       </c>
-      <c r="N41" s="9" t="n">
+      <c r="N43" s="9" t="n">
         <v>27.63</v>
       </c>
-      <c r="O41" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P41" s="9" t="n">
+      <c r="O43" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P43" s="9" t="n">
         <v>27.18</v>
       </c>
-      <c r="Q41" s="9" t="n">
+      <c r="Q43" s="9" t="n">
         <v>27.42</v>
       </c>
-      <c r="R41" s="9" t="n">
+      <c r="R43" s="9" t="n">
         <v>29.01</v>
       </c>
-      <c r="S41" s="9" t="n">
+      <c r="S43" s="9" t="n">
         <v>27.59</v>
       </c>
-      <c r="T41" s="9" t="n">
+      <c r="T43" s="9" t="n">
         <v>27.61</v>
       </c>
-      <c r="U41" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="V41" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="W41" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="X41" s="9" t="n">
+      <c r="U43" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="V43" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="W43" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="X43" s="9" t="n">
         <v>27.49</v>
       </c>
-      <c r="Y41" s="9" t="n">
+      <c r="Y43" s="9" t="n">
         <v>27.51</v>
       </c>
-      <c r="Z41" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AA41" s="9" t="n">
+      <c r="Z43" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AA43" s="9" t="n">
         <v>27.53</v>
       </c>
-      <c r="AB41" s="9" t="n">
+      <c r="AB43" s="9" t="n">
         <v>27.47</v>
       </c>
-      <c r="AC41" s="9" t="n">
+      <c r="AC43" s="9" t="n">
         <v>27.33</v>
       </c>
-      <c r="AD41" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AE41" s="9" t="n">
+      <c r="AD43" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AE43" s="9" t="n">
         <v>27.68</v>
       </c>
-      <c r="AF41" s="9" t="n">
+      <c r="AF43" s="9" t="n">
         <v>27.72</v>
       </c>
-      <c r="AG41" s="9" t="n">
+      <c r="AG43" s="9" t="n">
         <v>27.44</v>
       </c>
-      <c r="AH41" s="9" t="n">
+      <c r="AH43" s="9" t="n">
         <v>27.59</v>
       </c>
-      <c r="AI41" s="9" t="inlineStr"/>
-      <c r="AJ41" s="9" t="inlineStr"/>
-      <c r="AK41" s="10" t="n"/>
+      <c r="AI43" s="9" t="inlineStr"/>
+      <c r="AJ43" s="9" t="inlineStr"/>
+      <c r="AK43" s="10" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="14">
+  <mergeCells count="16">
     <mergeCell ref="A5:AK5"/>
     <mergeCell ref="A4:AK4"/>
     <mergeCell ref="A3:AK3"/>
     <mergeCell ref="A26:AK26"/>
+    <mergeCell ref="A30:AK30"/>
+    <mergeCell ref="A31:AK31"/>
     <mergeCell ref="A29:AK29"/>
     <mergeCell ref="A7:AK7"/>
     <mergeCell ref="A25:AK25"/>
-    <mergeCell ref="A24:AK24"/>
     <mergeCell ref="A2:AK2"/>
     <mergeCell ref="A28:AK28"/>
     <mergeCell ref="A1:AK1"/>
-    <mergeCell ref="A23:AK23"/>
+    <mergeCell ref="A9:AK9"/>
     <mergeCell ref="A27:AK27"/>
+    <mergeCell ref="A8:AK8"/>
     <mergeCell ref="A6:AK6"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/ReportesUnificados/zamora_ReporteUnificado.xlsx
+++ b/ReportesUnificados/zamora_ReporteUnificado.xlsx
@@ -218,7 +218,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>3</row>
+      <row>2</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="4762500" cy="952500"/>
@@ -268,7 +268,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>27</row>
+      <row>26</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="4762500" cy="952500"/>

--- a/ReportesUnificados/zamora_ReporteUnificado.xlsx
+++ b/ReportesUnificados/zamora_ReporteUnificado.xlsx
@@ -38,7 +38,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="10">
+  <borders count="17">
     <border>
       <left/>
       <right/>
@@ -100,11 +100,60 @@
       <top style="thin"/>
       <bottom style="medium"/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin"/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="medium"/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium"/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin"/>
+      <top style="medium"/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin"/>
+      <top style="medium"/>
+      <bottom style="thin"/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -136,6 +185,9 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -644,7 +696,7 @@
     <col width="8" customWidth="1" min="33" max="33"/>
     <col width="15" customWidth="1" min="34" max="34"/>
     <col width="23" customWidth="1" min="35" max="35"/>
-    <col width="23" customWidth="1" min="36" max="36"/>
+    <col width="38" customWidth="1" min="36" max="36"/>
     <col width="15" customWidth="1" min="37" max="37"/>
   </cols>
   <sheetData>
@@ -2681,7 +2733,7 @@
           <t>OBSERVACIONES</t>
         </is>
       </c>
-      <c r="AK32" s="4" t="n"/>
+      <c r="AK32" s="11" t="n"/>
     </row>
     <row r="33">
       <c r="A33" s="5" t="inlineStr">
@@ -2818,7 +2870,7 @@
       </c>
       <c r="AI33" s="6" t="inlineStr"/>
       <c r="AJ33" s="6" t="inlineStr"/>
-      <c r="AK33" s="7" t="n"/>
+      <c r="AK33" s="12" t="n"/>
     </row>
     <row r="34">
       <c r="A34" s="5" t="inlineStr">
@@ -2955,7 +3007,7 @@
       </c>
       <c r="AI34" s="6" t="inlineStr"/>
       <c r="AJ34" s="6" t="inlineStr"/>
-      <c r="AK34" s="7" t="n"/>
+      <c r="AK34" s="12" t="n"/>
     </row>
     <row r="35">
       <c r="A35" s="5" t="inlineStr">
@@ -3092,7 +3144,7 @@
       </c>
       <c r="AI35" s="6" t="inlineStr"/>
       <c r="AJ35" s="6" t="inlineStr"/>
-      <c r="AK35" s="7" t="n"/>
+      <c r="AK35" s="12" t="n"/>
     </row>
     <row r="36">
       <c r="A36" s="5" t="inlineStr">
@@ -3229,7 +3281,7 @@
       </c>
       <c r="AI36" s="6" t="inlineStr"/>
       <c r="AJ36" s="6" t="inlineStr"/>
-      <c r="AK36" s="7" t="n"/>
+      <c r="AK36" s="12" t="n"/>
     </row>
     <row r="37">
       <c r="A37" s="5" t="inlineStr">
@@ -3366,7 +3418,7 @@
       </c>
       <c r="AI37" s="6" t="inlineStr"/>
       <c r="AJ37" s="6" t="inlineStr"/>
-      <c r="AK37" s="7" t="n"/>
+      <c r="AK37" s="12" t="n"/>
     </row>
     <row r="38">
       <c r="A38" s="5" t="inlineStr">
@@ -3503,7 +3555,7 @@
       </c>
       <c r="AI38" s="6" t="inlineStr"/>
       <c r="AJ38" s="6" t="inlineStr"/>
-      <c r="AK38" s="7" t="n"/>
+      <c r="AK38" s="12" t="n"/>
     </row>
     <row r="39">
       <c r="A39" s="5" t="inlineStr">
@@ -3640,7 +3692,7 @@
       </c>
       <c r="AI39" s="6" t="inlineStr"/>
       <c r="AJ39" s="6" t="inlineStr"/>
-      <c r="AK39" s="7" t="n"/>
+      <c r="AK39" s="12" t="n"/>
     </row>
     <row r="40">
       <c r="A40" s="5" t="inlineStr">
@@ -3777,7 +3829,7 @@
       </c>
       <c r="AI40" s="6" t="inlineStr"/>
       <c r="AJ40" s="6" t="inlineStr"/>
-      <c r="AK40" s="7" t="n"/>
+      <c r="AK40" s="12" t="n"/>
     </row>
     <row r="41">
       <c r="A41" s="5" t="inlineStr">
@@ -3914,7 +3966,7 @@
       </c>
       <c r="AI41" s="6" t="inlineStr"/>
       <c r="AJ41" s="6" t="inlineStr"/>
-      <c r="AK41" s="7" t="n"/>
+      <c r="AK41" s="12" t="n"/>
     </row>
     <row r="42">
       <c r="A42" s="5" t="inlineStr">
@@ -4051,7 +4103,7 @@
       </c>
       <c r="AI42" s="6" t="inlineStr"/>
       <c r="AJ42" s="6" t="inlineStr"/>
-      <c r="AK42" s="7" t="n"/>
+      <c r="AK42" s="12" t="n"/>
     </row>
     <row r="43">
       <c r="A43" s="8" t="inlineStr">
@@ -4188,26 +4240,38 @@
       </c>
       <c r="AI43" s="9" t="inlineStr"/>
       <c r="AJ43" s="9" t="inlineStr"/>
-      <c r="AK43" s="10" t="n"/>
+      <c r="AK43" s="13" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="16">
-    <mergeCell ref="A5:AK5"/>
-    <mergeCell ref="A4:AK4"/>
+  <mergeCells count="28">
     <mergeCell ref="A3:AK3"/>
     <mergeCell ref="A26:AK26"/>
+    <mergeCell ref="AJ43:AK43"/>
+    <mergeCell ref="A2:AK2"/>
+    <mergeCell ref="AJ40:AK40"/>
+    <mergeCell ref="AJ42:AK42"/>
+    <mergeCell ref="A5:AK5"/>
+    <mergeCell ref="A8:AK8"/>
+    <mergeCell ref="AJ39:AK39"/>
+    <mergeCell ref="A4:AK4"/>
+    <mergeCell ref="A29:AK29"/>
+    <mergeCell ref="A28:AK28"/>
+    <mergeCell ref="AJ38:AK38"/>
+    <mergeCell ref="A9:AK9"/>
+    <mergeCell ref="A31:AK31"/>
     <mergeCell ref="A30:AK30"/>
-    <mergeCell ref="A31:AK31"/>
-    <mergeCell ref="A29:AK29"/>
+    <mergeCell ref="AJ34:AK34"/>
+    <mergeCell ref="AJ37:AK37"/>
+    <mergeCell ref="AJ33:AK33"/>
+    <mergeCell ref="A1:AK1"/>
+    <mergeCell ref="AJ36:AK36"/>
+    <mergeCell ref="A6:AK6"/>
+    <mergeCell ref="AJ35:AK35"/>
     <mergeCell ref="A7:AK7"/>
     <mergeCell ref="A25:AK25"/>
-    <mergeCell ref="A2:AK2"/>
-    <mergeCell ref="A28:AK28"/>
-    <mergeCell ref="A1:AK1"/>
-    <mergeCell ref="A9:AK9"/>
+    <mergeCell ref="AJ41:AK41"/>
+    <mergeCell ref="AJ32:AK32"/>
     <mergeCell ref="A27:AK27"/>
-    <mergeCell ref="A8:AK8"/>
-    <mergeCell ref="A6:AK6"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>

--- a/ReportesUnificados/zamora_ReporteUnificado.xlsx
+++ b/ReportesUnificados/zamora_ReporteUnificado.xlsx
@@ -30,12 +30,30 @@
       <sz val="12"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCDFECE"/>
+        <bgColor rgb="FFCDFECE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFE9F"/>
+        <bgColor rgb="FFFFFE9F"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFD9BCB"/>
+        <bgColor rgb="FFFD9BCB"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="17">
@@ -153,7 +171,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -173,6 +191,15 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -182,11 +209,17 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="16" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="12" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="13" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
@@ -759,7 +792,7 @@
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>FECHA PRESENTACIÓN: 27/08/2025</t>
+          <t>FECHA PRESENTACIÓN: 28/08/2025</t>
         </is>
       </c>
     </row>
@@ -941,16 +974,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="K11" s="6" t="n">
+      <c r="K11" s="7" t="n">
         <v>56.96</v>
       </c>
-      <c r="L11" s="6" t="n">
+      <c r="L11" s="7" t="n">
         <v>54.92</v>
       </c>
-      <c r="M11" s="6" t="n">
+      <c r="M11" s="7" t="n">
         <v>55.02</v>
       </c>
-      <c r="N11" s="6" t="n">
+      <c r="N11" s="8" t="n">
         <v>53.54</v>
       </c>
       <c r="O11" s="6" t="inlineStr">
@@ -958,19 +991,19 @@
           <t>-</t>
         </is>
       </c>
-      <c r="P11" s="6" t="n">
+      <c r="P11" s="9" t="n">
         <v>41.6</v>
       </c>
-      <c r="Q11" s="6" t="n">
+      <c r="Q11" s="9" t="n">
         <v>40.72</v>
       </c>
-      <c r="R11" s="6" t="n">
+      <c r="R11" s="9" t="n">
         <v>39.48</v>
       </c>
-      <c r="S11" s="6" t="n">
+      <c r="S11" s="9" t="n">
         <v>39</v>
       </c>
-      <c r="T11" s="6" t="n">
+      <c r="T11" s="9" t="n">
         <v>39.18</v>
       </c>
       <c r="U11" s="6" t="inlineStr">
@@ -988,10 +1021,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="X11" s="6" t="n">
+      <c r="X11" s="8" t="n">
         <v>43.07</v>
       </c>
-      <c r="Y11" s="6" t="n">
+      <c r="Y11" s="9" t="n">
         <v>38.32</v>
       </c>
       <c r="Z11" s="6" t="inlineStr">
@@ -999,13 +1032,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="AA11" s="6" t="n">
+      <c r="AA11" s="8" t="n">
         <v>46.74</v>
       </c>
-      <c r="AB11" s="6" t="n">
+      <c r="AB11" s="8" t="n">
         <v>43.68</v>
       </c>
-      <c r="AC11" s="6" t="n">
+      <c r="AC11" s="9" t="n">
         <v>40.17</v>
       </c>
       <c r="AD11" s="6" t="inlineStr">
@@ -1013,13 +1046,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="AE11" s="6" t="n">
+      <c r="AE11" s="9" t="n">
         <v>42.11</v>
       </c>
-      <c r="AF11" s="6" t="n">
+      <c r="AF11" s="9" t="n">
         <v>40.11</v>
       </c>
-      <c r="AG11" s="6" t="n">
+      <c r="AG11" s="9" t="n">
         <v>41.92</v>
       </c>
       <c r="AH11" s="6" t="n">
@@ -1029,7 +1062,7 @@
         <v>485.74</v>
       </c>
       <c r="AJ11" s="6" t="inlineStr"/>
-      <c r="AK11" s="7" t="inlineStr"/>
+      <c r="AK11" s="10" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
@@ -1080,16 +1113,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="K12" s="6" t="n">
+      <c r="K12" s="7" t="n">
         <v>75.64</v>
       </c>
-      <c r="L12" s="6" t="n">
+      <c r="L12" s="7" t="n">
         <v>76.81</v>
       </c>
-      <c r="M12" s="6" t="n">
+      <c r="M12" s="7" t="n">
         <v>79.76000000000001</v>
       </c>
-      <c r="N12" s="6" t="n">
+      <c r="N12" s="7" t="n">
         <v>81.90000000000001</v>
       </c>
       <c r="O12" s="6" t="inlineStr">
@@ -1097,19 +1130,19 @@
           <t>-</t>
         </is>
       </c>
-      <c r="P12" s="6" t="n">
+      <c r="P12" s="7" t="n">
         <v>82.14</v>
       </c>
-      <c r="Q12" s="6" t="n">
+      <c r="Q12" s="7" t="n">
         <v>81.20999999999999</v>
       </c>
-      <c r="R12" s="6" t="n">
+      <c r="R12" s="7" t="n">
         <v>81.06</v>
       </c>
-      <c r="S12" s="6" t="n">
+      <c r="S12" s="7" t="n">
         <v>78.68000000000001</v>
       </c>
-      <c r="T12" s="6" t="n">
+      <c r="T12" s="7" t="n">
         <v>77.7</v>
       </c>
       <c r="U12" s="6" t="inlineStr">
@@ -1127,10 +1160,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="X12" s="6" t="n">
+      <c r="X12" s="7" t="n">
         <v>81.20999999999999</v>
       </c>
-      <c r="Y12" s="6" t="n">
+      <c r="Y12" s="7" t="n">
         <v>80.66</v>
       </c>
       <c r="Z12" s="6" t="inlineStr">
@@ -1138,13 +1171,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="AA12" s="6" t="n">
+      <c r="AA12" s="7" t="n">
         <v>81.11</v>
       </c>
-      <c r="AB12" s="6" t="n">
+      <c r="AB12" s="7" t="n">
         <v>79.63</v>
       </c>
-      <c r="AC12" s="6" t="n">
+      <c r="AC12" s="7" t="n">
         <v>78.40000000000001</v>
       </c>
       <c r="AD12" s="6" t="inlineStr">
@@ -1152,13 +1185,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="AE12" s="6" t="n">
+      <c r="AE12" s="8" t="n">
         <v>46.82</v>
       </c>
-      <c r="AF12" s="6" t="n">
+      <c r="AF12" s="9" t="n">
         <v>40.81</v>
       </c>
-      <c r="AG12" s="6" t="n">
+      <c r="AG12" s="9" t="n">
         <v>41.96</v>
       </c>
       <c r="AH12" s="6" t="n">
@@ -1168,7 +1201,7 @@
         <v>101.16</v>
       </c>
       <c r="AJ12" s="6" t="inlineStr"/>
-      <c r="AK12" s="7" t="inlineStr"/>
+      <c r="AK12" s="10" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
@@ -1219,16 +1252,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="K13" s="6" t="n">
+      <c r="K13" s="7" t="n">
         <v>103.89</v>
       </c>
-      <c r="L13" s="6" t="n">
+      <c r="L13" s="7" t="n">
         <v>99.87</v>
       </c>
-      <c r="M13" s="6" t="n">
+      <c r="M13" s="7" t="n">
         <v>101.34</v>
       </c>
-      <c r="N13" s="6" t="n">
+      <c r="N13" s="7" t="n">
         <v>98.73999999999999</v>
       </c>
       <c r="O13" s="6" t="inlineStr">
@@ -1236,19 +1269,19 @@
           <t>-</t>
         </is>
       </c>
-      <c r="P13" s="6" t="n">
+      <c r="P13" s="7" t="n">
         <v>102.67</v>
       </c>
-      <c r="Q13" s="6" t="n">
+      <c r="Q13" s="7" t="n">
         <v>103.09</v>
       </c>
-      <c r="R13" s="6" t="n">
+      <c r="R13" s="7" t="n">
         <v>101.87</v>
       </c>
-      <c r="S13" s="6" t="n">
+      <c r="S13" s="7" t="n">
         <v>102.12</v>
       </c>
-      <c r="T13" s="6" t="n">
+      <c r="T13" s="7" t="n">
         <v>102.97</v>
       </c>
       <c r="U13" s="6" t="inlineStr">
@@ -1266,10 +1299,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="X13" s="6" t="n">
+      <c r="X13" s="7" t="n">
         <v>102.96</v>
       </c>
-      <c r="Y13" s="6" t="n">
+      <c r="Y13" s="7" t="n">
         <v>101.1</v>
       </c>
       <c r="Z13" s="6" t="inlineStr">
@@ -1277,13 +1310,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="AA13" s="6" t="n">
+      <c r="AA13" s="7" t="n">
         <v>102.83</v>
       </c>
-      <c r="AB13" s="6" t="n">
+      <c r="AB13" s="7" t="n">
         <v>102.38</v>
       </c>
-      <c r="AC13" s="6" t="n">
+      <c r="AC13" s="7" t="n">
         <v>101.42</v>
       </c>
       <c r="AD13" s="6" t="inlineStr">
@@ -1291,13 +1324,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="AE13" s="6" t="n">
+      <c r="AE13" s="7" t="n">
         <v>101.67</v>
       </c>
-      <c r="AF13" s="6" t="n">
+      <c r="AF13" s="7" t="n">
         <v>102.23</v>
       </c>
-      <c r="AG13" s="6" t="n">
+      <c r="AG13" s="7" t="n">
         <v>100.99</v>
       </c>
       <c r="AH13" s="6" t="n">
@@ -1307,7 +1340,7 @@
         <v>104.99</v>
       </c>
       <c r="AJ13" s="6" t="inlineStr"/>
-      <c r="AK13" s="7" t="inlineStr"/>
+      <c r="AK13" s="10" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
@@ -1358,16 +1391,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="K14" s="6" t="n">
+      <c r="K14" s="7" t="n">
         <v>89.91</v>
       </c>
-      <c r="L14" s="6" t="n">
+      <c r="L14" s="7" t="n">
         <v>89.05</v>
       </c>
-      <c r="M14" s="6" t="n">
+      <c r="M14" s="7" t="n">
         <v>89.79000000000001</v>
       </c>
-      <c r="N14" s="6" t="n">
+      <c r="N14" s="7" t="n">
         <v>90.05</v>
       </c>
       <c r="O14" s="6" t="inlineStr">
@@ -1375,19 +1408,19 @@
           <t>-</t>
         </is>
       </c>
-      <c r="P14" s="6" t="n">
+      <c r="P14" s="7" t="n">
         <v>91.48</v>
       </c>
-      <c r="Q14" s="6" t="n">
+      <c r="Q14" s="7" t="n">
         <v>91.84</v>
       </c>
-      <c r="R14" s="6" t="n">
+      <c r="R14" s="7" t="n">
         <v>90.95999999999999</v>
       </c>
-      <c r="S14" s="6" t="n">
+      <c r="S14" s="7" t="n">
         <v>90.70999999999999</v>
       </c>
-      <c r="T14" s="6" t="n">
+      <c r="T14" s="7" t="n">
         <v>90.53</v>
       </c>
       <c r="U14" s="6" t="inlineStr">
@@ -1405,10 +1438,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="X14" s="6" t="n">
+      <c r="X14" s="7" t="n">
         <v>92.17</v>
       </c>
-      <c r="Y14" s="6" t="n">
+      <c r="Y14" s="7" t="n">
         <v>89.58</v>
       </c>
       <c r="Z14" s="6" t="inlineStr">
@@ -1416,13 +1449,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="AA14" s="6" t="n">
+      <c r="AA14" s="7" t="n">
         <v>92.22</v>
       </c>
-      <c r="AB14" s="6" t="n">
+      <c r="AB14" s="7" t="n">
         <v>91.28</v>
       </c>
-      <c r="AC14" s="6" t="n">
+      <c r="AC14" s="7" t="n">
         <v>91.42</v>
       </c>
       <c r="AD14" s="6" t="inlineStr">
@@ -1430,13 +1463,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="AE14" s="6" t="n">
+      <c r="AE14" s="7" t="n">
         <v>92.08</v>
       </c>
-      <c r="AF14" s="6" t="n">
+      <c r="AF14" s="7" t="n">
         <v>91.31999999999999</v>
       </c>
-      <c r="AG14" s="6" t="n">
+      <c r="AG14" s="7" t="n">
         <v>90.73999999999999</v>
       </c>
       <c r="AH14" s="6" t="n">
@@ -1446,7 +1479,7 @@
         <v>119.83</v>
       </c>
       <c r="AJ14" s="6" t="inlineStr"/>
-      <c r="AK14" s="7" t="inlineStr"/>
+      <c r="AK14" s="10" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
@@ -1497,16 +1530,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="K15" s="6" t="n">
+      <c r="K15" s="7" t="n">
         <v>73.76000000000001</v>
       </c>
-      <c r="L15" s="6" t="n">
+      <c r="L15" s="7" t="n">
         <v>72.86</v>
       </c>
-      <c r="M15" s="6" t="n">
+      <c r="M15" s="7" t="n">
         <v>73.77</v>
       </c>
-      <c r="N15" s="6" t="n">
+      <c r="N15" s="7" t="n">
         <v>73.42</v>
       </c>
       <c r="O15" s="6" t="inlineStr">
@@ -1514,19 +1547,19 @@
           <t>-</t>
         </is>
       </c>
-      <c r="P15" s="6" t="n">
+      <c r="P15" s="7" t="n">
         <v>74.97</v>
       </c>
-      <c r="Q15" s="6" t="n">
+      <c r="Q15" s="7" t="n">
         <v>74.93000000000001</v>
       </c>
-      <c r="R15" s="6" t="n">
+      <c r="R15" s="7" t="n">
         <v>74.58</v>
       </c>
-      <c r="S15" s="6" t="n">
+      <c r="S15" s="7" t="n">
         <v>74.12</v>
       </c>
-      <c r="T15" s="6" t="n">
+      <c r="T15" s="7" t="n">
         <v>74.38</v>
       </c>
       <c r="U15" s="6" t="inlineStr">
@@ -1544,10 +1577,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="X15" s="6" t="n">
+      <c r="X15" s="7" t="n">
         <v>74.73999999999999</v>
       </c>
-      <c r="Y15" s="6" t="n">
+      <c r="Y15" s="7" t="n">
         <v>74.34</v>
       </c>
       <c r="Z15" s="6" t="inlineStr">
@@ -1555,13 +1588,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="AA15" s="6" t="n">
+      <c r="AA15" s="7" t="n">
         <v>74.92</v>
       </c>
-      <c r="AB15" s="6" t="n">
+      <c r="AB15" s="7" t="n">
         <v>75.15000000000001</v>
       </c>
-      <c r="AC15" s="6" t="n">
+      <c r="AC15" s="7" t="n">
         <v>75.31</v>
       </c>
       <c r="AD15" s="6" t="inlineStr">
@@ -1569,13 +1602,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="AE15" s="6" t="n">
+      <c r="AE15" s="7" t="n">
         <v>74.61</v>
       </c>
-      <c r="AF15" s="6" t="n">
+      <c r="AF15" s="7" t="n">
         <v>75.12</v>
       </c>
-      <c r="AG15" s="6" t="n">
+      <c r="AG15" s="7" t="n">
         <v>74.22</v>
       </c>
       <c r="AH15" s="6" t="n">
@@ -1585,7 +1618,7 @@
         <v>156.6</v>
       </c>
       <c r="AJ15" s="6" t="inlineStr"/>
-      <c r="AK15" s="7" t="inlineStr"/>
+      <c r="AK15" s="10" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
@@ -1636,16 +1669,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="K16" s="6" t="n">
+      <c r="K16" s="7" t="n">
         <v>90.2</v>
       </c>
-      <c r="L16" s="6" t="n">
+      <c r="L16" s="7" t="n">
         <v>87.67</v>
       </c>
-      <c r="M16" s="6" t="n">
+      <c r="M16" s="7" t="n">
         <v>89.05</v>
       </c>
-      <c r="N16" s="6" t="n">
+      <c r="N16" s="7" t="n">
         <v>88.61</v>
       </c>
       <c r="O16" s="6" t="inlineStr">
@@ -1653,19 +1686,19 @@
           <t>-</t>
         </is>
       </c>
-      <c r="P16" s="6" t="n">
+      <c r="P16" s="7" t="n">
         <v>90.01000000000001</v>
       </c>
-      <c r="Q16" s="6" t="n">
+      <c r="Q16" s="7" t="n">
         <v>89.26000000000001</v>
       </c>
-      <c r="R16" s="6" t="n">
+      <c r="R16" s="7" t="n">
         <v>89.18000000000001</v>
       </c>
-      <c r="S16" s="6" t="n">
+      <c r="S16" s="7" t="n">
         <v>90.37</v>
       </c>
-      <c r="T16" s="6" t="n">
+      <c r="T16" s="7" t="n">
         <v>90.94</v>
       </c>
       <c r="U16" s="6" t="inlineStr">
@@ -1683,10 +1716,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="X16" s="6" t="n">
+      <c r="X16" s="7" t="n">
         <v>90.41</v>
       </c>
-      <c r="Y16" s="6" t="n">
+      <c r="Y16" s="7" t="n">
         <v>88.64</v>
       </c>
       <c r="Z16" s="6" t="inlineStr">
@@ -1694,13 +1727,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="AA16" s="6" t="n">
+      <c r="AA16" s="7" t="n">
         <v>90.01000000000001</v>
       </c>
-      <c r="AB16" s="6" t="n">
+      <c r="AB16" s="7" t="n">
         <v>89.69</v>
       </c>
-      <c r="AC16" s="6" t="n">
+      <c r="AC16" s="7" t="n">
         <v>89.87</v>
       </c>
       <c r="AD16" s="6" t="inlineStr">
@@ -1708,13 +1741,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="AE16" s="6" t="n">
+      <c r="AE16" s="7" t="n">
         <v>89.26000000000001</v>
       </c>
-      <c r="AF16" s="6" t="n">
+      <c r="AF16" s="7" t="n">
         <v>88.64</v>
       </c>
-      <c r="AG16" s="6" t="n">
+      <c r="AG16" s="7" t="n">
         <v>88.94</v>
       </c>
       <c r="AH16" s="6" t="n">
@@ -1724,7 +1757,7 @@
         <v>138.26</v>
       </c>
       <c r="AJ16" s="6" t="inlineStr"/>
-      <c r="AK16" s="7" t="inlineStr"/>
+      <c r="AK16" s="10" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
@@ -1775,16 +1808,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="K17" s="6" t="n">
+      <c r="K17" s="7" t="n">
         <v>103.71</v>
       </c>
-      <c r="L17" s="6" t="n">
+      <c r="L17" s="7" t="n">
         <v>102.89</v>
       </c>
-      <c r="M17" s="6" t="n">
+      <c r="M17" s="7" t="n">
         <v>104.26</v>
       </c>
-      <c r="N17" s="6" t="n">
+      <c r="N17" s="7" t="n">
         <v>103.16</v>
       </c>
       <c r="O17" s="6" t="inlineStr">
@@ -1792,19 +1825,19 @@
           <t>-</t>
         </is>
       </c>
-      <c r="P17" s="6" t="n">
+      <c r="P17" s="7" t="n">
         <v>105.67</v>
       </c>
-      <c r="Q17" s="6" t="n">
+      <c r="Q17" s="7" t="n">
         <v>105.56</v>
       </c>
-      <c r="R17" s="6" t="n">
+      <c r="R17" s="7" t="n">
         <v>105</v>
       </c>
-      <c r="S17" s="6" t="n">
+      <c r="S17" s="7" t="n">
         <v>104.83</v>
       </c>
-      <c r="T17" s="6" t="n">
+      <c r="T17" s="7" t="n">
         <v>105.03</v>
       </c>
       <c r="U17" s="6" t="inlineStr">
@@ -1822,10 +1855,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="X17" s="6" t="n">
+      <c r="X17" s="7" t="n">
         <v>105.37</v>
       </c>
-      <c r="Y17" s="6" t="n">
+      <c r="Y17" s="7" t="n">
         <v>104.17</v>
       </c>
       <c r="Z17" s="6" t="inlineStr">
@@ -1833,13 +1866,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="AA17" s="6" t="n">
+      <c r="AA17" s="7" t="n">
         <v>105.66</v>
       </c>
-      <c r="AB17" s="6" t="n">
+      <c r="AB17" s="7" t="n">
         <v>105.14</v>
       </c>
-      <c r="AC17" s="6" t="n">
+      <c r="AC17" s="7" t="n">
         <v>104.84</v>
       </c>
       <c r="AD17" s="6" t="inlineStr">
@@ -1847,13 +1880,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="AE17" s="6" t="n">
+      <c r="AE17" s="7" t="n">
         <v>105.13</v>
       </c>
-      <c r="AF17" s="6" t="n">
+      <c r="AF17" s="7" t="n">
         <v>105.22</v>
       </c>
-      <c r="AG17" s="6" t="n">
+      <c r="AG17" s="7" t="n">
         <v>104.76</v>
       </c>
       <c r="AH17" s="6" t="n">
@@ -1863,7 +1896,7 @@
         <v>246.97</v>
       </c>
       <c r="AJ17" s="6" t="inlineStr"/>
-      <c r="AK17" s="7" t="inlineStr"/>
+      <c r="AK17" s="10" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
@@ -1914,16 +1947,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="K18" s="6" t="n">
+      <c r="K18" s="7" t="n">
         <v>66.56</v>
       </c>
-      <c r="L18" s="6" t="n">
+      <c r="L18" s="7" t="n">
         <v>70.83</v>
       </c>
-      <c r="M18" s="6" t="n">
+      <c r="M18" s="7" t="n">
         <v>71.56999999999999</v>
       </c>
-      <c r="N18" s="6" t="n">
+      <c r="N18" s="7" t="n">
         <v>70.55</v>
       </c>
       <c r="O18" s="6" t="inlineStr">
@@ -1931,19 +1964,19 @@
           <t>-</t>
         </is>
       </c>
-      <c r="P18" s="6" t="n">
+      <c r="P18" s="7" t="n">
         <v>73.66</v>
       </c>
-      <c r="Q18" s="6" t="n">
+      <c r="Q18" s="7" t="n">
         <v>73.25</v>
       </c>
-      <c r="R18" s="6" t="n">
+      <c r="R18" s="7" t="n">
         <v>73.23</v>
       </c>
-      <c r="S18" s="6" t="n">
+      <c r="S18" s="7" t="n">
         <v>68.51000000000001</v>
       </c>
-      <c r="T18" s="6" t="n">
+      <c r="T18" s="7" t="n">
         <v>70.68000000000001</v>
       </c>
       <c r="U18" s="6" t="inlineStr">
@@ -1961,10 +1994,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="X18" s="6" t="n">
+      <c r="X18" s="7" t="n">
         <v>72.51000000000001</v>
       </c>
-      <c r="Y18" s="6" t="n">
+      <c r="Y18" s="7" t="n">
         <v>66.12</v>
       </c>
       <c r="Z18" s="6" t="inlineStr">
@@ -1972,13 +2005,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="AA18" s="6" t="n">
+      <c r="AA18" s="7" t="n">
         <v>71.5</v>
       </c>
-      <c r="AB18" s="6" t="n">
+      <c r="AB18" s="7" t="n">
         <v>70.66</v>
       </c>
-      <c r="AC18" s="6" t="n">
+      <c r="AC18" s="7" t="n">
         <v>70.8</v>
       </c>
       <c r="AD18" s="6" t="inlineStr">
@@ -1986,13 +2019,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="AE18" s="6" t="n">
+      <c r="AE18" s="7" t="n">
         <v>71.98999999999999</v>
       </c>
-      <c r="AF18" s="6" t="n">
+      <c r="AF18" s="7" t="n">
         <v>71.06999999999999</v>
       </c>
-      <c r="AG18" s="6" t="n">
+      <c r="AG18" s="7" t="n">
         <v>71.56999999999999</v>
       </c>
       <c r="AH18" s="6" t="n">
@@ -2002,7 +2035,7 @@
         <v>52.8</v>
       </c>
       <c r="AJ18" s="6" t="inlineStr"/>
-      <c r="AK18" s="7" t="inlineStr"/>
+      <c r="AK18" s="10" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
@@ -2053,16 +2086,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="K19" s="6" t="n">
+      <c r="K19" s="8" t="n">
         <v>46.03</v>
       </c>
-      <c r="L19" s="6" t="n">
+      <c r="L19" s="8" t="n">
         <v>43.57</v>
       </c>
-      <c r="M19" s="6" t="n">
+      <c r="M19" s="8" t="n">
         <v>45.68</v>
       </c>
-      <c r="N19" s="6" t="n">
+      <c r="N19" s="8" t="n">
         <v>44.8</v>
       </c>
       <c r="O19" s="6" t="inlineStr">
@@ -2070,19 +2103,19 @@
           <t>-</t>
         </is>
       </c>
-      <c r="P19" s="6" t="n">
+      <c r="P19" s="8" t="n">
         <v>47.17</v>
       </c>
-      <c r="Q19" s="6" t="n">
+      <c r="Q19" s="8" t="n">
         <v>46.81</v>
       </c>
-      <c r="R19" s="6" t="n">
+      <c r="R19" s="8" t="n">
         <v>46.39</v>
       </c>
-      <c r="S19" s="6" t="n">
+      <c r="S19" s="8" t="n">
         <v>47.11</v>
       </c>
-      <c r="T19" s="6" t="n">
+      <c r="T19" s="8" t="n">
         <v>47</v>
       </c>
       <c r="U19" s="6" t="inlineStr">
@@ -2100,10 +2133,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="X19" s="6" t="n">
+      <c r="X19" s="8" t="n">
         <v>47.87</v>
       </c>
-      <c r="Y19" s="6" t="n">
+      <c r="Y19" s="8" t="n">
         <v>45.81</v>
       </c>
       <c r="Z19" s="6" t="inlineStr">
@@ -2111,13 +2144,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="AA19" s="6" t="n">
+      <c r="AA19" s="8" t="n">
         <v>47.24</v>
       </c>
-      <c r="AB19" s="6" t="n">
+      <c r="AB19" s="8" t="n">
         <v>46.43</v>
       </c>
-      <c r="AC19" s="6" t="n">
+      <c r="AC19" s="8" t="n">
         <v>46.17</v>
       </c>
       <c r="AD19" s="6" t="inlineStr">
@@ -2125,13 +2158,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="AE19" s="6" t="n">
+      <c r="AE19" s="8" t="n">
         <v>46.36</v>
       </c>
-      <c r="AF19" s="6" t="n">
+      <c r="AF19" s="8" t="n">
         <v>46.06</v>
       </c>
-      <c r="AG19" s="6" t="n">
+      <c r="AG19" s="8" t="n">
         <v>45.74</v>
       </c>
       <c r="AH19" s="6" t="n">
@@ -2141,7 +2174,7 @@
         <v>477.49</v>
       </c>
       <c r="AJ19" s="6" t="inlineStr"/>
-      <c r="AK19" s="7" t="inlineStr"/>
+      <c r="AK19" s="10" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="5" t="inlineStr">
@@ -2192,16 +2225,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="K20" s="6" t="n">
+      <c r="K20" s="7" t="n">
         <v>82.23999999999999</v>
       </c>
-      <c r="L20" s="6" t="n">
+      <c r="L20" s="7" t="n">
         <v>83.69</v>
       </c>
-      <c r="M20" s="6" t="n">
+      <c r="M20" s="7" t="n">
         <v>81.95999999999999</v>
       </c>
-      <c r="N20" s="6" t="n">
+      <c r="N20" s="7" t="n">
         <v>82.68000000000001</v>
       </c>
       <c r="O20" s="6" t="inlineStr">
@@ -2209,19 +2242,19 @@
           <t>-</t>
         </is>
       </c>
-      <c r="P20" s="6" t="n">
+      <c r="P20" s="7" t="n">
         <v>81.26000000000001</v>
       </c>
-      <c r="Q20" s="6" t="n">
+      <c r="Q20" s="7" t="n">
         <v>80.44</v>
       </c>
-      <c r="R20" s="6" t="n">
+      <c r="R20" s="7" t="n">
         <v>79.55</v>
       </c>
-      <c r="S20" s="6" t="n">
+      <c r="S20" s="7" t="n">
         <v>82.98</v>
       </c>
-      <c r="T20" s="6" t="n">
+      <c r="T20" s="7" t="n">
         <v>82.94</v>
       </c>
       <c r="U20" s="6" t="inlineStr">
@@ -2239,10 +2272,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="X20" s="6" t="n">
+      <c r="X20" s="7" t="n">
         <v>82.48999999999999</v>
       </c>
-      <c r="Y20" s="6" t="n">
+      <c r="Y20" s="7" t="n">
         <v>81.39</v>
       </c>
       <c r="Z20" s="6" t="inlineStr">
@@ -2250,13 +2283,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="AA20" s="6" t="n">
+      <c r="AA20" s="7" t="n">
         <v>80.79000000000001</v>
       </c>
-      <c r="AB20" s="6" t="n">
+      <c r="AB20" s="7" t="n">
         <v>81.12</v>
       </c>
-      <c r="AC20" s="6" t="n">
+      <c r="AC20" s="7" t="n">
         <v>78.63</v>
       </c>
       <c r="AD20" s="6" t="inlineStr">
@@ -2264,13 +2297,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="AE20" s="6" t="n">
+      <c r="AE20" s="7" t="n">
         <v>80.22</v>
       </c>
-      <c r="AF20" s="6" t="n">
+      <c r="AF20" s="7" t="n">
         <v>80.81</v>
       </c>
-      <c r="AG20" s="6" t="n">
+      <c r="AG20" s="7" t="n">
         <v>80.31999999999999</v>
       </c>
       <c r="AH20" s="6" t="n">
@@ -2280,7 +2313,7 @@
         <v>149.08</v>
       </c>
       <c r="AJ20" s="6" t="inlineStr"/>
-      <c r="AK20" s="7" t="inlineStr"/>
+      <c r="AK20" s="10" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
@@ -2331,16 +2364,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="K21" s="6" t="n">
+      <c r="K21" s="7" t="n">
         <v>55.96</v>
       </c>
-      <c r="L21" s="6" t="n">
+      <c r="L21" s="7" t="n">
         <v>57.99</v>
       </c>
-      <c r="M21" s="6" t="n">
+      <c r="M21" s="7" t="n">
         <v>56.92</v>
       </c>
-      <c r="N21" s="6" t="n">
+      <c r="N21" s="7" t="n">
         <v>59.21</v>
       </c>
       <c r="O21" s="6" t="inlineStr">
@@ -2348,19 +2381,19 @@
           <t>-</t>
         </is>
       </c>
-      <c r="P21" s="6" t="n">
+      <c r="P21" s="7" t="n">
         <v>55.46</v>
       </c>
-      <c r="Q21" s="6" t="n">
+      <c r="Q21" s="7" t="n">
         <v>55.44</v>
       </c>
-      <c r="R21" s="6" t="n">
+      <c r="R21" s="7" t="n">
         <v>56.11</v>
       </c>
-      <c r="S21" s="6" t="n">
+      <c r="S21" s="7" t="n">
         <v>54.27</v>
       </c>
-      <c r="T21" s="6" t="n">
+      <c r="T21" s="7" t="n">
         <v>55.4</v>
       </c>
       <c r="U21" s="6" t="inlineStr">
@@ -2378,10 +2411,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="X21" s="6" t="n">
+      <c r="X21" s="7" t="n">
         <v>55.71</v>
       </c>
-      <c r="Y21" s="6" t="n">
+      <c r="Y21" s="7" t="n">
         <v>57.52</v>
       </c>
       <c r="Z21" s="6" t="inlineStr">
@@ -2389,13 +2422,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="AA21" s="6" t="n">
+      <c r="AA21" s="7" t="n">
         <v>55.4</v>
       </c>
-      <c r="AB21" s="6" t="n">
+      <c r="AB21" s="7" t="n">
         <v>56.72</v>
       </c>
-      <c r="AC21" s="6" t="n">
+      <c r="AC21" s="7" t="n">
         <v>56.56</v>
       </c>
       <c r="AD21" s="6" t="inlineStr">
@@ -2403,13 +2436,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="AE21" s="6" t="n">
+      <c r="AE21" s="7" t="n">
         <v>55.47</v>
       </c>
-      <c r="AF21" s="6" t="n">
+      <c r="AF21" s="7" t="n">
         <v>56.47</v>
       </c>
-      <c r="AG21" s="6" t="n">
+      <c r="AG21" s="7" t="n">
         <v>57.08</v>
       </c>
       <c r="AH21" s="6" t="n">
@@ -2419,146 +2452,146 @@
         <v>157.64</v>
       </c>
       <c r="AJ21" s="6" t="inlineStr"/>
-      <c r="AK21" s="7" t="inlineStr"/>
+      <c r="AK21" s="10" t="inlineStr"/>
     </row>
     <row r="22">
-      <c r="A22" s="8" t="inlineStr">
+      <c r="A22" s="11" t="inlineStr">
         <is>
           <t>ZETA</t>
         </is>
       </c>
-      <c r="B22" s="9" t="n">
+      <c r="B22" s="12" t="n">
         <v>106.9</v>
       </c>
-      <c r="C22" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D22" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E22" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F22" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G22" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H22" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I22" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J22" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K22" s="9" t="n">
+      <c r="C22" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D22" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E22" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F22" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G22" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H22" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I22" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J22" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K22" s="13" t="n">
         <v>94.18000000000001</v>
       </c>
-      <c r="L22" s="9" t="n">
+      <c r="L22" s="13" t="n">
         <v>93.93000000000001</v>
       </c>
-      <c r="M22" s="9" t="n">
+      <c r="M22" s="13" t="n">
         <v>95.51000000000001</v>
       </c>
-      <c r="N22" s="9" t="n">
+      <c r="N22" s="13" t="n">
         <v>94.7</v>
       </c>
-      <c r="O22" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P22" s="9" t="n">
+      <c r="O22" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P22" s="13" t="n">
         <v>96.44</v>
       </c>
-      <c r="Q22" s="9" t="n">
+      <c r="Q22" s="13" t="n">
         <v>96.55</v>
       </c>
-      <c r="R22" s="9" t="n">
+      <c r="R22" s="13" t="n">
         <v>96.68000000000001</v>
       </c>
-      <c r="S22" s="9" t="n">
+      <c r="S22" s="13" t="n">
         <v>95.59</v>
       </c>
-      <c r="T22" s="9" t="n">
+      <c r="T22" s="13" t="n">
         <v>95.16</v>
       </c>
-      <c r="U22" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="V22" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="W22" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="X22" s="9" t="n">
+      <c r="U22" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="V22" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="W22" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="X22" s="13" t="n">
         <v>96.52</v>
       </c>
-      <c r="Y22" s="9" t="n">
+      <c r="Y22" s="13" t="n">
         <v>96.81</v>
       </c>
-      <c r="Z22" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AA22" s="9" t="n">
+      <c r="Z22" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AA22" s="13" t="n">
         <v>96.84</v>
       </c>
-      <c r="AB22" s="9" t="n">
+      <c r="AB22" s="13" t="n">
         <v>97.22</v>
       </c>
-      <c r="AC22" s="9" t="n">
+      <c r="AC22" s="13" t="n">
         <v>96.81</v>
       </c>
-      <c r="AD22" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AE22" s="9" t="n">
+      <c r="AD22" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AE22" s="13" t="n">
         <v>96.48</v>
       </c>
-      <c r="AF22" s="9" t="n">
+      <c r="AF22" s="13" t="n">
         <v>97.16</v>
       </c>
-      <c r="AG22" s="9" t="n">
+      <c r="AG22" s="13" t="n">
         <v>96.37</v>
       </c>
-      <c r="AH22" s="9" t="n">
+      <c r="AH22" s="12" t="n">
         <v>96.06</v>
       </c>
-      <c r="AI22" s="9" t="n">
+      <c r="AI22" s="12" t="n">
         <v>127.1</v>
       </c>
-      <c r="AJ22" s="9" t="inlineStr"/>
-      <c r="AK22" s="10" t="inlineStr"/>
+      <c r="AJ22" s="12" t="inlineStr"/>
+      <c r="AK22" s="14" t="inlineStr"/>
     </row>
     <row r="23"/>
     <row r="24"/>
@@ -2607,7 +2640,7 @@
     <row r="31">
       <c r="A31" s="1" t="inlineStr">
         <is>
-          <t>FECHA PRESENTACIÓN: 27/08/2025</t>
+          <t>FECHA PRESENTACIÓN: 28/08/2025</t>
         </is>
       </c>
     </row>
@@ -2733,7 +2766,7 @@
           <t>OBSERVACIONES</t>
         </is>
       </c>
-      <c r="AK32" s="11" t="n"/>
+      <c r="AK32" s="15" t="n"/>
     </row>
     <row r="33">
       <c r="A33" s="5" t="inlineStr">
@@ -2784,16 +2817,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="K33" s="6" t="n">
+      <c r="K33" s="7" t="n">
         <v>57.55</v>
       </c>
-      <c r="L33" s="6" t="n">
+      <c r="L33" s="7" t="n">
         <v>57.75</v>
       </c>
-      <c r="M33" s="6" t="n">
+      <c r="M33" s="7" t="n">
         <v>57.28</v>
       </c>
-      <c r="N33" s="6" t="n">
+      <c r="N33" s="7" t="n">
         <v>57.49</v>
       </c>
       <c r="O33" s="6" t="inlineStr">
@@ -2801,19 +2834,19 @@
           <t>-</t>
         </is>
       </c>
-      <c r="P33" s="6" t="n">
+      <c r="P33" s="7" t="n">
         <v>56.76</v>
       </c>
-      <c r="Q33" s="6" t="n">
+      <c r="Q33" s="7" t="n">
         <v>55.79</v>
       </c>
-      <c r="R33" s="6" t="n">
+      <c r="R33" s="7" t="n">
         <v>54.35</v>
       </c>
-      <c r="S33" s="6" t="n">
+      <c r="S33" s="7" t="n">
         <v>56.31</v>
       </c>
-      <c r="T33" s="6" t="n">
+      <c r="T33" s="7" t="n">
         <v>55.88</v>
       </c>
       <c r="U33" s="6" t="inlineStr">
@@ -2831,10 +2864,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="X33" s="6" t="n">
+      <c r="X33" s="7" t="n">
         <v>55.13</v>
       </c>
-      <c r="Y33" s="6" t="n">
+      <c r="Y33" s="7" t="n">
         <v>54.41</v>
       </c>
       <c r="Z33" s="6" t="inlineStr">
@@ -2842,13 +2875,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="AA33" s="6" t="n">
+      <c r="AA33" s="7" t="n">
         <v>55</v>
       </c>
-      <c r="AB33" s="6" t="n">
+      <c r="AB33" s="7" t="n">
         <v>55.06</v>
       </c>
-      <c r="AC33" s="6" t="n">
+      <c r="AC33" s="7" t="n">
         <v>54.2</v>
       </c>
       <c r="AD33" s="6" t="inlineStr">
@@ -2856,13 +2889,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="AE33" s="6" t="n">
+      <c r="AE33" s="7" t="n">
         <v>54.14</v>
       </c>
-      <c r="AF33" s="6" t="n">
+      <c r="AF33" s="7" t="n">
         <v>54.39</v>
       </c>
-      <c r="AG33" s="6" t="n">
+      <c r="AG33" s="7" t="n">
         <v>54.92</v>
       </c>
       <c r="AH33" s="6" t="n">
@@ -2870,7 +2903,7 @@
       </c>
       <c r="AI33" s="6" t="inlineStr"/>
       <c r="AJ33" s="6" t="inlineStr"/>
-      <c r="AK33" s="12" t="n"/>
+      <c r="AK33" s="16" t="n"/>
     </row>
     <row r="34">
       <c r="A34" s="5" t="inlineStr">
@@ -2921,16 +2954,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="K34" s="6" t="n">
+      <c r="K34" s="9" t="n">
         <v>38.7</v>
       </c>
-      <c r="L34" s="6" t="n">
+      <c r="L34" s="9" t="n">
         <v>40.12</v>
       </c>
-      <c r="M34" s="6" t="n">
+      <c r="M34" s="9" t="n">
         <v>39.56</v>
       </c>
-      <c r="N34" s="6" t="n">
+      <c r="N34" s="9" t="n">
         <v>38.39</v>
       </c>
       <c r="O34" s="6" t="inlineStr">
@@ -2938,19 +2971,19 @@
           <t>-</t>
         </is>
       </c>
-      <c r="P34" s="6" t="n">
+      <c r="P34" s="9" t="n">
         <v>39.4</v>
       </c>
-      <c r="Q34" s="6" t="n">
+      <c r="Q34" s="9" t="n">
         <v>38.11</v>
       </c>
-      <c r="R34" s="6" t="n">
+      <c r="R34" s="9" t="n">
         <v>39.07</v>
       </c>
-      <c r="S34" s="6" t="n">
+      <c r="S34" s="9" t="n">
         <v>38.31</v>
       </c>
-      <c r="T34" s="6" t="n">
+      <c r="T34" s="9" t="n">
         <v>38.94</v>
       </c>
       <c r="U34" s="6" t="inlineStr">
@@ -2968,10 +3001,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="X34" s="6" t="n">
+      <c r="X34" s="9" t="n">
         <v>39.57</v>
       </c>
-      <c r="Y34" s="6" t="n">
+      <c r="Y34" s="9" t="n">
         <v>38.75</v>
       </c>
       <c r="Z34" s="6" t="inlineStr">
@@ -2979,13 +3012,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="AA34" s="6" t="n">
+      <c r="AA34" s="9" t="n">
         <v>39.83</v>
       </c>
-      <c r="AB34" s="6" t="n">
+      <c r="AB34" s="9" t="n">
         <v>39.13</v>
       </c>
-      <c r="AC34" s="6" t="n">
+      <c r="AC34" s="9" t="n">
         <v>38.66</v>
       </c>
       <c r="AD34" s="6" t="inlineStr">
@@ -2993,13 +3026,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="AE34" s="6" t="n">
+      <c r="AE34" s="9" t="n">
         <v>40.58</v>
       </c>
-      <c r="AF34" s="6" t="n">
+      <c r="AF34" s="9" t="n">
         <v>40.04</v>
       </c>
-      <c r="AG34" s="6" t="n">
+      <c r="AG34" s="9" t="n">
         <v>39.34</v>
       </c>
       <c r="AH34" s="6" t="n">
@@ -3007,7 +3040,7 @@
       </c>
       <c r="AI34" s="6" t="inlineStr"/>
       <c r="AJ34" s="6" t="inlineStr"/>
-      <c r="AK34" s="12" t="n"/>
+      <c r="AK34" s="16" t="n"/>
     </row>
     <row r="35">
       <c r="A35" s="5" t="inlineStr">
@@ -3058,16 +3091,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="K35" s="6" t="n">
+      <c r="K35" s="9" t="n">
         <v>42.34</v>
       </c>
-      <c r="L35" s="6" t="n">
+      <c r="L35" s="9" t="n">
         <v>40.07</v>
       </c>
-      <c r="M35" s="6" t="n">
+      <c r="M35" s="9" t="n">
         <v>41.68</v>
       </c>
-      <c r="N35" s="6" t="n">
+      <c r="N35" s="9" t="n">
         <v>39.71</v>
       </c>
       <c r="O35" s="6" t="inlineStr">
@@ -3075,19 +3108,19 @@
           <t>-</t>
         </is>
       </c>
-      <c r="P35" s="6" t="n">
+      <c r="P35" s="9" t="n">
         <v>42.02</v>
       </c>
-      <c r="Q35" s="6" t="n">
+      <c r="Q35" s="9" t="n">
         <v>40.85</v>
       </c>
-      <c r="R35" s="6" t="n">
+      <c r="R35" s="9" t="n">
         <v>42.52</v>
       </c>
-      <c r="S35" s="6" t="n">
+      <c r="S35" s="9" t="n">
         <v>40.18</v>
       </c>
-      <c r="T35" s="6" t="n">
+      <c r="T35" s="9" t="n">
         <v>42.59</v>
       </c>
       <c r="U35" s="6" t="inlineStr">
@@ -3105,10 +3138,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="X35" s="6" t="n">
+      <c r="X35" s="9" t="n">
         <v>40.06</v>
       </c>
-      <c r="Y35" s="6" t="n">
+      <c r="Y35" s="9" t="n">
         <v>37.89</v>
       </c>
       <c r="Z35" s="6" t="inlineStr">
@@ -3116,13 +3149,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="AA35" s="6" t="n">
+      <c r="AA35" s="9" t="n">
         <v>41.15</v>
       </c>
-      <c r="AB35" s="6" t="n">
+      <c r="AB35" s="9" t="n">
         <v>38.92</v>
       </c>
-      <c r="AC35" s="6" t="n">
+      <c r="AC35" s="9" t="n">
         <v>39.38</v>
       </c>
       <c r="AD35" s="6" t="inlineStr">
@@ -3130,13 +3163,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="AE35" s="6" t="n">
+      <c r="AE35" s="9" t="n">
         <v>40.89</v>
       </c>
-      <c r="AF35" s="6" t="n">
+      <c r="AF35" s="9" t="n">
         <v>41.14</v>
       </c>
-      <c r="AG35" s="6" t="n">
+      <c r="AG35" s="9" t="n">
         <v>41.74</v>
       </c>
       <c r="AH35" s="6" t="n">
@@ -3144,7 +3177,7 @@
       </c>
       <c r="AI35" s="6" t="inlineStr"/>
       <c r="AJ35" s="6" t="inlineStr"/>
-      <c r="AK35" s="12" t="n"/>
+      <c r="AK35" s="16" t="n"/>
     </row>
     <row r="36">
       <c r="A36" s="5" t="inlineStr">
@@ -3195,16 +3228,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="K36" s="6" t="n">
+      <c r="K36" s="9" t="n">
         <v>32.85</v>
       </c>
-      <c r="L36" s="6" t="n">
+      <c r="L36" s="9" t="n">
         <v>34.68</v>
       </c>
-      <c r="M36" s="6" t="n">
+      <c r="M36" s="9" t="n">
         <v>34.93</v>
       </c>
-      <c r="N36" s="6" t="n">
+      <c r="N36" s="9" t="n">
         <v>32.62</v>
       </c>
       <c r="O36" s="6" t="inlineStr">
@@ -3212,19 +3245,19 @@
           <t>-</t>
         </is>
       </c>
-      <c r="P36" s="6" t="n">
+      <c r="P36" s="9" t="n">
         <v>35.57</v>
       </c>
-      <c r="Q36" s="6" t="n">
+      <c r="Q36" s="9" t="n">
         <v>33.22</v>
       </c>
-      <c r="R36" s="6" t="n">
+      <c r="R36" s="9" t="n">
         <v>33.28</v>
       </c>
-      <c r="S36" s="6" t="n">
+      <c r="S36" s="9" t="n">
         <v>33.37</v>
       </c>
-      <c r="T36" s="6" t="n">
+      <c r="T36" s="9" t="n">
         <v>33.94</v>
       </c>
       <c r="U36" s="6" t="inlineStr">
@@ -3242,10 +3275,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="X36" s="6" t="n">
+      <c r="X36" s="9" t="n">
         <v>33.7</v>
       </c>
-      <c r="Y36" s="6" t="n">
+      <c r="Y36" s="9" t="n">
         <v>32.97</v>
       </c>
       <c r="Z36" s="6" t="inlineStr">
@@ -3253,13 +3286,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="AA36" s="6" t="n">
+      <c r="AA36" s="9" t="n">
         <v>33.07</v>
       </c>
-      <c r="AB36" s="6" t="n">
+      <c r="AB36" s="9" t="n">
         <v>33.43</v>
       </c>
-      <c r="AC36" s="6" t="n">
+      <c r="AC36" s="9" t="n">
         <v>33.04</v>
       </c>
       <c r="AD36" s="6" t="inlineStr">
@@ -3267,13 +3300,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="AE36" s="6" t="n">
+      <c r="AE36" s="9" t="n">
         <v>33.12</v>
       </c>
-      <c r="AF36" s="6" t="n">
+      <c r="AF36" s="9" t="n">
         <v>35.94</v>
       </c>
-      <c r="AG36" s="6" t="n">
+      <c r="AG36" s="9" t="n">
         <v>33.06</v>
       </c>
       <c r="AH36" s="6" t="n">
@@ -3281,7 +3314,7 @@
       </c>
       <c r="AI36" s="6" t="inlineStr"/>
       <c r="AJ36" s="6" t="inlineStr"/>
-      <c r="AK36" s="12" t="n"/>
+      <c r="AK36" s="16" t="n"/>
     </row>
     <row r="37">
       <c r="A37" s="5" t="inlineStr">
@@ -3332,16 +3365,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="K37" s="6" t="n">
+      <c r="K37" s="9" t="n">
         <v>31.68</v>
       </c>
-      <c r="L37" s="6" t="n">
+      <c r="L37" s="9" t="n">
         <v>34.34</v>
       </c>
-      <c r="M37" s="6" t="n">
+      <c r="M37" s="9" t="n">
         <v>34.12</v>
       </c>
-      <c r="N37" s="6" t="n">
+      <c r="N37" s="9" t="n">
         <v>31.96</v>
       </c>
       <c r="O37" s="6" t="inlineStr">
@@ -3349,19 +3382,19 @@
           <t>-</t>
         </is>
       </c>
-      <c r="P37" s="6" t="n">
+      <c r="P37" s="9" t="n">
         <v>32.38</v>
       </c>
-      <c r="Q37" s="6" t="n">
+      <c r="Q37" s="9" t="n">
         <v>33.12</v>
       </c>
-      <c r="R37" s="6" t="n">
+      <c r="R37" s="9" t="n">
         <v>33.15</v>
       </c>
-      <c r="S37" s="6" t="n">
+      <c r="S37" s="9" t="n">
         <v>31.32</v>
       </c>
-      <c r="T37" s="6" t="n">
+      <c r="T37" s="9" t="n">
         <v>31.71</v>
       </c>
       <c r="U37" s="6" t="inlineStr">
@@ -3379,10 +3412,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="X37" s="6" t="n">
+      <c r="X37" s="9" t="n">
         <v>32.34</v>
       </c>
-      <c r="Y37" s="6" t="n">
+      <c r="Y37" s="9" t="n">
         <v>32.37</v>
       </c>
       <c r="Z37" s="6" t="inlineStr">
@@ -3390,13 +3423,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="AA37" s="6" t="n">
+      <c r="AA37" s="9" t="n">
         <v>32.65</v>
       </c>
-      <c r="AB37" s="6" t="n">
+      <c r="AB37" s="9" t="n">
         <v>33.45</v>
       </c>
-      <c r="AC37" s="6" t="n">
+      <c r="AC37" s="9" t="n">
         <v>31.78</v>
       </c>
       <c r="AD37" s="6" t="inlineStr">
@@ -3404,13 +3437,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="AE37" s="6" t="n">
+      <c r="AE37" s="9" t="n">
         <v>31.59</v>
       </c>
-      <c r="AF37" s="6" t="n">
+      <c r="AF37" s="9" t="n">
         <v>33.82</v>
       </c>
-      <c r="AG37" s="6" t="n">
+      <c r="AG37" s="9" t="n">
         <v>31.83</v>
       </c>
       <c r="AH37" s="6" t="n">
@@ -3418,7 +3451,7 @@
       </c>
       <c r="AI37" s="6" t="inlineStr"/>
       <c r="AJ37" s="6" t="inlineStr"/>
-      <c r="AK37" s="12" t="n"/>
+      <c r="AK37" s="16" t="n"/>
     </row>
     <row r="38">
       <c r="A38" s="5" t="inlineStr">
@@ -3469,16 +3502,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="K38" s="6" t="n">
+      <c r="K38" s="9" t="n">
         <v>30.38</v>
       </c>
-      <c r="L38" s="6" t="n">
+      <c r="L38" s="9" t="n">
         <v>33.09</v>
       </c>
-      <c r="M38" s="6" t="n">
+      <c r="M38" s="9" t="n">
         <v>32.21</v>
       </c>
-      <c r="N38" s="6" t="n">
+      <c r="N38" s="9" t="n">
         <v>30.17</v>
       </c>
       <c r="O38" s="6" t="inlineStr">
@@ -3486,19 +3519,19 @@
           <t>-</t>
         </is>
       </c>
-      <c r="P38" s="6" t="n">
+      <c r="P38" s="9" t="n">
         <v>32.04</v>
       </c>
-      <c r="Q38" s="6" t="n">
+      <c r="Q38" s="9" t="n">
         <v>30.86</v>
       </c>
-      <c r="R38" s="6" t="n">
+      <c r="R38" s="9" t="n">
         <v>30.69</v>
       </c>
-      <c r="S38" s="6" t="n">
+      <c r="S38" s="9" t="n">
         <v>30.45</v>
       </c>
-      <c r="T38" s="6" t="n">
+      <c r="T38" s="9" t="n">
         <v>30.94</v>
       </c>
       <c r="U38" s="6" t="inlineStr">
@@ -3516,10 +3549,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="X38" s="6" t="n">
+      <c r="X38" s="9" t="n">
         <v>31.18</v>
       </c>
-      <c r="Y38" s="6" t="n">
+      <c r="Y38" s="9" t="n">
         <v>30.95</v>
       </c>
       <c r="Z38" s="6" t="inlineStr">
@@ -3527,13 +3560,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="AA38" s="6" t="n">
+      <c r="AA38" s="9" t="n">
         <v>30.83</v>
       </c>
-      <c r="AB38" s="6" t="n">
+      <c r="AB38" s="9" t="n">
         <v>31.03</v>
       </c>
-      <c r="AC38" s="6" t="n">
+      <c r="AC38" s="9" t="n">
         <v>30.71</v>
       </c>
       <c r="AD38" s="6" t="inlineStr">
@@ -3541,13 +3574,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="AE38" s="6" t="n">
+      <c r="AE38" s="9" t="n">
         <v>30.44</v>
       </c>
-      <c r="AF38" s="6" t="n">
+      <c r="AF38" s="9" t="n">
         <v>33.05</v>
       </c>
-      <c r="AG38" s="6" t="n">
+      <c r="AG38" s="9" t="n">
         <v>30.7</v>
       </c>
       <c r="AH38" s="6" t="n">
@@ -3555,7 +3588,7 @@
       </c>
       <c r="AI38" s="6" t="inlineStr"/>
       <c r="AJ38" s="6" t="inlineStr"/>
-      <c r="AK38" s="12" t="n"/>
+      <c r="AK38" s="16" t="n"/>
     </row>
     <row r="39">
       <c r="A39" s="5" t="inlineStr">
@@ -3606,16 +3639,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="K39" s="6" t="n">
+      <c r="K39" s="9" t="n">
         <v>29.23</v>
       </c>
-      <c r="L39" s="6" t="n">
+      <c r="L39" s="9" t="n">
         <v>29.27</v>
       </c>
-      <c r="M39" s="6" t="n">
+      <c r="M39" s="9" t="n">
         <v>29.72</v>
       </c>
-      <c r="N39" s="6" t="n">
+      <c r="N39" s="9" t="n">
         <v>28.44</v>
       </c>
       <c r="O39" s="6" t="inlineStr">
@@ -3623,19 +3656,19 @@
           <t>-</t>
         </is>
       </c>
-      <c r="P39" s="6" t="n">
+      <c r="P39" s="9" t="n">
         <v>29.66</v>
       </c>
-      <c r="Q39" s="6" t="n">
+      <c r="Q39" s="9" t="n">
         <v>28.68</v>
       </c>
-      <c r="R39" s="6" t="n">
+      <c r="R39" s="9" t="n">
         <v>29.01</v>
       </c>
-      <c r="S39" s="6" t="n">
+      <c r="S39" s="9" t="n">
         <v>28.72</v>
       </c>
-      <c r="T39" s="6" t="n">
+      <c r="T39" s="9" t="n">
         <v>29.25</v>
       </c>
       <c r="U39" s="6" t="inlineStr">
@@ -3653,10 +3686,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="X39" s="6" t="n">
+      <c r="X39" s="9" t="n">
         <v>29.75</v>
       </c>
-      <c r="Y39" s="6" t="n">
+      <c r="Y39" s="9" t="n">
         <v>29.47</v>
       </c>
       <c r="Z39" s="6" t="inlineStr">
@@ -3664,13 +3697,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="AA39" s="6" t="n">
+      <c r="AA39" s="9" t="n">
         <v>29.05</v>
       </c>
-      <c r="AB39" s="6" t="n">
+      <c r="AB39" s="9" t="n">
         <v>29.35</v>
       </c>
-      <c r="AC39" s="6" t="n">
+      <c r="AC39" s="9" t="n">
         <v>28.38</v>
       </c>
       <c r="AD39" s="6" t="inlineStr">
@@ -3678,13 +3711,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="AE39" s="6" t="n">
+      <c r="AE39" s="9" t="n">
         <v>29.33</v>
       </c>
-      <c r="AF39" s="6" t="n">
+      <c r="AF39" s="9" t="n">
         <v>29.64</v>
       </c>
-      <c r="AG39" s="6" t="n">
+      <c r="AG39" s="9" t="n">
         <v>29.19</v>
       </c>
       <c r="AH39" s="6" t="n">
@@ -3692,7 +3725,7 @@
       </c>
       <c r="AI39" s="6" t="inlineStr"/>
       <c r="AJ39" s="6" t="inlineStr"/>
-      <c r="AK39" s="12" t="n"/>
+      <c r="AK39" s="16" t="n"/>
     </row>
     <row r="40">
       <c r="A40" s="5" t="inlineStr">
@@ -3743,16 +3776,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="K40" s="6" t="n">
+      <c r="K40" s="9" t="n">
         <v>26.49</v>
       </c>
-      <c r="L40" s="6" t="n">
+      <c r="L40" s="9" t="n">
         <v>26.61</v>
       </c>
-      <c r="M40" s="6" t="n">
+      <c r="M40" s="9" t="n">
         <v>26.76</v>
       </c>
-      <c r="N40" s="6" t="n">
+      <c r="N40" s="9" t="n">
         <v>26.86</v>
       </c>
       <c r="O40" s="6" t="inlineStr">
@@ -3760,19 +3793,19 @@
           <t>-</t>
         </is>
       </c>
-      <c r="P40" s="6" t="n">
+      <c r="P40" s="9" t="n">
         <v>26.77</v>
       </c>
-      <c r="Q40" s="6" t="n">
+      <c r="Q40" s="9" t="n">
         <v>26.84</v>
       </c>
-      <c r="R40" s="6" t="n">
+      <c r="R40" s="9" t="n">
         <v>27.65</v>
       </c>
-      <c r="S40" s="6" t="n">
+      <c r="S40" s="9" t="n">
         <v>26.75</v>
       </c>
-      <c r="T40" s="6" t="n">
+      <c r="T40" s="9" t="n">
         <v>26.91</v>
       </c>
       <c r="U40" s="6" t="inlineStr">
@@ -3790,10 +3823,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="X40" s="6" t="n">
+      <c r="X40" s="9" t="n">
         <v>26.82</v>
       </c>
-      <c r="Y40" s="6" t="n">
+      <c r="Y40" s="9" t="n">
         <v>26.87</v>
       </c>
       <c r="Z40" s="6" t="inlineStr">
@@ -3801,13 +3834,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="AA40" s="6" t="n">
+      <c r="AA40" s="9" t="n">
         <v>26.65</v>
       </c>
-      <c r="AB40" s="6" t="n">
+      <c r="AB40" s="9" t="n">
         <v>26.82</v>
       </c>
-      <c r="AC40" s="6" t="n">
+      <c r="AC40" s="9" t="n">
         <v>26.56</v>
       </c>
       <c r="AD40" s="6" t="inlineStr">
@@ -3815,13 +3848,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="AE40" s="6" t="n">
+      <c r="AE40" s="9" t="n">
         <v>26.93</v>
       </c>
-      <c r="AF40" s="6" t="n">
+      <c r="AF40" s="9" t="n">
         <v>26.84</v>
       </c>
-      <c r="AG40" s="6" t="n">
+      <c r="AG40" s="9" t="n">
         <v>26.69</v>
       </c>
       <c r="AH40" s="6" t="n">
@@ -3829,7 +3862,7 @@
       </c>
       <c r="AI40" s="6" t="inlineStr"/>
       <c r="AJ40" s="6" t="inlineStr"/>
-      <c r="AK40" s="12" t="n"/>
+      <c r="AK40" s="16" t="n"/>
     </row>
     <row r="41">
       <c r="A41" s="5" t="inlineStr">
@@ -3880,16 +3913,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="K41" s="6" t="n">
+      <c r="K41" s="9" t="n">
         <v>26.63</v>
       </c>
-      <c r="L41" s="6" t="n">
+      <c r="L41" s="9" t="n">
         <v>26.96</v>
       </c>
-      <c r="M41" s="6" t="n">
+      <c r="M41" s="9" t="n">
         <v>26.84</v>
       </c>
-      <c r="N41" s="6" t="n">
+      <c r="N41" s="9" t="n">
         <v>26.93</v>
       </c>
       <c r="O41" s="6" t="inlineStr">
@@ -3897,19 +3930,19 @@
           <t>-</t>
         </is>
       </c>
-      <c r="P41" s="6" t="n">
+      <c r="P41" s="9" t="n">
         <v>27.04</v>
       </c>
-      <c r="Q41" s="6" t="n">
+      <c r="Q41" s="9" t="n">
         <v>26.67</v>
       </c>
-      <c r="R41" s="6" t="n">
+      <c r="R41" s="9" t="n">
         <v>26.77</v>
       </c>
-      <c r="S41" s="6" t="n">
+      <c r="S41" s="9" t="n">
         <v>26.6</v>
       </c>
-      <c r="T41" s="6" t="n">
+      <c r="T41" s="9" t="n">
         <v>27.2</v>
       </c>
       <c r="U41" s="6" t="inlineStr">
@@ -3927,10 +3960,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="X41" s="6" t="n">
+      <c r="X41" s="9" t="n">
         <v>26.92</v>
       </c>
-      <c r="Y41" s="6" t="n">
+      <c r="Y41" s="9" t="n">
         <v>27.06</v>
       </c>
       <c r="Z41" s="6" t="inlineStr">
@@ -3938,13 +3971,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="AA41" s="6" t="n">
+      <c r="AA41" s="9" t="n">
         <v>26.83</v>
       </c>
-      <c r="AB41" s="6" t="n">
+      <c r="AB41" s="9" t="n">
         <v>26.85</v>
       </c>
-      <c r="AC41" s="6" t="n">
+      <c r="AC41" s="9" t="n">
         <v>26.68</v>
       </c>
       <c r="AD41" s="6" t="inlineStr">
@@ -3952,13 +3985,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="AE41" s="6" t="n">
+      <c r="AE41" s="9" t="n">
         <v>27.21</v>
       </c>
-      <c r="AF41" s="6" t="n">
+      <c r="AF41" s="9" t="n">
         <v>27.19</v>
       </c>
-      <c r="AG41" s="6" t="n">
+      <c r="AG41" s="9" t="n">
         <v>26.73</v>
       </c>
       <c r="AH41" s="6" t="n">
@@ -3966,7 +3999,7 @@
       </c>
       <c r="AI41" s="6" t="inlineStr"/>
       <c r="AJ41" s="6" t="inlineStr"/>
-      <c r="AK41" s="12" t="n"/>
+      <c r="AK41" s="16" t="n"/>
     </row>
     <row r="42">
       <c r="A42" s="5" t="inlineStr">
@@ -4017,16 +4050,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="K42" s="6" t="n">
+      <c r="K42" s="9" t="n">
         <v>27.35</v>
       </c>
-      <c r="L42" s="6" t="n">
+      <c r="L42" s="9" t="n">
         <v>27.68</v>
       </c>
-      <c r="M42" s="6" t="n">
+      <c r="M42" s="9" t="n">
         <v>26.97</v>
       </c>
-      <c r="N42" s="6" t="n">
+      <c r="N42" s="9" t="n">
         <v>27.55</v>
       </c>
       <c r="O42" s="6" t="inlineStr">
@@ -4034,19 +4067,19 @@
           <t>-</t>
         </is>
       </c>
-      <c r="P42" s="6" t="n">
+      <c r="P42" s="9" t="n">
         <v>28.86</v>
       </c>
-      <c r="Q42" s="6" t="n">
+      <c r="Q42" s="9" t="n">
         <v>27.39</v>
       </c>
-      <c r="R42" s="6" t="n">
+      <c r="R42" s="9" t="n">
         <v>29.27</v>
       </c>
-      <c r="S42" s="6" t="n">
+      <c r="S42" s="9" t="n">
         <v>27.56</v>
       </c>
-      <c r="T42" s="6" t="n">
+      <c r="T42" s="9" t="n">
         <v>28.35</v>
       </c>
       <c r="U42" s="6" t="inlineStr">
@@ -4064,10 +4097,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="X42" s="6" t="n">
+      <c r="X42" s="9" t="n">
         <v>27.35</v>
       </c>
-      <c r="Y42" s="6" t="n">
+      <c r="Y42" s="9" t="n">
         <v>27.39</v>
       </c>
       <c r="Z42" s="6" t="inlineStr">
@@ -4075,13 +4108,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="AA42" s="6" t="n">
+      <c r="AA42" s="9" t="n">
         <v>27.07</v>
       </c>
-      <c r="AB42" s="6" t="n">
+      <c r="AB42" s="9" t="n">
         <v>27.45</v>
       </c>
-      <c r="AC42" s="6" t="n">
+      <c r="AC42" s="9" t="n">
         <v>27.13</v>
       </c>
       <c r="AD42" s="6" t="inlineStr">
@@ -4089,13 +4122,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="AE42" s="6" t="n">
+      <c r="AE42" s="9" t="n">
         <v>27.25</v>
       </c>
-      <c r="AF42" s="6" t="n">
+      <c r="AF42" s="9" t="n">
         <v>27.71</v>
       </c>
-      <c r="AG42" s="6" t="n">
+      <c r="AG42" s="9" t="n">
         <v>27.53</v>
       </c>
       <c r="AH42" s="6" t="n">
@@ -4103,144 +4136,144 @@
       </c>
       <c r="AI42" s="6" t="inlineStr"/>
       <c r="AJ42" s="6" t="inlineStr"/>
-      <c r="AK42" s="12" t="n"/>
+      <c r="AK42" s="16" t="n"/>
     </row>
     <row r="43">
-      <c r="A43" s="8" t="inlineStr">
+      <c r="A43" s="11" t="inlineStr">
         <is>
           <t>TELECIUDADANA</t>
         </is>
       </c>
-      <c r="B43" s="9" t="n">
+      <c r="B43" s="12" t="n">
         <v>681.25</v>
       </c>
-      <c r="C43" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D43" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E43" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F43" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G43" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H43" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I43" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J43" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K43" s="9" t="n">
+      <c r="C43" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D43" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E43" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F43" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G43" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H43" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I43" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J43" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K43" s="17" t="n">
         <v>27.51</v>
       </c>
-      <c r="L43" s="9" t="n">
+      <c r="L43" s="17" t="n">
         <v>27.51</v>
       </c>
-      <c r="M43" s="9" t="n">
+      <c r="M43" s="17" t="n">
         <v>27.42</v>
       </c>
-      <c r="N43" s="9" t="n">
+      <c r="N43" s="17" t="n">
         <v>27.63</v>
       </c>
-      <c r="O43" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P43" s="9" t="n">
+      <c r="O43" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P43" s="17" t="n">
         <v>27.18</v>
       </c>
-      <c r="Q43" s="9" t="n">
+      <c r="Q43" s="17" t="n">
         <v>27.42</v>
       </c>
-      <c r="R43" s="9" t="n">
+      <c r="R43" s="17" t="n">
         <v>29.01</v>
       </c>
-      <c r="S43" s="9" t="n">
+      <c r="S43" s="17" t="n">
         <v>27.59</v>
       </c>
-      <c r="T43" s="9" t="n">
+      <c r="T43" s="17" t="n">
         <v>27.61</v>
       </c>
-      <c r="U43" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="V43" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="W43" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="X43" s="9" t="n">
+      <c r="U43" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="V43" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="W43" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="X43" s="17" t="n">
         <v>27.49</v>
       </c>
-      <c r="Y43" s="9" t="n">
+      <c r="Y43" s="17" t="n">
         <v>27.51</v>
       </c>
-      <c r="Z43" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AA43" s="9" t="n">
+      <c r="Z43" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AA43" s="17" t="n">
         <v>27.53</v>
       </c>
-      <c r="AB43" s="9" t="n">
+      <c r="AB43" s="17" t="n">
         <v>27.47</v>
       </c>
-      <c r="AC43" s="9" t="n">
+      <c r="AC43" s="17" t="n">
         <v>27.33</v>
       </c>
-      <c r="AD43" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AE43" s="9" t="n">
+      <c r="AD43" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AE43" s="17" t="n">
         <v>27.68</v>
       </c>
-      <c r="AF43" s="9" t="n">
+      <c r="AF43" s="17" t="n">
         <v>27.72</v>
       </c>
-      <c r="AG43" s="9" t="n">
+      <c r="AG43" s="17" t="n">
         <v>27.44</v>
       </c>
-      <c r="AH43" s="9" t="n">
+      <c r="AH43" s="12" t="n">
         <v>27.59</v>
       </c>
-      <c r="AI43" s="9" t="inlineStr"/>
-      <c r="AJ43" s="9" t="inlineStr"/>
-      <c r="AK43" s="13" t="n"/>
+      <c r="AI43" s="12" t="inlineStr"/>
+      <c r="AJ43" s="12" t="inlineStr"/>
+      <c r="AK43" s="18" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="28">

--- a/ReportesUnificados/zamora_ReporteUnificado.xlsx
+++ b/ReportesUnificados/zamora_ReporteUnificado.xlsx
@@ -30,30 +30,12 @@
       <sz val="12"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="2">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCDFECE"/>
-        <bgColor rgb="FFCDFECE"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFE9F"/>
-        <bgColor rgb="FFFFFE9F"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFD9BCB"/>
-        <bgColor rgb="FFFD9BCB"/>
-      </patternFill>
     </fill>
   </fills>
   <borders count="17">
@@ -171,7 +153,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -191,15 +173,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -209,17 +182,11 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="16" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="12" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="13" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
@@ -792,7 +759,7 @@
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>FECHA PRESENTACIÓN: 28/08/2025</t>
+          <t>FECHA PRESENTACIÓN: 27/08/2025</t>
         </is>
       </c>
     </row>
@@ -974,16 +941,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="K11" s="7" t="n">
+      <c r="K11" s="6" t="n">
         <v>56.96</v>
       </c>
-      <c r="L11" s="7" t="n">
+      <c r="L11" s="6" t="n">
         <v>54.92</v>
       </c>
-      <c r="M11" s="7" t="n">
+      <c r="M11" s="6" t="n">
         <v>55.02</v>
       </c>
-      <c r="N11" s="8" t="n">
+      <c r="N11" s="6" t="n">
         <v>53.54</v>
       </c>
       <c r="O11" s="6" t="inlineStr">
@@ -991,19 +958,19 @@
           <t>-</t>
         </is>
       </c>
-      <c r="P11" s="9" t="n">
+      <c r="P11" s="6" t="n">
         <v>41.6</v>
       </c>
-      <c r="Q11" s="9" t="n">
+      <c r="Q11" s="6" t="n">
         <v>40.72</v>
       </c>
-      <c r="R11" s="9" t="n">
+      <c r="R11" s="6" t="n">
         <v>39.48</v>
       </c>
-      <c r="S11" s="9" t="n">
+      <c r="S11" s="6" t="n">
         <v>39</v>
       </c>
-      <c r="T11" s="9" t="n">
+      <c r="T11" s="6" t="n">
         <v>39.18</v>
       </c>
       <c r="U11" s="6" t="inlineStr">
@@ -1021,10 +988,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="X11" s="8" t="n">
+      <c r="X11" s="6" t="n">
         <v>43.07</v>
       </c>
-      <c r="Y11" s="9" t="n">
+      <c r="Y11" s="6" t="n">
         <v>38.32</v>
       </c>
       <c r="Z11" s="6" t="inlineStr">
@@ -1032,13 +999,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="AA11" s="8" t="n">
+      <c r="AA11" s="6" t="n">
         <v>46.74</v>
       </c>
-      <c r="AB11" s="8" t="n">
+      <c r="AB11" s="6" t="n">
         <v>43.68</v>
       </c>
-      <c r="AC11" s="9" t="n">
+      <c r="AC11" s="6" t="n">
         <v>40.17</v>
       </c>
       <c r="AD11" s="6" t="inlineStr">
@@ -1046,13 +1013,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="AE11" s="9" t="n">
+      <c r="AE11" s="6" t="n">
         <v>42.11</v>
       </c>
-      <c r="AF11" s="9" t="n">
+      <c r="AF11" s="6" t="n">
         <v>40.11</v>
       </c>
-      <c r="AG11" s="9" t="n">
+      <c r="AG11" s="6" t="n">
         <v>41.92</v>
       </c>
       <c r="AH11" s="6" t="n">
@@ -1062,7 +1029,7 @@
         <v>485.74</v>
       </c>
       <c r="AJ11" s="6" t="inlineStr"/>
-      <c r="AK11" s="10" t="inlineStr"/>
+      <c r="AK11" s="7" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
@@ -1113,16 +1080,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="K12" s="7" t="n">
+      <c r="K12" s="6" t="n">
         <v>75.64</v>
       </c>
-      <c r="L12" s="7" t="n">
+      <c r="L12" s="6" t="n">
         <v>76.81</v>
       </c>
-      <c r="M12" s="7" t="n">
+      <c r="M12" s="6" t="n">
         <v>79.76000000000001</v>
       </c>
-      <c r="N12" s="7" t="n">
+      <c r="N12" s="6" t="n">
         <v>81.90000000000001</v>
       </c>
       <c r="O12" s="6" t="inlineStr">
@@ -1130,19 +1097,19 @@
           <t>-</t>
         </is>
       </c>
-      <c r="P12" s="7" t="n">
+      <c r="P12" s="6" t="n">
         <v>82.14</v>
       </c>
-      <c r="Q12" s="7" t="n">
+      <c r="Q12" s="6" t="n">
         <v>81.20999999999999</v>
       </c>
-      <c r="R12" s="7" t="n">
+      <c r="R12" s="6" t="n">
         <v>81.06</v>
       </c>
-      <c r="S12" s="7" t="n">
+      <c r="S12" s="6" t="n">
         <v>78.68000000000001</v>
       </c>
-      <c r="T12" s="7" t="n">
+      <c r="T12" s="6" t="n">
         <v>77.7</v>
       </c>
       <c r="U12" s="6" t="inlineStr">
@@ -1160,10 +1127,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="X12" s="7" t="n">
+      <c r="X12" s="6" t="n">
         <v>81.20999999999999</v>
       </c>
-      <c r="Y12" s="7" t="n">
+      <c r="Y12" s="6" t="n">
         <v>80.66</v>
       </c>
       <c r="Z12" s="6" t="inlineStr">
@@ -1171,13 +1138,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="AA12" s="7" t="n">
+      <c r="AA12" s="6" t="n">
         <v>81.11</v>
       </c>
-      <c r="AB12" s="7" t="n">
+      <c r="AB12" s="6" t="n">
         <v>79.63</v>
       </c>
-      <c r="AC12" s="7" t="n">
+      <c r="AC12" s="6" t="n">
         <v>78.40000000000001</v>
       </c>
       <c r="AD12" s="6" t="inlineStr">
@@ -1185,13 +1152,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="AE12" s="8" t="n">
+      <c r="AE12" s="6" t="n">
         <v>46.82</v>
       </c>
-      <c r="AF12" s="9" t="n">
+      <c r="AF12" s="6" t="n">
         <v>40.81</v>
       </c>
-      <c r="AG12" s="9" t="n">
+      <c r="AG12" s="6" t="n">
         <v>41.96</v>
       </c>
       <c r="AH12" s="6" t="n">
@@ -1201,7 +1168,7 @@
         <v>101.16</v>
       </c>
       <c r="AJ12" s="6" t="inlineStr"/>
-      <c r="AK12" s="10" t="inlineStr"/>
+      <c r="AK12" s="7" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
@@ -1252,16 +1219,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="K13" s="7" t="n">
+      <c r="K13" s="6" t="n">
         <v>103.89</v>
       </c>
-      <c r="L13" s="7" t="n">
+      <c r="L13" s="6" t="n">
         <v>99.87</v>
       </c>
-      <c r="M13" s="7" t="n">
+      <c r="M13" s="6" t="n">
         <v>101.34</v>
       </c>
-      <c r="N13" s="7" t="n">
+      <c r="N13" s="6" t="n">
         <v>98.73999999999999</v>
       </c>
       <c r="O13" s="6" t="inlineStr">
@@ -1269,19 +1236,19 @@
           <t>-</t>
         </is>
       </c>
-      <c r="P13" s="7" t="n">
+      <c r="P13" s="6" t="n">
         <v>102.67</v>
       </c>
-      <c r="Q13" s="7" t="n">
+      <c r="Q13" s="6" t="n">
         <v>103.09</v>
       </c>
-      <c r="R13" s="7" t="n">
+      <c r="R13" s="6" t="n">
         <v>101.87</v>
       </c>
-      <c r="S13" s="7" t="n">
+      <c r="S13" s="6" t="n">
         <v>102.12</v>
       </c>
-      <c r="T13" s="7" t="n">
+      <c r="T13" s="6" t="n">
         <v>102.97</v>
       </c>
       <c r="U13" s="6" t="inlineStr">
@@ -1299,10 +1266,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="X13" s="7" t="n">
+      <c r="X13" s="6" t="n">
         <v>102.96</v>
       </c>
-      <c r="Y13" s="7" t="n">
+      <c r="Y13" s="6" t="n">
         <v>101.1</v>
       </c>
       <c r="Z13" s="6" t="inlineStr">
@@ -1310,13 +1277,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="AA13" s="7" t="n">
+      <c r="AA13" s="6" t="n">
         <v>102.83</v>
       </c>
-      <c r="AB13" s="7" t="n">
+      <c r="AB13" s="6" t="n">
         <v>102.38</v>
       </c>
-      <c r="AC13" s="7" t="n">
+      <c r="AC13" s="6" t="n">
         <v>101.42</v>
       </c>
       <c r="AD13" s="6" t="inlineStr">
@@ -1324,13 +1291,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="AE13" s="7" t="n">
+      <c r="AE13" s="6" t="n">
         <v>101.67</v>
       </c>
-      <c r="AF13" s="7" t="n">
+      <c r="AF13" s="6" t="n">
         <v>102.23</v>
       </c>
-      <c r="AG13" s="7" t="n">
+      <c r="AG13" s="6" t="n">
         <v>100.99</v>
       </c>
       <c r="AH13" s="6" t="n">
@@ -1340,7 +1307,7 @@
         <v>104.99</v>
       </c>
       <c r="AJ13" s="6" t="inlineStr"/>
-      <c r="AK13" s="10" t="inlineStr"/>
+      <c r="AK13" s="7" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
@@ -1391,16 +1358,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="K14" s="7" t="n">
+      <c r="K14" s="6" t="n">
         <v>89.91</v>
       </c>
-      <c r="L14" s="7" t="n">
+      <c r="L14" s="6" t="n">
         <v>89.05</v>
       </c>
-      <c r="M14" s="7" t="n">
+      <c r="M14" s="6" t="n">
         <v>89.79000000000001</v>
       </c>
-      <c r="N14" s="7" t="n">
+      <c r="N14" s="6" t="n">
         <v>90.05</v>
       </c>
       <c r="O14" s="6" t="inlineStr">
@@ -1408,19 +1375,19 @@
           <t>-</t>
         </is>
       </c>
-      <c r="P14" s="7" t="n">
+      <c r="P14" s="6" t="n">
         <v>91.48</v>
       </c>
-      <c r="Q14" s="7" t="n">
+      <c r="Q14" s="6" t="n">
         <v>91.84</v>
       </c>
-      <c r="R14" s="7" t="n">
+      <c r="R14" s="6" t="n">
         <v>90.95999999999999</v>
       </c>
-      <c r="S14" s="7" t="n">
+      <c r="S14" s="6" t="n">
         <v>90.70999999999999</v>
       </c>
-      <c r="T14" s="7" t="n">
+      <c r="T14" s="6" t="n">
         <v>90.53</v>
       </c>
       <c r="U14" s="6" t="inlineStr">
@@ -1438,10 +1405,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="X14" s="7" t="n">
+      <c r="X14" s="6" t="n">
         <v>92.17</v>
       </c>
-      <c r="Y14" s="7" t="n">
+      <c r="Y14" s="6" t="n">
         <v>89.58</v>
       </c>
       <c r="Z14" s="6" t="inlineStr">
@@ -1449,13 +1416,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="AA14" s="7" t="n">
+      <c r="AA14" s="6" t="n">
         <v>92.22</v>
       </c>
-      <c r="AB14" s="7" t="n">
+      <c r="AB14" s="6" t="n">
         <v>91.28</v>
       </c>
-      <c r="AC14" s="7" t="n">
+      <c r="AC14" s="6" t="n">
         <v>91.42</v>
       </c>
       <c r="AD14" s="6" t="inlineStr">
@@ -1463,13 +1430,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="AE14" s="7" t="n">
+      <c r="AE14" s="6" t="n">
         <v>92.08</v>
       </c>
-      <c r="AF14" s="7" t="n">
+      <c r="AF14" s="6" t="n">
         <v>91.31999999999999</v>
       </c>
-      <c r="AG14" s="7" t="n">
+      <c r="AG14" s="6" t="n">
         <v>90.73999999999999</v>
       </c>
       <c r="AH14" s="6" t="n">
@@ -1479,7 +1446,7 @@
         <v>119.83</v>
       </c>
       <c r="AJ14" s="6" t="inlineStr"/>
-      <c r="AK14" s="10" t="inlineStr"/>
+      <c r="AK14" s="7" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
@@ -1530,16 +1497,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="K15" s="7" t="n">
+      <c r="K15" s="6" t="n">
         <v>73.76000000000001</v>
       </c>
-      <c r="L15" s="7" t="n">
+      <c r="L15" s="6" t="n">
         <v>72.86</v>
       </c>
-      <c r="M15" s="7" t="n">
+      <c r="M15" s="6" t="n">
         <v>73.77</v>
       </c>
-      <c r="N15" s="7" t="n">
+      <c r="N15" s="6" t="n">
         <v>73.42</v>
       </c>
       <c r="O15" s="6" t="inlineStr">
@@ -1547,19 +1514,19 @@
           <t>-</t>
         </is>
       </c>
-      <c r="P15" s="7" t="n">
+      <c r="P15" s="6" t="n">
         <v>74.97</v>
       </c>
-      <c r="Q15" s="7" t="n">
+      <c r="Q15" s="6" t="n">
         <v>74.93000000000001</v>
       </c>
-      <c r="R15" s="7" t="n">
+      <c r="R15" s="6" t="n">
         <v>74.58</v>
       </c>
-      <c r="S15" s="7" t="n">
+      <c r="S15" s="6" t="n">
         <v>74.12</v>
       </c>
-      <c r="T15" s="7" t="n">
+      <c r="T15" s="6" t="n">
         <v>74.38</v>
       </c>
       <c r="U15" s="6" t="inlineStr">
@@ -1577,10 +1544,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="X15" s="7" t="n">
+      <c r="X15" s="6" t="n">
         <v>74.73999999999999</v>
       </c>
-      <c r="Y15" s="7" t="n">
+      <c r="Y15" s="6" t="n">
         <v>74.34</v>
       </c>
       <c r="Z15" s="6" t="inlineStr">
@@ -1588,13 +1555,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="AA15" s="7" t="n">
+      <c r="AA15" s="6" t="n">
         <v>74.92</v>
       </c>
-      <c r="AB15" s="7" t="n">
+      <c r="AB15" s="6" t="n">
         <v>75.15000000000001</v>
       </c>
-      <c r="AC15" s="7" t="n">
+      <c r="AC15" s="6" t="n">
         <v>75.31</v>
       </c>
       <c r="AD15" s="6" t="inlineStr">
@@ -1602,13 +1569,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="AE15" s="7" t="n">
+      <c r="AE15" s="6" t="n">
         <v>74.61</v>
       </c>
-      <c r="AF15" s="7" t="n">
+      <c r="AF15" s="6" t="n">
         <v>75.12</v>
       </c>
-      <c r="AG15" s="7" t="n">
+      <c r="AG15" s="6" t="n">
         <v>74.22</v>
       </c>
       <c r="AH15" s="6" t="n">
@@ -1618,7 +1585,7 @@
         <v>156.6</v>
       </c>
       <c r="AJ15" s="6" t="inlineStr"/>
-      <c r="AK15" s="10" t="inlineStr"/>
+      <c r="AK15" s="7" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
@@ -1669,16 +1636,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="K16" s="7" t="n">
+      <c r="K16" s="6" t="n">
         <v>90.2</v>
       </c>
-      <c r="L16" s="7" t="n">
+      <c r="L16" s="6" t="n">
         <v>87.67</v>
       </c>
-      <c r="M16" s="7" t="n">
+      <c r="M16" s="6" t="n">
         <v>89.05</v>
       </c>
-      <c r="N16" s="7" t="n">
+      <c r="N16" s="6" t="n">
         <v>88.61</v>
       </c>
       <c r="O16" s="6" t="inlineStr">
@@ -1686,19 +1653,19 @@
           <t>-</t>
         </is>
       </c>
-      <c r="P16" s="7" t="n">
+      <c r="P16" s="6" t="n">
         <v>90.01000000000001</v>
       </c>
-      <c r="Q16" s="7" t="n">
+      <c r="Q16" s="6" t="n">
         <v>89.26000000000001</v>
       </c>
-      <c r="R16" s="7" t="n">
+      <c r="R16" s="6" t="n">
         <v>89.18000000000001</v>
       </c>
-      <c r="S16" s="7" t="n">
+      <c r="S16" s="6" t="n">
         <v>90.37</v>
       </c>
-      <c r="T16" s="7" t="n">
+      <c r="T16" s="6" t="n">
         <v>90.94</v>
       </c>
       <c r="U16" s="6" t="inlineStr">
@@ -1716,10 +1683,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="X16" s="7" t="n">
+      <c r="X16" s="6" t="n">
         <v>90.41</v>
       </c>
-      <c r="Y16" s="7" t="n">
+      <c r="Y16" s="6" t="n">
         <v>88.64</v>
       </c>
       <c r="Z16" s="6" t="inlineStr">
@@ -1727,13 +1694,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="AA16" s="7" t="n">
+      <c r="AA16" s="6" t="n">
         <v>90.01000000000001</v>
       </c>
-      <c r="AB16" s="7" t="n">
+      <c r="AB16" s="6" t="n">
         <v>89.69</v>
       </c>
-      <c r="AC16" s="7" t="n">
+      <c r="AC16" s="6" t="n">
         <v>89.87</v>
       </c>
       <c r="AD16" s="6" t="inlineStr">
@@ -1741,13 +1708,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="AE16" s="7" t="n">
+      <c r="AE16" s="6" t="n">
         <v>89.26000000000001</v>
       </c>
-      <c r="AF16" s="7" t="n">
+      <c r="AF16" s="6" t="n">
         <v>88.64</v>
       </c>
-      <c r="AG16" s="7" t="n">
+      <c r="AG16" s="6" t="n">
         <v>88.94</v>
       </c>
       <c r="AH16" s="6" t="n">
@@ -1757,7 +1724,7 @@
         <v>138.26</v>
       </c>
       <c r="AJ16" s="6" t="inlineStr"/>
-      <c r="AK16" s="10" t="inlineStr"/>
+      <c r="AK16" s="7" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
@@ -1808,16 +1775,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="K17" s="7" t="n">
+      <c r="K17" s="6" t="n">
         <v>103.71</v>
       </c>
-      <c r="L17" s="7" t="n">
+      <c r="L17" s="6" t="n">
         <v>102.89</v>
       </c>
-      <c r="M17" s="7" t="n">
+      <c r="M17" s="6" t="n">
         <v>104.26</v>
       </c>
-      <c r="N17" s="7" t="n">
+      <c r="N17" s="6" t="n">
         <v>103.16</v>
       </c>
       <c r="O17" s="6" t="inlineStr">
@@ -1825,19 +1792,19 @@
           <t>-</t>
         </is>
       </c>
-      <c r="P17" s="7" t="n">
+      <c r="P17" s="6" t="n">
         <v>105.67</v>
       </c>
-      <c r="Q17" s="7" t="n">
+      <c r="Q17" s="6" t="n">
         <v>105.56</v>
       </c>
-      <c r="R17" s="7" t="n">
+      <c r="R17" s="6" t="n">
         <v>105</v>
       </c>
-      <c r="S17" s="7" t="n">
+      <c r="S17" s="6" t="n">
         <v>104.83</v>
       </c>
-      <c r="T17" s="7" t="n">
+      <c r="T17" s="6" t="n">
         <v>105.03</v>
       </c>
       <c r="U17" s="6" t="inlineStr">
@@ -1855,10 +1822,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="X17" s="7" t="n">
+      <c r="X17" s="6" t="n">
         <v>105.37</v>
       </c>
-      <c r="Y17" s="7" t="n">
+      <c r="Y17" s="6" t="n">
         <v>104.17</v>
       </c>
       <c r="Z17" s="6" t="inlineStr">
@@ -1866,13 +1833,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="AA17" s="7" t="n">
+      <c r="AA17" s="6" t="n">
         <v>105.66</v>
       </c>
-      <c r="AB17" s="7" t="n">
+      <c r="AB17" s="6" t="n">
         <v>105.14</v>
       </c>
-      <c r="AC17" s="7" t="n">
+      <c r="AC17" s="6" t="n">
         <v>104.84</v>
       </c>
       <c r="AD17" s="6" t="inlineStr">
@@ -1880,13 +1847,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="AE17" s="7" t="n">
+      <c r="AE17" s="6" t="n">
         <v>105.13</v>
       </c>
-      <c r="AF17" s="7" t="n">
+      <c r="AF17" s="6" t="n">
         <v>105.22</v>
       </c>
-      <c r="AG17" s="7" t="n">
+      <c r="AG17" s="6" t="n">
         <v>104.76</v>
       </c>
       <c r="AH17" s="6" t="n">
@@ -1896,7 +1863,7 @@
         <v>246.97</v>
       </c>
       <c r="AJ17" s="6" t="inlineStr"/>
-      <c r="AK17" s="10" t="inlineStr"/>
+      <c r="AK17" s="7" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
@@ -1947,16 +1914,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="K18" s="7" t="n">
+      <c r="K18" s="6" t="n">
         <v>66.56</v>
       </c>
-      <c r="L18" s="7" t="n">
+      <c r="L18" s="6" t="n">
         <v>70.83</v>
       </c>
-      <c r="M18" s="7" t="n">
+      <c r="M18" s="6" t="n">
         <v>71.56999999999999</v>
       </c>
-      <c r="N18" s="7" t="n">
+      <c r="N18" s="6" t="n">
         <v>70.55</v>
       </c>
       <c r="O18" s="6" t="inlineStr">
@@ -1964,19 +1931,19 @@
           <t>-</t>
         </is>
       </c>
-      <c r="P18" s="7" t="n">
+      <c r="P18" s="6" t="n">
         <v>73.66</v>
       </c>
-      <c r="Q18" s="7" t="n">
+      <c r="Q18" s="6" t="n">
         <v>73.25</v>
       </c>
-      <c r="R18" s="7" t="n">
+      <c r="R18" s="6" t="n">
         <v>73.23</v>
       </c>
-      <c r="S18" s="7" t="n">
+      <c r="S18" s="6" t="n">
         <v>68.51000000000001</v>
       </c>
-      <c r="T18" s="7" t="n">
+      <c r="T18" s="6" t="n">
         <v>70.68000000000001</v>
       </c>
       <c r="U18" s="6" t="inlineStr">
@@ -1994,10 +1961,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="X18" s="7" t="n">
+      <c r="X18" s="6" t="n">
         <v>72.51000000000001</v>
       </c>
-      <c r="Y18" s="7" t="n">
+      <c r="Y18" s="6" t="n">
         <v>66.12</v>
       </c>
       <c r="Z18" s="6" t="inlineStr">
@@ -2005,13 +1972,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="AA18" s="7" t="n">
+      <c r="AA18" s="6" t="n">
         <v>71.5</v>
       </c>
-      <c r="AB18" s="7" t="n">
+      <c r="AB18" s="6" t="n">
         <v>70.66</v>
       </c>
-      <c r="AC18" s="7" t="n">
+      <c r="AC18" s="6" t="n">
         <v>70.8</v>
       </c>
       <c r="AD18" s="6" t="inlineStr">
@@ -2019,13 +1986,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="AE18" s="7" t="n">
+      <c r="AE18" s="6" t="n">
         <v>71.98999999999999</v>
       </c>
-      <c r="AF18" s="7" t="n">
+      <c r="AF18" s="6" t="n">
         <v>71.06999999999999</v>
       </c>
-      <c r="AG18" s="7" t="n">
+      <c r="AG18" s="6" t="n">
         <v>71.56999999999999</v>
       </c>
       <c r="AH18" s="6" t="n">
@@ -2035,7 +2002,7 @@
         <v>52.8</v>
       </c>
       <c r="AJ18" s="6" t="inlineStr"/>
-      <c r="AK18" s="10" t="inlineStr"/>
+      <c r="AK18" s="7" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
@@ -2086,16 +2053,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="K19" s="8" t="n">
+      <c r="K19" s="6" t="n">
         <v>46.03</v>
       </c>
-      <c r="L19" s="8" t="n">
+      <c r="L19" s="6" t="n">
         <v>43.57</v>
       </c>
-      <c r="M19" s="8" t="n">
+      <c r="M19" s="6" t="n">
         <v>45.68</v>
       </c>
-      <c r="N19" s="8" t="n">
+      <c r="N19" s="6" t="n">
         <v>44.8</v>
       </c>
       <c r="O19" s="6" t="inlineStr">
@@ -2103,19 +2070,19 @@
           <t>-</t>
         </is>
       </c>
-      <c r="P19" s="8" t="n">
+      <c r="P19" s="6" t="n">
         <v>47.17</v>
       </c>
-      <c r="Q19" s="8" t="n">
+      <c r="Q19" s="6" t="n">
         <v>46.81</v>
       </c>
-      <c r="R19" s="8" t="n">
+      <c r="R19" s="6" t="n">
         <v>46.39</v>
       </c>
-      <c r="S19" s="8" t="n">
+      <c r="S19" s="6" t="n">
         <v>47.11</v>
       </c>
-      <c r="T19" s="8" t="n">
+      <c r="T19" s="6" t="n">
         <v>47</v>
       </c>
       <c r="U19" s="6" t="inlineStr">
@@ -2133,10 +2100,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="X19" s="8" t="n">
+      <c r="X19" s="6" t="n">
         <v>47.87</v>
       </c>
-      <c r="Y19" s="8" t="n">
+      <c r="Y19" s="6" t="n">
         <v>45.81</v>
       </c>
       <c r="Z19" s="6" t="inlineStr">
@@ -2144,13 +2111,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="AA19" s="8" t="n">
+      <c r="AA19" s="6" t="n">
         <v>47.24</v>
       </c>
-      <c r="AB19" s="8" t="n">
+      <c r="AB19" s="6" t="n">
         <v>46.43</v>
       </c>
-      <c r="AC19" s="8" t="n">
+      <c r="AC19" s="6" t="n">
         <v>46.17</v>
       </c>
       <c r="AD19" s="6" t="inlineStr">
@@ -2158,13 +2125,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="AE19" s="8" t="n">
+      <c r="AE19" s="6" t="n">
         <v>46.36</v>
       </c>
-      <c r="AF19" s="8" t="n">
+      <c r="AF19" s="6" t="n">
         <v>46.06</v>
       </c>
-      <c r="AG19" s="8" t="n">
+      <c r="AG19" s="6" t="n">
         <v>45.74</v>
       </c>
       <c r="AH19" s="6" t="n">
@@ -2174,7 +2141,7 @@
         <v>477.49</v>
       </c>
       <c r="AJ19" s="6" t="inlineStr"/>
-      <c r="AK19" s="10" t="inlineStr"/>
+      <c r="AK19" s="7" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="5" t="inlineStr">
@@ -2225,16 +2192,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="K20" s="7" t="n">
+      <c r="K20" s="6" t="n">
         <v>82.23999999999999</v>
       </c>
-      <c r="L20" s="7" t="n">
+      <c r="L20" s="6" t="n">
         <v>83.69</v>
       </c>
-      <c r="M20" s="7" t="n">
+      <c r="M20" s="6" t="n">
         <v>81.95999999999999</v>
       </c>
-      <c r="N20" s="7" t="n">
+      <c r="N20" s="6" t="n">
         <v>82.68000000000001</v>
       </c>
       <c r="O20" s="6" t="inlineStr">
@@ -2242,19 +2209,19 @@
           <t>-</t>
         </is>
       </c>
-      <c r="P20" s="7" t="n">
+      <c r="P20" s="6" t="n">
         <v>81.26000000000001</v>
       </c>
-      <c r="Q20" s="7" t="n">
+      <c r="Q20" s="6" t="n">
         <v>80.44</v>
       </c>
-      <c r="R20" s="7" t="n">
+      <c r="R20" s="6" t="n">
         <v>79.55</v>
       </c>
-      <c r="S20" s="7" t="n">
+      <c r="S20" s="6" t="n">
         <v>82.98</v>
       </c>
-      <c r="T20" s="7" t="n">
+      <c r="T20" s="6" t="n">
         <v>82.94</v>
       </c>
       <c r="U20" s="6" t="inlineStr">
@@ -2272,10 +2239,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="X20" s="7" t="n">
+      <c r="X20" s="6" t="n">
         <v>82.48999999999999</v>
       </c>
-      <c r="Y20" s="7" t="n">
+      <c r="Y20" s="6" t="n">
         <v>81.39</v>
       </c>
       <c r="Z20" s="6" t="inlineStr">
@@ -2283,13 +2250,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="AA20" s="7" t="n">
+      <c r="AA20" s="6" t="n">
         <v>80.79000000000001</v>
       </c>
-      <c r="AB20" s="7" t="n">
+      <c r="AB20" s="6" t="n">
         <v>81.12</v>
       </c>
-      <c r="AC20" s="7" t="n">
+      <c r="AC20" s="6" t="n">
         <v>78.63</v>
       </c>
       <c r="AD20" s="6" t="inlineStr">
@@ -2297,13 +2264,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="AE20" s="7" t="n">
+      <c r="AE20" s="6" t="n">
         <v>80.22</v>
       </c>
-      <c r="AF20" s="7" t="n">
+      <c r="AF20" s="6" t="n">
         <v>80.81</v>
       </c>
-      <c r="AG20" s="7" t="n">
+      <c r="AG20" s="6" t="n">
         <v>80.31999999999999</v>
       </c>
       <c r="AH20" s="6" t="n">
@@ -2313,7 +2280,7 @@
         <v>149.08</v>
       </c>
       <c r="AJ20" s="6" t="inlineStr"/>
-      <c r="AK20" s="10" t="inlineStr"/>
+      <c r="AK20" s="7" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
@@ -2364,16 +2331,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="K21" s="7" t="n">
+      <c r="K21" s="6" t="n">
         <v>55.96</v>
       </c>
-      <c r="L21" s="7" t="n">
+      <c r="L21" s="6" t="n">
         <v>57.99</v>
       </c>
-      <c r="M21" s="7" t="n">
+      <c r="M21" s="6" t="n">
         <v>56.92</v>
       </c>
-      <c r="N21" s="7" t="n">
+      <c r="N21" s="6" t="n">
         <v>59.21</v>
       </c>
       <c r="O21" s="6" t="inlineStr">
@@ -2381,19 +2348,19 @@
           <t>-</t>
         </is>
       </c>
-      <c r="P21" s="7" t="n">
+      <c r="P21" s="6" t="n">
         <v>55.46</v>
       </c>
-      <c r="Q21" s="7" t="n">
+      <c r="Q21" s="6" t="n">
         <v>55.44</v>
       </c>
-      <c r="R21" s="7" t="n">
+      <c r="R21" s="6" t="n">
         <v>56.11</v>
       </c>
-      <c r="S21" s="7" t="n">
+      <c r="S21" s="6" t="n">
         <v>54.27</v>
       </c>
-      <c r="T21" s="7" t="n">
+      <c r="T21" s="6" t="n">
         <v>55.4</v>
       </c>
       <c r="U21" s="6" t="inlineStr">
@@ -2411,10 +2378,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="X21" s="7" t="n">
+      <c r="X21" s="6" t="n">
         <v>55.71</v>
       </c>
-      <c r="Y21" s="7" t="n">
+      <c r="Y21" s="6" t="n">
         <v>57.52</v>
       </c>
       <c r="Z21" s="6" t="inlineStr">
@@ -2422,13 +2389,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="AA21" s="7" t="n">
+      <c r="AA21" s="6" t="n">
         <v>55.4</v>
       </c>
-      <c r="AB21" s="7" t="n">
+      <c r="AB21" s="6" t="n">
         <v>56.72</v>
       </c>
-      <c r="AC21" s="7" t="n">
+      <c r="AC21" s="6" t="n">
         <v>56.56</v>
       </c>
       <c r="AD21" s="6" t="inlineStr">
@@ -2436,13 +2403,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="AE21" s="7" t="n">
+      <c r="AE21" s="6" t="n">
         <v>55.47</v>
       </c>
-      <c r="AF21" s="7" t="n">
+      <c r="AF21" s="6" t="n">
         <v>56.47</v>
       </c>
-      <c r="AG21" s="7" t="n">
+      <c r="AG21" s="6" t="n">
         <v>57.08</v>
       </c>
       <c r="AH21" s="6" t="n">
@@ -2452,146 +2419,146 @@
         <v>157.64</v>
       </c>
       <c r="AJ21" s="6" t="inlineStr"/>
-      <c r="AK21" s="10" t="inlineStr"/>
+      <c r="AK21" s="7" t="inlineStr"/>
     </row>
     <row r="22">
-      <c r="A22" s="11" t="inlineStr">
+      <c r="A22" s="8" t="inlineStr">
         <is>
           <t>ZETA</t>
         </is>
       </c>
-      <c r="B22" s="12" t="n">
+      <c r="B22" s="9" t="n">
         <v>106.9</v>
       </c>
-      <c r="C22" s="12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D22" s="12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E22" s="12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F22" s="12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G22" s="12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H22" s="12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I22" s="12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J22" s="12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K22" s="13" t="n">
+      <c r="C22" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D22" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E22" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F22" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G22" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H22" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I22" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J22" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K22" s="9" t="n">
         <v>94.18000000000001</v>
       </c>
-      <c r="L22" s="13" t="n">
+      <c r="L22" s="9" t="n">
         <v>93.93000000000001</v>
       </c>
-      <c r="M22" s="13" t="n">
+      <c r="M22" s="9" t="n">
         <v>95.51000000000001</v>
       </c>
-      <c r="N22" s="13" t="n">
+      <c r="N22" s="9" t="n">
         <v>94.7</v>
       </c>
-      <c r="O22" s="12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P22" s="13" t="n">
+      <c r="O22" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P22" s="9" t="n">
         <v>96.44</v>
       </c>
-      <c r="Q22" s="13" t="n">
+      <c r="Q22" s="9" t="n">
         <v>96.55</v>
       </c>
-      <c r="R22" s="13" t="n">
+      <c r="R22" s="9" t="n">
         <v>96.68000000000001</v>
       </c>
-      <c r="S22" s="13" t="n">
+      <c r="S22" s="9" t="n">
         <v>95.59</v>
       </c>
-      <c r="T22" s="13" t="n">
+      <c r="T22" s="9" t="n">
         <v>95.16</v>
       </c>
-      <c r="U22" s="12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="V22" s="12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="W22" s="12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="X22" s="13" t="n">
+      <c r="U22" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="V22" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="W22" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="X22" s="9" t="n">
         <v>96.52</v>
       </c>
-      <c r="Y22" s="13" t="n">
+      <c r="Y22" s="9" t="n">
         <v>96.81</v>
       </c>
-      <c r="Z22" s="12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AA22" s="13" t="n">
+      <c r="Z22" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AA22" s="9" t="n">
         <v>96.84</v>
       </c>
-      <c r="AB22" s="13" t="n">
+      <c r="AB22" s="9" t="n">
         <v>97.22</v>
       </c>
-      <c r="AC22" s="13" t="n">
+      <c r="AC22" s="9" t="n">
         <v>96.81</v>
       </c>
-      <c r="AD22" s="12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AE22" s="13" t="n">
+      <c r="AD22" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AE22" s="9" t="n">
         <v>96.48</v>
       </c>
-      <c r="AF22" s="13" t="n">
+      <c r="AF22" s="9" t="n">
         <v>97.16</v>
       </c>
-      <c r="AG22" s="13" t="n">
+      <c r="AG22" s="9" t="n">
         <v>96.37</v>
       </c>
-      <c r="AH22" s="12" t="n">
+      <c r="AH22" s="9" t="n">
         <v>96.06</v>
       </c>
-      <c r="AI22" s="12" t="n">
+      <c r="AI22" s="9" t="n">
         <v>127.1</v>
       </c>
-      <c r="AJ22" s="12" t="inlineStr"/>
-      <c r="AK22" s="14" t="inlineStr"/>
+      <c r="AJ22" s="9" t="inlineStr"/>
+      <c r="AK22" s="10" t="inlineStr"/>
     </row>
     <row r="23"/>
     <row r="24"/>
@@ -2640,7 +2607,7 @@
     <row r="31">
       <c r="A31" s="1" t="inlineStr">
         <is>
-          <t>FECHA PRESENTACIÓN: 28/08/2025</t>
+          <t>FECHA PRESENTACIÓN: 27/08/2025</t>
         </is>
       </c>
     </row>
@@ -2766,7 +2733,7 @@
           <t>OBSERVACIONES</t>
         </is>
       </c>
-      <c r="AK32" s="15" t="n"/>
+      <c r="AK32" s="11" t="n"/>
     </row>
     <row r="33">
       <c r="A33" s="5" t="inlineStr">
@@ -2817,16 +2784,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="K33" s="7" t="n">
+      <c r="K33" s="6" t="n">
         <v>57.55</v>
       </c>
-      <c r="L33" s="7" t="n">
+      <c r="L33" s="6" t="n">
         <v>57.75</v>
       </c>
-      <c r="M33" s="7" t="n">
+      <c r="M33" s="6" t="n">
         <v>57.28</v>
       </c>
-      <c r="N33" s="7" t="n">
+      <c r="N33" s="6" t="n">
         <v>57.49</v>
       </c>
       <c r="O33" s="6" t="inlineStr">
@@ -2834,19 +2801,19 @@
           <t>-</t>
         </is>
       </c>
-      <c r="P33" s="7" t="n">
+      <c r="P33" s="6" t="n">
         <v>56.76</v>
       </c>
-      <c r="Q33" s="7" t="n">
+      <c r="Q33" s="6" t="n">
         <v>55.79</v>
       </c>
-      <c r="R33" s="7" t="n">
+      <c r="R33" s="6" t="n">
         <v>54.35</v>
       </c>
-      <c r="S33" s="7" t="n">
+      <c r="S33" s="6" t="n">
         <v>56.31</v>
       </c>
-      <c r="T33" s="7" t="n">
+      <c r="T33" s="6" t="n">
         <v>55.88</v>
       </c>
       <c r="U33" s="6" t="inlineStr">
@@ -2864,10 +2831,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="X33" s="7" t="n">
+      <c r="X33" s="6" t="n">
         <v>55.13</v>
       </c>
-      <c r="Y33" s="7" t="n">
+      <c r="Y33" s="6" t="n">
         <v>54.41</v>
       </c>
       <c r="Z33" s="6" t="inlineStr">
@@ -2875,13 +2842,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="AA33" s="7" t="n">
+      <c r="AA33" s="6" t="n">
         <v>55</v>
       </c>
-      <c r="AB33" s="7" t="n">
+      <c r="AB33" s="6" t="n">
         <v>55.06</v>
       </c>
-      <c r="AC33" s="7" t="n">
+      <c r="AC33" s="6" t="n">
         <v>54.2</v>
       </c>
       <c r="AD33" s="6" t="inlineStr">
@@ -2889,13 +2856,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="AE33" s="7" t="n">
+      <c r="AE33" s="6" t="n">
         <v>54.14</v>
       </c>
-      <c r="AF33" s="7" t="n">
+      <c r="AF33" s="6" t="n">
         <v>54.39</v>
       </c>
-      <c r="AG33" s="7" t="n">
+      <c r="AG33" s="6" t="n">
         <v>54.92</v>
       </c>
       <c r="AH33" s="6" t="n">
@@ -2903,7 +2870,7 @@
       </c>
       <c r="AI33" s="6" t="inlineStr"/>
       <c r="AJ33" s="6" t="inlineStr"/>
-      <c r="AK33" s="16" t="n"/>
+      <c r="AK33" s="12" t="n"/>
     </row>
     <row r="34">
       <c r="A34" s="5" t="inlineStr">
@@ -2954,16 +2921,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="K34" s="9" t="n">
+      <c r="K34" s="6" t="n">
         <v>38.7</v>
       </c>
-      <c r="L34" s="9" t="n">
+      <c r="L34" s="6" t="n">
         <v>40.12</v>
       </c>
-      <c r="M34" s="9" t="n">
+      <c r="M34" s="6" t="n">
         <v>39.56</v>
       </c>
-      <c r="N34" s="9" t="n">
+      <c r="N34" s="6" t="n">
         <v>38.39</v>
       </c>
       <c r="O34" s="6" t="inlineStr">
@@ -2971,19 +2938,19 @@
           <t>-</t>
         </is>
       </c>
-      <c r="P34" s="9" t="n">
+      <c r="P34" s="6" t="n">
         <v>39.4</v>
       </c>
-      <c r="Q34" s="9" t="n">
+      <c r="Q34" s="6" t="n">
         <v>38.11</v>
       </c>
-      <c r="R34" s="9" t="n">
+      <c r="R34" s="6" t="n">
         <v>39.07</v>
       </c>
-      <c r="S34" s="9" t="n">
+      <c r="S34" s="6" t="n">
         <v>38.31</v>
       </c>
-      <c r="T34" s="9" t="n">
+      <c r="T34" s="6" t="n">
         <v>38.94</v>
       </c>
       <c r="U34" s="6" t="inlineStr">
@@ -3001,10 +2968,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="X34" s="9" t="n">
+      <c r="X34" s="6" t="n">
         <v>39.57</v>
       </c>
-      <c r="Y34" s="9" t="n">
+      <c r="Y34" s="6" t="n">
         <v>38.75</v>
       </c>
       <c r="Z34" s="6" t="inlineStr">
@@ -3012,13 +2979,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="AA34" s="9" t="n">
+      <c r="AA34" s="6" t="n">
         <v>39.83</v>
       </c>
-      <c r="AB34" s="9" t="n">
+      <c r="AB34" s="6" t="n">
         <v>39.13</v>
       </c>
-      <c r="AC34" s="9" t="n">
+      <c r="AC34" s="6" t="n">
         <v>38.66</v>
       </c>
       <c r="AD34" s="6" t="inlineStr">
@@ -3026,13 +2993,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="AE34" s="9" t="n">
+      <c r="AE34" s="6" t="n">
         <v>40.58</v>
       </c>
-      <c r="AF34" s="9" t="n">
+      <c r="AF34" s="6" t="n">
         <v>40.04</v>
       </c>
-      <c r="AG34" s="9" t="n">
+      <c r="AG34" s="6" t="n">
         <v>39.34</v>
       </c>
       <c r="AH34" s="6" t="n">
@@ -3040,7 +3007,7 @@
       </c>
       <c r="AI34" s="6" t="inlineStr"/>
       <c r="AJ34" s="6" t="inlineStr"/>
-      <c r="AK34" s="16" t="n"/>
+      <c r="AK34" s="12" t="n"/>
     </row>
     <row r="35">
       <c r="A35" s="5" t="inlineStr">
@@ -3091,16 +3058,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="K35" s="9" t="n">
+      <c r="K35" s="6" t="n">
         <v>42.34</v>
       </c>
-      <c r="L35" s="9" t="n">
+      <c r="L35" s="6" t="n">
         <v>40.07</v>
       </c>
-      <c r="M35" s="9" t="n">
+      <c r="M35" s="6" t="n">
         <v>41.68</v>
       </c>
-      <c r="N35" s="9" t="n">
+      <c r="N35" s="6" t="n">
         <v>39.71</v>
       </c>
       <c r="O35" s="6" t="inlineStr">
@@ -3108,19 +3075,19 @@
           <t>-</t>
         </is>
       </c>
-      <c r="P35" s="9" t="n">
+      <c r="P35" s="6" t="n">
         <v>42.02</v>
       </c>
-      <c r="Q35" s="9" t="n">
+      <c r="Q35" s="6" t="n">
         <v>40.85</v>
       </c>
-      <c r="R35" s="9" t="n">
+      <c r="R35" s="6" t="n">
         <v>42.52</v>
       </c>
-      <c r="S35" s="9" t="n">
+      <c r="S35" s="6" t="n">
         <v>40.18</v>
       </c>
-      <c r="T35" s="9" t="n">
+      <c r="T35" s="6" t="n">
         <v>42.59</v>
       </c>
       <c r="U35" s="6" t="inlineStr">
@@ -3138,10 +3105,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="X35" s="9" t="n">
+      <c r="X35" s="6" t="n">
         <v>40.06</v>
       </c>
-      <c r="Y35" s="9" t="n">
+      <c r="Y35" s="6" t="n">
         <v>37.89</v>
       </c>
       <c r="Z35" s="6" t="inlineStr">
@@ -3149,13 +3116,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="AA35" s="9" t="n">
+      <c r="AA35" s="6" t="n">
         <v>41.15</v>
       </c>
-      <c r="AB35" s="9" t="n">
+      <c r="AB35" s="6" t="n">
         <v>38.92</v>
       </c>
-      <c r="AC35" s="9" t="n">
+      <c r="AC35" s="6" t="n">
         <v>39.38</v>
       </c>
       <c r="AD35" s="6" t="inlineStr">
@@ -3163,13 +3130,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="AE35" s="9" t="n">
+      <c r="AE35" s="6" t="n">
         <v>40.89</v>
       </c>
-      <c r="AF35" s="9" t="n">
+      <c r="AF35" s="6" t="n">
         <v>41.14</v>
       </c>
-      <c r="AG35" s="9" t="n">
+      <c r="AG35" s="6" t="n">
         <v>41.74</v>
       </c>
       <c r="AH35" s="6" t="n">
@@ -3177,7 +3144,7 @@
       </c>
       <c r="AI35" s="6" t="inlineStr"/>
       <c r="AJ35" s="6" t="inlineStr"/>
-      <c r="AK35" s="16" t="n"/>
+      <c r="AK35" s="12" t="n"/>
     </row>
     <row r="36">
       <c r="A36" s="5" t="inlineStr">
@@ -3228,16 +3195,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="K36" s="9" t="n">
+      <c r="K36" s="6" t="n">
         <v>32.85</v>
       </c>
-      <c r="L36" s="9" t="n">
+      <c r="L36" s="6" t="n">
         <v>34.68</v>
       </c>
-      <c r="M36" s="9" t="n">
+      <c r="M36" s="6" t="n">
         <v>34.93</v>
       </c>
-      <c r="N36" s="9" t="n">
+      <c r="N36" s="6" t="n">
         <v>32.62</v>
       </c>
       <c r="O36" s="6" t="inlineStr">
@@ -3245,19 +3212,19 @@
           <t>-</t>
         </is>
       </c>
-      <c r="P36" s="9" t="n">
+      <c r="P36" s="6" t="n">
         <v>35.57</v>
       </c>
-      <c r="Q36" s="9" t="n">
+      <c r="Q36" s="6" t="n">
         <v>33.22</v>
       </c>
-      <c r="R36" s="9" t="n">
+      <c r="R36" s="6" t="n">
         <v>33.28</v>
       </c>
-      <c r="S36" s="9" t="n">
+      <c r="S36" s="6" t="n">
         <v>33.37</v>
       </c>
-      <c r="T36" s="9" t="n">
+      <c r="T36" s="6" t="n">
         <v>33.94</v>
       </c>
       <c r="U36" s="6" t="inlineStr">
@@ -3275,10 +3242,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="X36" s="9" t="n">
+      <c r="X36" s="6" t="n">
         <v>33.7</v>
       </c>
-      <c r="Y36" s="9" t="n">
+      <c r="Y36" s="6" t="n">
         <v>32.97</v>
       </c>
       <c r="Z36" s="6" t="inlineStr">
@@ -3286,13 +3253,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="AA36" s="9" t="n">
+      <c r="AA36" s="6" t="n">
         <v>33.07</v>
       </c>
-      <c r="AB36" s="9" t="n">
+      <c r="AB36" s="6" t="n">
         <v>33.43</v>
       </c>
-      <c r="AC36" s="9" t="n">
+      <c r="AC36" s="6" t="n">
         <v>33.04</v>
       </c>
       <c r="AD36" s="6" t="inlineStr">
@@ -3300,13 +3267,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="AE36" s="9" t="n">
+      <c r="AE36" s="6" t="n">
         <v>33.12</v>
       </c>
-      <c r="AF36" s="9" t="n">
+      <c r="AF36" s="6" t="n">
         <v>35.94</v>
       </c>
-      <c r="AG36" s="9" t="n">
+      <c r="AG36" s="6" t="n">
         <v>33.06</v>
       </c>
       <c r="AH36" s="6" t="n">
@@ -3314,7 +3281,7 @@
       </c>
       <c r="AI36" s="6" t="inlineStr"/>
       <c r="AJ36" s="6" t="inlineStr"/>
-      <c r="AK36" s="16" t="n"/>
+      <c r="AK36" s="12" t="n"/>
     </row>
     <row r="37">
       <c r="A37" s="5" t="inlineStr">
@@ -3365,16 +3332,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="K37" s="9" t="n">
+      <c r="K37" s="6" t="n">
         <v>31.68</v>
       </c>
-      <c r="L37" s="9" t="n">
+      <c r="L37" s="6" t="n">
         <v>34.34</v>
       </c>
-      <c r="M37" s="9" t="n">
+      <c r="M37" s="6" t="n">
         <v>34.12</v>
       </c>
-      <c r="N37" s="9" t="n">
+      <c r="N37" s="6" t="n">
         <v>31.96</v>
       </c>
       <c r="O37" s="6" t="inlineStr">
@@ -3382,19 +3349,19 @@
           <t>-</t>
         </is>
       </c>
-      <c r="P37" s="9" t="n">
+      <c r="P37" s="6" t="n">
         <v>32.38</v>
       </c>
-      <c r="Q37" s="9" t="n">
+      <c r="Q37" s="6" t="n">
         <v>33.12</v>
       </c>
-      <c r="R37" s="9" t="n">
+      <c r="R37" s="6" t="n">
         <v>33.15</v>
       </c>
-      <c r="S37" s="9" t="n">
+      <c r="S37" s="6" t="n">
         <v>31.32</v>
       </c>
-      <c r="T37" s="9" t="n">
+      <c r="T37" s="6" t="n">
         <v>31.71</v>
       </c>
       <c r="U37" s="6" t="inlineStr">
@@ -3412,10 +3379,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="X37" s="9" t="n">
+      <c r="X37" s="6" t="n">
         <v>32.34</v>
       </c>
-      <c r="Y37" s="9" t="n">
+      <c r="Y37" s="6" t="n">
         <v>32.37</v>
       </c>
       <c r="Z37" s="6" t="inlineStr">
@@ -3423,13 +3390,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="AA37" s="9" t="n">
+      <c r="AA37" s="6" t="n">
         <v>32.65</v>
       </c>
-      <c r="AB37" s="9" t="n">
+      <c r="AB37" s="6" t="n">
         <v>33.45</v>
       </c>
-      <c r="AC37" s="9" t="n">
+      <c r="AC37" s="6" t="n">
         <v>31.78</v>
       </c>
       <c r="AD37" s="6" t="inlineStr">
@@ -3437,13 +3404,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="AE37" s="9" t="n">
+      <c r="AE37" s="6" t="n">
         <v>31.59</v>
       </c>
-      <c r="AF37" s="9" t="n">
+      <c r="AF37" s="6" t="n">
         <v>33.82</v>
       </c>
-      <c r="AG37" s="9" t="n">
+      <c r="AG37" s="6" t="n">
         <v>31.83</v>
       </c>
       <c r="AH37" s="6" t="n">
@@ -3451,7 +3418,7 @@
       </c>
       <c r="AI37" s="6" t="inlineStr"/>
       <c r="AJ37" s="6" t="inlineStr"/>
-      <c r="AK37" s="16" t="n"/>
+      <c r="AK37" s="12" t="n"/>
     </row>
     <row r="38">
       <c r="A38" s="5" t="inlineStr">
@@ -3502,16 +3469,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="K38" s="9" t="n">
+      <c r="K38" s="6" t="n">
         <v>30.38</v>
       </c>
-      <c r="L38" s="9" t="n">
+      <c r="L38" s="6" t="n">
         <v>33.09</v>
       </c>
-      <c r="M38" s="9" t="n">
+      <c r="M38" s="6" t="n">
         <v>32.21</v>
       </c>
-      <c r="N38" s="9" t="n">
+      <c r="N38" s="6" t="n">
         <v>30.17</v>
       </c>
       <c r="O38" s="6" t="inlineStr">
@@ -3519,19 +3486,19 @@
           <t>-</t>
         </is>
       </c>
-      <c r="P38" s="9" t="n">
+      <c r="P38" s="6" t="n">
         <v>32.04</v>
       </c>
-      <c r="Q38" s="9" t="n">
+      <c r="Q38" s="6" t="n">
         <v>30.86</v>
       </c>
-      <c r="R38" s="9" t="n">
+      <c r="R38" s="6" t="n">
         <v>30.69</v>
       </c>
-      <c r="S38" s="9" t="n">
+      <c r="S38" s="6" t="n">
         <v>30.45</v>
       </c>
-      <c r="T38" s="9" t="n">
+      <c r="T38" s="6" t="n">
         <v>30.94</v>
       </c>
       <c r="U38" s="6" t="inlineStr">
@@ -3549,10 +3516,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="X38" s="9" t="n">
+      <c r="X38" s="6" t="n">
         <v>31.18</v>
       </c>
-      <c r="Y38" s="9" t="n">
+      <c r="Y38" s="6" t="n">
         <v>30.95</v>
       </c>
       <c r="Z38" s="6" t="inlineStr">
@@ -3560,13 +3527,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="AA38" s="9" t="n">
+      <c r="AA38" s="6" t="n">
         <v>30.83</v>
       </c>
-      <c r="AB38" s="9" t="n">
+      <c r="AB38" s="6" t="n">
         <v>31.03</v>
       </c>
-      <c r="AC38" s="9" t="n">
+      <c r="AC38" s="6" t="n">
         <v>30.71</v>
       </c>
       <c r="AD38" s="6" t="inlineStr">
@@ -3574,13 +3541,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="AE38" s="9" t="n">
+      <c r="AE38" s="6" t="n">
         <v>30.44</v>
       </c>
-      <c r="AF38" s="9" t="n">
+      <c r="AF38" s="6" t="n">
         <v>33.05</v>
       </c>
-      <c r="AG38" s="9" t="n">
+      <c r="AG38" s="6" t="n">
         <v>30.7</v>
       </c>
       <c r="AH38" s="6" t="n">
@@ -3588,7 +3555,7 @@
       </c>
       <c r="AI38" s="6" t="inlineStr"/>
       <c r="AJ38" s="6" t="inlineStr"/>
-      <c r="AK38" s="16" t="n"/>
+      <c r="AK38" s="12" t="n"/>
     </row>
     <row r="39">
       <c r="A39" s="5" t="inlineStr">
@@ -3639,16 +3606,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="K39" s="9" t="n">
+      <c r="K39" s="6" t="n">
         <v>29.23</v>
       </c>
-      <c r="L39" s="9" t="n">
+      <c r="L39" s="6" t="n">
         <v>29.27</v>
       </c>
-      <c r="M39" s="9" t="n">
+      <c r="M39" s="6" t="n">
         <v>29.72</v>
       </c>
-      <c r="N39" s="9" t="n">
+      <c r="N39" s="6" t="n">
         <v>28.44</v>
       </c>
       <c r="O39" s="6" t="inlineStr">
@@ -3656,19 +3623,19 @@
           <t>-</t>
         </is>
       </c>
-      <c r="P39" s="9" t="n">
+      <c r="P39" s="6" t="n">
         <v>29.66</v>
       </c>
-      <c r="Q39" s="9" t="n">
+      <c r="Q39" s="6" t="n">
         <v>28.68</v>
       </c>
-      <c r="R39" s="9" t="n">
+      <c r="R39" s="6" t="n">
         <v>29.01</v>
       </c>
-      <c r="S39" s="9" t="n">
+      <c r="S39" s="6" t="n">
         <v>28.72</v>
       </c>
-      <c r="T39" s="9" t="n">
+      <c r="T39" s="6" t="n">
         <v>29.25</v>
       </c>
       <c r="U39" s="6" t="inlineStr">
@@ -3686,10 +3653,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="X39" s="9" t="n">
+      <c r="X39" s="6" t="n">
         <v>29.75</v>
       </c>
-      <c r="Y39" s="9" t="n">
+      <c r="Y39" s="6" t="n">
         <v>29.47</v>
       </c>
       <c r="Z39" s="6" t="inlineStr">
@@ -3697,13 +3664,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="AA39" s="9" t="n">
+      <c r="AA39" s="6" t="n">
         <v>29.05</v>
       </c>
-      <c r="AB39" s="9" t="n">
+      <c r="AB39" s="6" t="n">
         <v>29.35</v>
       </c>
-      <c r="AC39" s="9" t="n">
+      <c r="AC39" s="6" t="n">
         <v>28.38</v>
       </c>
       <c r="AD39" s="6" t="inlineStr">
@@ -3711,13 +3678,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="AE39" s="9" t="n">
+      <c r="AE39" s="6" t="n">
         <v>29.33</v>
       </c>
-      <c r="AF39" s="9" t="n">
+      <c r="AF39" s="6" t="n">
         <v>29.64</v>
       </c>
-      <c r="AG39" s="9" t="n">
+      <c r="AG39" s="6" t="n">
         <v>29.19</v>
       </c>
       <c r="AH39" s="6" t="n">
@@ -3725,7 +3692,7 @@
       </c>
       <c r="AI39" s="6" t="inlineStr"/>
       <c r="AJ39" s="6" t="inlineStr"/>
-      <c r="AK39" s="16" t="n"/>
+      <c r="AK39" s="12" t="n"/>
     </row>
     <row r="40">
       <c r="A40" s="5" t="inlineStr">
@@ -3776,16 +3743,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="K40" s="9" t="n">
+      <c r="K40" s="6" t="n">
         <v>26.49</v>
       </c>
-      <c r="L40" s="9" t="n">
+      <c r="L40" s="6" t="n">
         <v>26.61</v>
       </c>
-      <c r="M40" s="9" t="n">
+      <c r="M40" s="6" t="n">
         <v>26.76</v>
       </c>
-      <c r="N40" s="9" t="n">
+      <c r="N40" s="6" t="n">
         <v>26.86</v>
       </c>
       <c r="O40" s="6" t="inlineStr">
@@ -3793,19 +3760,19 @@
           <t>-</t>
         </is>
       </c>
-      <c r="P40" s="9" t="n">
+      <c r="P40" s="6" t="n">
         <v>26.77</v>
       </c>
-      <c r="Q40" s="9" t="n">
+      <c r="Q40" s="6" t="n">
         <v>26.84</v>
       </c>
-      <c r="R40" s="9" t="n">
+      <c r="R40" s="6" t="n">
         <v>27.65</v>
       </c>
-      <c r="S40" s="9" t="n">
+      <c r="S40" s="6" t="n">
         <v>26.75</v>
       </c>
-      <c r="T40" s="9" t="n">
+      <c r="T40" s="6" t="n">
         <v>26.91</v>
       </c>
       <c r="U40" s="6" t="inlineStr">
@@ -3823,10 +3790,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="X40" s="9" t="n">
+      <c r="X40" s="6" t="n">
         <v>26.82</v>
       </c>
-      <c r="Y40" s="9" t="n">
+      <c r="Y40" s="6" t="n">
         <v>26.87</v>
       </c>
       <c r="Z40" s="6" t="inlineStr">
@@ -3834,13 +3801,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="AA40" s="9" t="n">
+      <c r="AA40" s="6" t="n">
         <v>26.65</v>
       </c>
-      <c r="AB40" s="9" t="n">
+      <c r="AB40" s="6" t="n">
         <v>26.82</v>
       </c>
-      <c r="AC40" s="9" t="n">
+      <c r="AC40" s="6" t="n">
         <v>26.56</v>
       </c>
       <c r="AD40" s="6" t="inlineStr">
@@ -3848,13 +3815,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="AE40" s="9" t="n">
+      <c r="AE40" s="6" t="n">
         <v>26.93</v>
       </c>
-      <c r="AF40" s="9" t="n">
+      <c r="AF40" s="6" t="n">
         <v>26.84</v>
       </c>
-      <c r="AG40" s="9" t="n">
+      <c r="AG40" s="6" t="n">
         <v>26.69</v>
       </c>
       <c r="AH40" s="6" t="n">
@@ -3862,7 +3829,7 @@
       </c>
       <c r="AI40" s="6" t="inlineStr"/>
       <c r="AJ40" s="6" t="inlineStr"/>
-      <c r="AK40" s="16" t="n"/>
+      <c r="AK40" s="12" t="n"/>
     </row>
     <row r="41">
       <c r="A41" s="5" t="inlineStr">
@@ -3913,16 +3880,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="K41" s="9" t="n">
+      <c r="K41" s="6" t="n">
         <v>26.63</v>
       </c>
-      <c r="L41" s="9" t="n">
+      <c r="L41" s="6" t="n">
         <v>26.96</v>
       </c>
-      <c r="M41" s="9" t="n">
+      <c r="M41" s="6" t="n">
         <v>26.84</v>
       </c>
-      <c r="N41" s="9" t="n">
+      <c r="N41" s="6" t="n">
         <v>26.93</v>
       </c>
       <c r="O41" s="6" t="inlineStr">
@@ -3930,19 +3897,19 @@
           <t>-</t>
         </is>
       </c>
-      <c r="P41" s="9" t="n">
+      <c r="P41" s="6" t="n">
         <v>27.04</v>
       </c>
-      <c r="Q41" s="9" t="n">
+      <c r="Q41" s="6" t="n">
         <v>26.67</v>
       </c>
-      <c r="R41" s="9" t="n">
+      <c r="R41" s="6" t="n">
         <v>26.77</v>
       </c>
-      <c r="S41" s="9" t="n">
+      <c r="S41" s="6" t="n">
         <v>26.6</v>
       </c>
-      <c r="T41" s="9" t="n">
+      <c r="T41" s="6" t="n">
         <v>27.2</v>
       </c>
       <c r="U41" s="6" t="inlineStr">
@@ -3960,10 +3927,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="X41" s="9" t="n">
+      <c r="X41" s="6" t="n">
         <v>26.92</v>
       </c>
-      <c r="Y41" s="9" t="n">
+      <c r="Y41" s="6" t="n">
         <v>27.06</v>
       </c>
       <c r="Z41" s="6" t="inlineStr">
@@ -3971,13 +3938,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="AA41" s="9" t="n">
+      <c r="AA41" s="6" t="n">
         <v>26.83</v>
       </c>
-      <c r="AB41" s="9" t="n">
+      <c r="AB41" s="6" t="n">
         <v>26.85</v>
       </c>
-      <c r="AC41" s="9" t="n">
+      <c r="AC41" s="6" t="n">
         <v>26.68</v>
       </c>
       <c r="AD41" s="6" t="inlineStr">
@@ -3985,13 +3952,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="AE41" s="9" t="n">
+      <c r="AE41" s="6" t="n">
         <v>27.21</v>
       </c>
-      <c r="AF41" s="9" t="n">
+      <c r="AF41" s="6" t="n">
         <v>27.19</v>
       </c>
-      <c r="AG41" s="9" t="n">
+      <c r="AG41" s="6" t="n">
         <v>26.73</v>
       </c>
       <c r="AH41" s="6" t="n">
@@ -3999,7 +3966,7 @@
       </c>
       <c r="AI41" s="6" t="inlineStr"/>
       <c r="AJ41" s="6" t="inlineStr"/>
-      <c r="AK41" s="16" t="n"/>
+      <c r="AK41" s="12" t="n"/>
     </row>
     <row r="42">
       <c r="A42" s="5" t="inlineStr">
@@ -4050,16 +4017,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="K42" s="9" t="n">
+      <c r="K42" s="6" t="n">
         <v>27.35</v>
       </c>
-      <c r="L42" s="9" t="n">
+      <c r="L42" s="6" t="n">
         <v>27.68</v>
       </c>
-      <c r="M42" s="9" t="n">
+      <c r="M42" s="6" t="n">
         <v>26.97</v>
       </c>
-      <c r="N42" s="9" t="n">
+      <c r="N42" s="6" t="n">
         <v>27.55</v>
       </c>
       <c r="O42" s="6" t="inlineStr">
@@ -4067,19 +4034,19 @@
           <t>-</t>
         </is>
       </c>
-      <c r="P42" s="9" t="n">
+      <c r="P42" s="6" t="n">
         <v>28.86</v>
       </c>
-      <c r="Q42" s="9" t="n">
+      <c r="Q42" s="6" t="n">
         <v>27.39</v>
       </c>
-      <c r="R42" s="9" t="n">
+      <c r="R42" s="6" t="n">
         <v>29.27</v>
       </c>
-      <c r="S42" s="9" t="n">
+      <c r="S42" s="6" t="n">
         <v>27.56</v>
       </c>
-      <c r="T42" s="9" t="n">
+      <c r="T42" s="6" t="n">
         <v>28.35</v>
       </c>
       <c r="U42" s="6" t="inlineStr">
@@ -4097,10 +4064,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="X42" s="9" t="n">
+      <c r="X42" s="6" t="n">
         <v>27.35</v>
       </c>
-      <c r="Y42" s="9" t="n">
+      <c r="Y42" s="6" t="n">
         <v>27.39</v>
       </c>
       <c r="Z42" s="6" t="inlineStr">
@@ -4108,13 +4075,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="AA42" s="9" t="n">
+      <c r="AA42" s="6" t="n">
         <v>27.07</v>
       </c>
-      <c r="AB42" s="9" t="n">
+      <c r="AB42" s="6" t="n">
         <v>27.45</v>
       </c>
-      <c r="AC42" s="9" t="n">
+      <c r="AC42" s="6" t="n">
         <v>27.13</v>
       </c>
       <c r="AD42" s="6" t="inlineStr">
@@ -4122,13 +4089,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="AE42" s="9" t="n">
+      <c r="AE42" s="6" t="n">
         <v>27.25</v>
       </c>
-      <c r="AF42" s="9" t="n">
+      <c r="AF42" s="6" t="n">
         <v>27.71</v>
       </c>
-      <c r="AG42" s="9" t="n">
+      <c r="AG42" s="6" t="n">
         <v>27.53</v>
       </c>
       <c r="AH42" s="6" t="n">
@@ -4136,144 +4103,144 @@
       </c>
       <c r="AI42" s="6" t="inlineStr"/>
       <c r="AJ42" s="6" t="inlineStr"/>
-      <c r="AK42" s="16" t="n"/>
+      <c r="AK42" s="12" t="n"/>
     </row>
     <row r="43">
-      <c r="A43" s="11" t="inlineStr">
+      <c r="A43" s="8" t="inlineStr">
         <is>
           <t>TELECIUDADANA</t>
         </is>
       </c>
-      <c r="B43" s="12" t="n">
+      <c r="B43" s="9" t="n">
         <v>681.25</v>
       </c>
-      <c r="C43" s="12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D43" s="12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E43" s="12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F43" s="12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G43" s="12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H43" s="12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I43" s="12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J43" s="12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K43" s="17" t="n">
+      <c r="C43" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D43" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E43" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F43" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G43" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H43" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I43" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J43" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K43" s="9" t="n">
         <v>27.51</v>
       </c>
-      <c r="L43" s="17" t="n">
+      <c r="L43" s="9" t="n">
         <v>27.51</v>
       </c>
-      <c r="M43" s="17" t="n">
+      <c r="M43" s="9" t="n">
         <v>27.42</v>
       </c>
-      <c r="N43" s="17" t="n">
+      <c r="N43" s="9" t="n">
         <v>27.63</v>
       </c>
-      <c r="O43" s="12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P43" s="17" t="n">
+      <c r="O43" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P43" s="9" t="n">
         <v>27.18</v>
       </c>
-      <c r="Q43" s="17" t="n">
+      <c r="Q43" s="9" t="n">
         <v>27.42</v>
       </c>
-      <c r="R43" s="17" t="n">
+      <c r="R43" s="9" t="n">
         <v>29.01</v>
       </c>
-      <c r="S43" s="17" t="n">
+      <c r="S43" s="9" t="n">
         <v>27.59</v>
       </c>
-      <c r="T43" s="17" t="n">
+      <c r="T43" s="9" t="n">
         <v>27.61</v>
       </c>
-      <c r="U43" s="12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="V43" s="12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="W43" s="12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="X43" s="17" t="n">
+      <c r="U43" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="V43" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="W43" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="X43" s="9" t="n">
         <v>27.49</v>
       </c>
-      <c r="Y43" s="17" t="n">
+      <c r="Y43" s="9" t="n">
         <v>27.51</v>
       </c>
-      <c r="Z43" s="12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AA43" s="17" t="n">
+      <c r="Z43" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AA43" s="9" t="n">
         <v>27.53</v>
       </c>
-      <c r="AB43" s="17" t="n">
+      <c r="AB43" s="9" t="n">
         <v>27.47</v>
       </c>
-      <c r="AC43" s="17" t="n">
+      <c r="AC43" s="9" t="n">
         <v>27.33</v>
       </c>
-      <c r="AD43" s="12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AE43" s="17" t="n">
+      <c r="AD43" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AE43" s="9" t="n">
         <v>27.68</v>
       </c>
-      <c r="AF43" s="17" t="n">
+      <c r="AF43" s="9" t="n">
         <v>27.72</v>
       </c>
-      <c r="AG43" s="17" t="n">
+      <c r="AG43" s="9" t="n">
         <v>27.44</v>
       </c>
-      <c r="AH43" s="12" t="n">
+      <c r="AH43" s="9" t="n">
         <v>27.59</v>
       </c>
-      <c r="AI43" s="12" t="inlineStr"/>
-      <c r="AJ43" s="12" t="inlineStr"/>
-      <c r="AK43" s="18" t="n"/>
+      <c r="AI43" s="9" t="inlineStr"/>
+      <c r="AJ43" s="9" t="inlineStr"/>
+      <c r="AK43" s="13" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="28">

--- a/ReportesUnificados/zamora_ReporteUnificado.xlsx
+++ b/ReportesUnificados/zamora_ReporteUnificado.xlsx
@@ -30,7 +30,7 @@
       <sz val="12"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="7">
     <fill>
       <patternFill/>
     </fill>
@@ -53,6 +53,18 @@
       <patternFill patternType="solid">
         <fgColor rgb="FFFD9BCB"/>
         <bgColor rgb="FFFD9BCB"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFF0000"/>
+        <bgColor rgb="FFFF0000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFF6666"/>
+        <bgColor rgb="FFFF6666"/>
       </patternFill>
     </fill>
   </fills>
@@ -171,7 +183,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -200,7 +212,13 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -210,6 +228,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -1058,11 +1079,11 @@
       <c r="AH11" s="6" t="n">
         <v>44.5</v>
       </c>
-      <c r="AI11" s="6" t="n">
+      <c r="AI11" s="10" t="n">
         <v>485.74</v>
       </c>
       <c r="AJ11" s="6" t="inlineStr"/>
-      <c r="AK11" s="10" t="inlineStr"/>
+      <c r="AK11" s="11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
@@ -1194,14 +1215,14 @@
       <c r="AG12" s="9" t="n">
         <v>41.96</v>
       </c>
-      <c r="AH12" s="6" t="n">
+      <c r="AH12" s="12" t="n">
         <v>73.26000000000001</v>
       </c>
       <c r="AI12" s="6" t="n">
         <v>101.16</v>
       </c>
       <c r="AJ12" s="6" t="inlineStr"/>
-      <c r="AK12" s="10" t="inlineStr"/>
+      <c r="AK12" s="11" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
@@ -1333,14 +1354,14 @@
       <c r="AG13" s="7" t="n">
         <v>100.99</v>
       </c>
-      <c r="AH13" s="6" t="n">
+      <c r="AH13" s="12" t="n">
         <v>101.89</v>
       </c>
       <c r="AI13" s="6" t="n">
         <v>104.99</v>
       </c>
       <c r="AJ13" s="6" t="inlineStr"/>
-      <c r="AK13" s="10" t="inlineStr"/>
+      <c r="AK13" s="11" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
@@ -1472,14 +1493,14 @@
       <c r="AG14" s="7" t="n">
         <v>90.73999999999999</v>
       </c>
-      <c r="AH14" s="6" t="n">
+      <c r="AH14" s="12" t="n">
         <v>90.89</v>
       </c>
       <c r="AI14" s="6" t="n">
         <v>119.83</v>
       </c>
       <c r="AJ14" s="6" t="inlineStr"/>
-      <c r="AK14" s="10" t="inlineStr"/>
+      <c r="AK14" s="11" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
@@ -1611,14 +1632,14 @@
       <c r="AG15" s="7" t="n">
         <v>74.22</v>
       </c>
-      <c r="AH15" s="6" t="n">
+      <c r="AH15" s="12" t="n">
         <v>74.42</v>
       </c>
       <c r="AI15" s="6" t="n">
         <v>156.6</v>
       </c>
       <c r="AJ15" s="6" t="inlineStr"/>
-      <c r="AK15" s="10" t="inlineStr"/>
+      <c r="AK15" s="11" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
@@ -1750,14 +1771,14 @@
       <c r="AG16" s="7" t="n">
         <v>88.94</v>
       </c>
-      <c r="AH16" s="6" t="n">
+      <c r="AH16" s="12" t="n">
         <v>89.45999999999999</v>
       </c>
       <c r="AI16" s="6" t="n">
         <v>138.26</v>
       </c>
       <c r="AJ16" s="6" t="inlineStr"/>
-      <c r="AK16" s="10" t="inlineStr"/>
+      <c r="AK16" s="11" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
@@ -1889,14 +1910,14 @@
       <c r="AG17" s="7" t="n">
         <v>104.76</v>
       </c>
-      <c r="AH17" s="6" t="n">
+      <c r="AH17" s="12" t="n">
         <v>104.73</v>
       </c>
-      <c r="AI17" s="6" t="n">
+      <c r="AI17" s="10" t="n">
         <v>246.97</v>
       </c>
       <c r="AJ17" s="6" t="inlineStr"/>
-      <c r="AK17" s="10" t="inlineStr"/>
+      <c r="AK17" s="11" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
@@ -2028,14 +2049,14 @@
       <c r="AG18" s="7" t="n">
         <v>71.56999999999999</v>
       </c>
-      <c r="AH18" s="6" t="n">
+      <c r="AH18" s="12" t="n">
         <v>70.88</v>
       </c>
       <c r="AI18" s="6" t="n">
         <v>52.8</v>
       </c>
       <c r="AJ18" s="6" t="inlineStr"/>
-      <c r="AK18" s="10" t="inlineStr"/>
+      <c r="AK18" s="11" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
@@ -2170,11 +2191,11 @@
       <c r="AH19" s="6" t="n">
         <v>46.25</v>
       </c>
-      <c r="AI19" s="6" t="n">
+      <c r="AI19" s="10" t="n">
         <v>477.49</v>
       </c>
       <c r="AJ19" s="6" t="inlineStr"/>
-      <c r="AK19" s="10" t="inlineStr"/>
+      <c r="AK19" s="11" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="5" t="inlineStr">
@@ -2306,14 +2327,14 @@
       <c r="AG20" s="7" t="n">
         <v>80.31999999999999</v>
       </c>
-      <c r="AH20" s="6" t="n">
+      <c r="AH20" s="12" t="n">
         <v>81.38</v>
       </c>
       <c r="AI20" s="6" t="n">
         <v>149.08</v>
       </c>
       <c r="AJ20" s="6" t="inlineStr"/>
-      <c r="AK20" s="10" t="inlineStr"/>
+      <c r="AK20" s="11" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
@@ -2452,146 +2473,146 @@
         <v>157.64</v>
       </c>
       <c r="AJ21" s="6" t="inlineStr"/>
-      <c r="AK21" s="10" t="inlineStr"/>
+      <c r="AK21" s="11" t="inlineStr"/>
     </row>
     <row r="22">
-      <c r="A22" s="11" t="inlineStr">
+      <c r="A22" s="13" t="inlineStr">
         <is>
           <t>ZETA</t>
         </is>
       </c>
-      <c r="B22" s="12" t="n">
+      <c r="B22" s="14" t="n">
         <v>106.9</v>
       </c>
-      <c r="C22" s="12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D22" s="12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E22" s="12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F22" s="12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G22" s="12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H22" s="12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I22" s="12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J22" s="12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K22" s="13" t="n">
+      <c r="C22" s="14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D22" s="14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E22" s="14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F22" s="14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G22" s="14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H22" s="14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I22" s="14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J22" s="14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K22" s="15" t="n">
         <v>94.18000000000001</v>
       </c>
-      <c r="L22" s="13" t="n">
+      <c r="L22" s="15" t="n">
         <v>93.93000000000001</v>
       </c>
-      <c r="M22" s="13" t="n">
+      <c r="M22" s="15" t="n">
         <v>95.51000000000001</v>
       </c>
-      <c r="N22" s="13" t="n">
+      <c r="N22" s="15" t="n">
         <v>94.7</v>
       </c>
-      <c r="O22" s="12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P22" s="13" t="n">
+      <c r="O22" s="14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P22" s="15" t="n">
         <v>96.44</v>
       </c>
-      <c r="Q22" s="13" t="n">
+      <c r="Q22" s="15" t="n">
         <v>96.55</v>
       </c>
-      <c r="R22" s="13" t="n">
+      <c r="R22" s="15" t="n">
         <v>96.68000000000001</v>
       </c>
-      <c r="S22" s="13" t="n">
+      <c r="S22" s="15" t="n">
         <v>95.59</v>
       </c>
-      <c r="T22" s="13" t="n">
+      <c r="T22" s="15" t="n">
         <v>95.16</v>
       </c>
-      <c r="U22" s="12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="V22" s="12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="W22" s="12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="X22" s="13" t="n">
+      <c r="U22" s="14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="V22" s="14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="W22" s="14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="X22" s="15" t="n">
         <v>96.52</v>
       </c>
-      <c r="Y22" s="13" t="n">
+      <c r="Y22" s="15" t="n">
         <v>96.81</v>
       </c>
-      <c r="Z22" s="12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AA22" s="13" t="n">
+      <c r="Z22" s="14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AA22" s="15" t="n">
         <v>96.84</v>
       </c>
-      <c r="AB22" s="13" t="n">
+      <c r="AB22" s="15" t="n">
         <v>97.22</v>
       </c>
-      <c r="AC22" s="13" t="n">
+      <c r="AC22" s="15" t="n">
         <v>96.81</v>
       </c>
-      <c r="AD22" s="12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AE22" s="13" t="n">
+      <c r="AD22" s="14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AE22" s="15" t="n">
         <v>96.48</v>
       </c>
-      <c r="AF22" s="13" t="n">
+      <c r="AF22" s="15" t="n">
         <v>97.16</v>
       </c>
-      <c r="AG22" s="13" t="n">
+      <c r="AG22" s="15" t="n">
         <v>96.37</v>
       </c>
-      <c r="AH22" s="12" t="n">
+      <c r="AH22" s="16" t="n">
         <v>96.06</v>
       </c>
-      <c r="AI22" s="12" t="n">
+      <c r="AI22" s="14" t="n">
         <v>127.1</v>
       </c>
-      <c r="AJ22" s="12" t="inlineStr"/>
-      <c r="AK22" s="14" t="inlineStr"/>
+      <c r="AJ22" s="14" t="inlineStr"/>
+      <c r="AK22" s="17" t="inlineStr"/>
     </row>
     <row r="23"/>
     <row r="24"/>
@@ -2766,7 +2787,7 @@
           <t>OBSERVACIONES</t>
         </is>
       </c>
-      <c r="AK32" s="15" t="n"/>
+      <c r="AK32" s="18" t="n"/>
     </row>
     <row r="33">
       <c r="A33" s="5" t="inlineStr">
@@ -2903,7 +2924,7 @@
       </c>
       <c r="AI33" s="6" t="inlineStr"/>
       <c r="AJ33" s="6" t="inlineStr"/>
-      <c r="AK33" s="16" t="n"/>
+      <c r="AK33" s="19" t="n"/>
     </row>
     <row r="34">
       <c r="A34" s="5" t="inlineStr">
@@ -3040,7 +3061,7 @@
       </c>
       <c r="AI34" s="6" t="inlineStr"/>
       <c r="AJ34" s="6" t="inlineStr"/>
-      <c r="AK34" s="16" t="n"/>
+      <c r="AK34" s="19" t="n"/>
     </row>
     <row r="35">
       <c r="A35" s="5" t="inlineStr">
@@ -3177,7 +3198,7 @@
       </c>
       <c r="AI35" s="6" t="inlineStr"/>
       <c r="AJ35" s="6" t="inlineStr"/>
-      <c r="AK35" s="16" t="n"/>
+      <c r="AK35" s="19" t="n"/>
     </row>
     <row r="36">
       <c r="A36" s="5" t="inlineStr">
@@ -3314,7 +3335,7 @@
       </c>
       <c r="AI36" s="6" t="inlineStr"/>
       <c r="AJ36" s="6" t="inlineStr"/>
-      <c r="AK36" s="16" t="n"/>
+      <c r="AK36" s="19" t="n"/>
     </row>
     <row r="37">
       <c r="A37" s="5" t="inlineStr">
@@ -3451,7 +3472,7 @@
       </c>
       <c r="AI37" s="6" t="inlineStr"/>
       <c r="AJ37" s="6" t="inlineStr"/>
-      <c r="AK37" s="16" t="n"/>
+      <c r="AK37" s="19" t="n"/>
     </row>
     <row r="38">
       <c r="A38" s="5" t="inlineStr">
@@ -3588,7 +3609,7 @@
       </c>
       <c r="AI38" s="6" t="inlineStr"/>
       <c r="AJ38" s="6" t="inlineStr"/>
-      <c r="AK38" s="16" t="n"/>
+      <c r="AK38" s="19" t="n"/>
     </row>
     <row r="39">
       <c r="A39" s="5" t="inlineStr">
@@ -3725,7 +3746,7 @@
       </c>
       <c r="AI39" s="6" t="inlineStr"/>
       <c r="AJ39" s="6" t="inlineStr"/>
-      <c r="AK39" s="16" t="n"/>
+      <c r="AK39" s="19" t="n"/>
     </row>
     <row r="40">
       <c r="A40" s="5" t="inlineStr">
@@ -3862,7 +3883,7 @@
       </c>
       <c r="AI40" s="6" t="inlineStr"/>
       <c r="AJ40" s="6" t="inlineStr"/>
-      <c r="AK40" s="16" t="n"/>
+      <c r="AK40" s="19" t="n"/>
     </row>
     <row r="41">
       <c r="A41" s="5" t="inlineStr">
@@ -3999,7 +4020,7 @@
       </c>
       <c r="AI41" s="6" t="inlineStr"/>
       <c r="AJ41" s="6" t="inlineStr"/>
-      <c r="AK41" s="16" t="n"/>
+      <c r="AK41" s="19" t="n"/>
     </row>
     <row r="42">
       <c r="A42" s="5" t="inlineStr">
@@ -4136,144 +4157,144 @@
       </c>
       <c r="AI42" s="6" t="inlineStr"/>
       <c r="AJ42" s="6" t="inlineStr"/>
-      <c r="AK42" s="16" t="n"/>
+      <c r="AK42" s="19" t="n"/>
     </row>
     <row r="43">
-      <c r="A43" s="11" t="inlineStr">
+      <c r="A43" s="13" t="inlineStr">
         <is>
           <t>TELECIUDADANA</t>
         </is>
       </c>
-      <c r="B43" s="12" t="n">
+      <c r="B43" s="14" t="n">
         <v>681.25</v>
       </c>
-      <c r="C43" s="12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D43" s="12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E43" s="12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F43" s="12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G43" s="12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H43" s="12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I43" s="12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J43" s="12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K43" s="17" t="n">
+      <c r="C43" s="14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D43" s="14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E43" s="14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F43" s="14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G43" s="14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H43" s="14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I43" s="14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J43" s="14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K43" s="20" t="n">
         <v>27.51</v>
       </c>
-      <c r="L43" s="17" t="n">
+      <c r="L43" s="20" t="n">
         <v>27.51</v>
       </c>
-      <c r="M43" s="17" t="n">
+      <c r="M43" s="20" t="n">
         <v>27.42</v>
       </c>
-      <c r="N43" s="17" t="n">
+      <c r="N43" s="20" t="n">
         <v>27.63</v>
       </c>
-      <c r="O43" s="12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P43" s="17" t="n">
+      <c r="O43" s="14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P43" s="20" t="n">
         <v>27.18</v>
       </c>
-      <c r="Q43" s="17" t="n">
+      <c r="Q43" s="20" t="n">
         <v>27.42</v>
       </c>
-      <c r="R43" s="17" t="n">
+      <c r="R43" s="20" t="n">
         <v>29.01</v>
       </c>
-      <c r="S43" s="17" t="n">
+      <c r="S43" s="20" t="n">
         <v>27.59</v>
       </c>
-      <c r="T43" s="17" t="n">
+      <c r="T43" s="20" t="n">
         <v>27.61</v>
       </c>
-      <c r="U43" s="12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="V43" s="12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="W43" s="12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="X43" s="17" t="n">
+      <c r="U43" s="14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="V43" s="14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="W43" s="14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="X43" s="20" t="n">
         <v>27.49</v>
       </c>
-      <c r="Y43" s="17" t="n">
+      <c r="Y43" s="20" t="n">
         <v>27.51</v>
       </c>
-      <c r="Z43" s="12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AA43" s="17" t="n">
+      <c r="Z43" s="14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AA43" s="20" t="n">
         <v>27.53</v>
       </c>
-      <c r="AB43" s="17" t="n">
+      <c r="AB43" s="20" t="n">
         <v>27.47</v>
       </c>
-      <c r="AC43" s="17" t="n">
+      <c r="AC43" s="20" t="n">
         <v>27.33</v>
       </c>
-      <c r="AD43" s="12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AE43" s="17" t="n">
+      <c r="AD43" s="14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AE43" s="20" t="n">
         <v>27.68</v>
       </c>
-      <c r="AF43" s="17" t="n">
+      <c r="AF43" s="20" t="n">
         <v>27.72</v>
       </c>
-      <c r="AG43" s="17" t="n">
+      <c r="AG43" s="20" t="n">
         <v>27.44</v>
       </c>
-      <c r="AH43" s="12" t="n">
+      <c r="AH43" s="14" t="n">
         <v>27.59</v>
       </c>
-      <c r="AI43" s="12" t="inlineStr"/>
-      <c r="AJ43" s="12" t="inlineStr"/>
-      <c r="AK43" s="18" t="n"/>
+      <c r="AI43" s="14" t="inlineStr"/>
+      <c r="AJ43" s="14" t="inlineStr"/>
+      <c r="AK43" s="21" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="28">

--- a/ReportesUnificados/zamora_ReporteUnificado.xlsx
+++ b/ReportesUnificados/zamora_ReporteUnificado.xlsx
@@ -303,7 +303,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>2</row>
+      <row>4</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="4762500" cy="952500"/>
@@ -326,9 +326,9 @@
   </oneCellAnchor>
   <oneCellAnchor>
     <from>
-      <col>33</col>
+      <col>35</col>
       <colOff>0</colOff>
-      <row>2</row>
+      <row>4</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="2476500" cy="1143000"/>
@@ -376,7 +376,7 @@
   </oneCellAnchor>
   <oneCellAnchor>
     <from>
-      <col>33</col>
+      <col>35</col>
       <colOff>0</colOff>
       <row>26</row>
       <rowOff>0</rowOff>

--- a/ReportesUnificados/zamora_ReporteUnificado.xlsx
+++ b/ReportesUnificados/zamora_ReporteUnificado.xlsx
@@ -30,12 +30,18 @@
       <sz val="12"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFC4A2C"/>
+        <bgColor rgb="FFFC4A2C"/>
+      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -171,7 +177,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -191,13 +197,16 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -209,7 +218,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -217,7 +226,10 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="16" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="12" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="13" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -792,7 +804,7 @@
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>FECHA PRESENTACIÓN: 28/08/2025</t>
+          <t>FECHA PRESENTACIÓN: 01/09/2025</t>
         </is>
       </c>
     </row>
@@ -1055,14 +1067,14 @@
       <c r="AG11" s="9" t="n">
         <v>41.92</v>
       </c>
-      <c r="AH11" s="6" t="n">
+      <c r="AH11" s="10" t="n">
         <v>44.5</v>
       </c>
-      <c r="AI11" s="6" t="n">
+      <c r="AI11" s="10" t="n">
         <v>485.74</v>
       </c>
       <c r="AJ11" s="6" t="inlineStr"/>
-      <c r="AK11" s="10" t="inlineStr"/>
+      <c r="AK11" s="11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
@@ -1201,7 +1213,7 @@
         <v>101.16</v>
       </c>
       <c r="AJ12" s="6" t="inlineStr"/>
-      <c r="AK12" s="10" t="inlineStr"/>
+      <c r="AK12" s="11" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
@@ -1340,7 +1352,7 @@
         <v>104.99</v>
       </c>
       <c r="AJ13" s="6" t="inlineStr"/>
-      <c r="AK13" s="10" t="inlineStr"/>
+      <c r="AK13" s="11" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
@@ -1479,7 +1491,7 @@
         <v>119.83</v>
       </c>
       <c r="AJ14" s="6" t="inlineStr"/>
-      <c r="AK14" s="10" t="inlineStr"/>
+      <c r="AK14" s="11" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
@@ -1618,7 +1630,7 @@
         <v>156.6</v>
       </c>
       <c r="AJ15" s="6" t="inlineStr"/>
-      <c r="AK15" s="10" t="inlineStr"/>
+      <c r="AK15" s="11" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
@@ -1757,7 +1769,7 @@
         <v>138.26</v>
       </c>
       <c r="AJ16" s="6" t="inlineStr"/>
-      <c r="AK16" s="10" t="inlineStr"/>
+      <c r="AK16" s="11" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
@@ -1892,11 +1904,11 @@
       <c r="AH17" s="6" t="n">
         <v>104.73</v>
       </c>
-      <c r="AI17" s="6" t="n">
+      <c r="AI17" s="10" t="n">
         <v>246.97</v>
       </c>
       <c r="AJ17" s="6" t="inlineStr"/>
-      <c r="AK17" s="10" t="inlineStr"/>
+      <c r="AK17" s="11" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
@@ -2035,7 +2047,7 @@
         <v>52.8</v>
       </c>
       <c r="AJ18" s="6" t="inlineStr"/>
-      <c r="AK18" s="10" t="inlineStr"/>
+      <c r="AK18" s="11" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
@@ -2167,14 +2179,14 @@
       <c r="AG19" s="8" t="n">
         <v>45.74</v>
       </c>
-      <c r="AH19" s="6" t="n">
+      <c r="AH19" s="10" t="n">
         <v>46.25</v>
       </c>
-      <c r="AI19" s="6" t="n">
+      <c r="AI19" s="10" t="n">
         <v>477.49</v>
       </c>
       <c r="AJ19" s="6" t="inlineStr"/>
-      <c r="AK19" s="10" t="inlineStr"/>
+      <c r="AK19" s="11" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="5" t="inlineStr">
@@ -2313,7 +2325,7 @@
         <v>149.08</v>
       </c>
       <c r="AJ20" s="6" t="inlineStr"/>
-      <c r="AK20" s="10" t="inlineStr"/>
+      <c r="AK20" s="11" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
@@ -2452,146 +2464,146 @@
         <v>157.64</v>
       </c>
       <c r="AJ21" s="6" t="inlineStr"/>
-      <c r="AK21" s="10" t="inlineStr"/>
+      <c r="AK21" s="11" t="inlineStr"/>
     </row>
     <row r="22">
-      <c r="A22" s="11" t="inlineStr">
+      <c r="A22" s="12" t="inlineStr">
         <is>
           <t>ZETA</t>
         </is>
       </c>
-      <c r="B22" s="12" t="n">
+      <c r="B22" s="13" t="n">
         <v>106.9</v>
       </c>
-      <c r="C22" s="12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D22" s="12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E22" s="12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F22" s="12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G22" s="12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H22" s="12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I22" s="12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J22" s="12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K22" s="13" t="n">
+      <c r="C22" s="13" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D22" s="13" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E22" s="13" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F22" s="13" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G22" s="13" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H22" s="13" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I22" s="13" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J22" s="13" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K22" s="14" t="n">
         <v>94.18000000000001</v>
       </c>
-      <c r="L22" s="13" t="n">
+      <c r="L22" s="14" t="n">
         <v>93.93000000000001</v>
       </c>
-      <c r="M22" s="13" t="n">
+      <c r="M22" s="14" t="n">
         <v>95.51000000000001</v>
       </c>
-      <c r="N22" s="13" t="n">
+      <c r="N22" s="14" t="n">
         <v>94.7</v>
       </c>
-      <c r="O22" s="12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P22" s="13" t="n">
+      <c r="O22" s="13" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P22" s="14" t="n">
         <v>96.44</v>
       </c>
-      <c r="Q22" s="13" t="n">
+      <c r="Q22" s="14" t="n">
         <v>96.55</v>
       </c>
-      <c r="R22" s="13" t="n">
+      <c r="R22" s="14" t="n">
         <v>96.68000000000001</v>
       </c>
-      <c r="S22" s="13" t="n">
+      <c r="S22" s="14" t="n">
         <v>95.59</v>
       </c>
-      <c r="T22" s="13" t="n">
+      <c r="T22" s="14" t="n">
         <v>95.16</v>
       </c>
-      <c r="U22" s="12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="V22" s="12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="W22" s="12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="X22" s="13" t="n">
+      <c r="U22" s="13" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="V22" s="13" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="W22" s="13" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="X22" s="14" t="n">
         <v>96.52</v>
       </c>
-      <c r="Y22" s="13" t="n">
+      <c r="Y22" s="14" t="n">
         <v>96.81</v>
       </c>
-      <c r="Z22" s="12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AA22" s="13" t="n">
+      <c r="Z22" s="13" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AA22" s="14" t="n">
         <v>96.84</v>
       </c>
-      <c r="AB22" s="13" t="n">
+      <c r="AB22" s="14" t="n">
         <v>97.22</v>
       </c>
-      <c r="AC22" s="13" t="n">
+      <c r="AC22" s="14" t="n">
         <v>96.81</v>
       </c>
-      <c r="AD22" s="12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AE22" s="13" t="n">
+      <c r="AD22" s="13" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AE22" s="14" t="n">
         <v>96.48</v>
       </c>
-      <c r="AF22" s="13" t="n">
+      <c r="AF22" s="14" t="n">
         <v>97.16</v>
       </c>
-      <c r="AG22" s="13" t="n">
+      <c r="AG22" s="14" t="n">
         <v>96.37</v>
       </c>
-      <c r="AH22" s="12" t="n">
+      <c r="AH22" s="13" t="n">
         <v>96.06</v>
       </c>
-      <c r="AI22" s="12" t="n">
+      <c r="AI22" s="13" t="n">
         <v>127.1</v>
       </c>
-      <c r="AJ22" s="12" t="inlineStr"/>
-      <c r="AK22" s="14" t="inlineStr"/>
+      <c r="AJ22" s="13" t="inlineStr"/>
+      <c r="AK22" s="15" t="inlineStr"/>
     </row>
     <row r="23"/>
     <row r="24"/>
@@ -2640,7 +2652,7 @@
     <row r="31">
       <c r="A31" s="1" t="inlineStr">
         <is>
-          <t>FECHA PRESENTACIÓN: 28/08/2025</t>
+          <t>FECHA PRESENTACIÓN: 01/09/2025</t>
         </is>
       </c>
     </row>
@@ -2766,7 +2778,7 @@
           <t>OBSERVACIONES</t>
         </is>
       </c>
-      <c r="AK32" s="15" t="n"/>
+      <c r="AK32" s="16" t="n"/>
     </row>
     <row r="33">
       <c r="A33" s="5" t="inlineStr">
@@ -2817,16 +2829,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="K33" s="7" t="n">
+      <c r="K33" s="8" t="n">
         <v>57.55</v>
       </c>
-      <c r="L33" s="7" t="n">
+      <c r="L33" s="8" t="n">
         <v>57.75</v>
       </c>
-      <c r="M33" s="7" t="n">
+      <c r="M33" s="8" t="n">
         <v>57.28</v>
       </c>
-      <c r="N33" s="7" t="n">
+      <c r="N33" s="8" t="n">
         <v>57.49</v>
       </c>
       <c r="O33" s="6" t="inlineStr">
@@ -2834,19 +2846,19 @@
           <t>-</t>
         </is>
       </c>
-      <c r="P33" s="7" t="n">
+      <c r="P33" s="8" t="n">
         <v>56.76</v>
       </c>
-      <c r="Q33" s="7" t="n">
+      <c r="Q33" s="9" t="n">
         <v>55.79</v>
       </c>
-      <c r="R33" s="7" t="n">
+      <c r="R33" s="9" t="n">
         <v>54.35</v>
       </c>
-      <c r="S33" s="7" t="n">
+      <c r="S33" s="8" t="n">
         <v>56.31</v>
       </c>
-      <c r="T33" s="7" t="n">
+      <c r="T33" s="9" t="n">
         <v>55.88</v>
       </c>
       <c r="U33" s="6" t="inlineStr">
@@ -2864,10 +2876,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="X33" s="7" t="n">
+      <c r="X33" s="9" t="n">
         <v>55.13</v>
       </c>
-      <c r="Y33" s="7" t="n">
+      <c r="Y33" s="9" t="n">
         <v>54.41</v>
       </c>
       <c r="Z33" s="6" t="inlineStr">
@@ -2875,13 +2887,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="AA33" s="7" t="n">
+      <c r="AA33" s="9" t="n">
         <v>55</v>
       </c>
-      <c r="AB33" s="7" t="n">
+      <c r="AB33" s="9" t="n">
         <v>55.06</v>
       </c>
-      <c r="AC33" s="7" t="n">
+      <c r="AC33" s="9" t="n">
         <v>54.2</v>
       </c>
       <c r="AD33" s="6" t="inlineStr">
@@ -2889,21 +2901,21 @@
           <t>-</t>
         </is>
       </c>
-      <c r="AE33" s="7" t="n">
+      <c r="AE33" s="9" t="n">
         <v>54.14</v>
       </c>
-      <c r="AF33" s="7" t="n">
+      <c r="AF33" s="9" t="n">
         <v>54.39</v>
       </c>
-      <c r="AG33" s="7" t="n">
+      <c r="AG33" s="9" t="n">
         <v>54.92</v>
       </c>
-      <c r="AH33" s="6" t="n">
+      <c r="AH33" s="10" t="n">
         <v>55.67</v>
       </c>
       <c r="AI33" s="6" t="inlineStr"/>
       <c r="AJ33" s="6" t="inlineStr"/>
-      <c r="AK33" s="16" t="n"/>
+      <c r="AK33" s="17" t="n"/>
     </row>
     <row r="34">
       <c r="A34" s="5" t="inlineStr">
@@ -3035,12 +3047,12 @@
       <c r="AG34" s="9" t="n">
         <v>39.34</v>
       </c>
-      <c r="AH34" s="6" t="n">
+      <c r="AH34" s="10" t="n">
         <v>39.21</v>
       </c>
       <c r="AI34" s="6" t="inlineStr"/>
       <c r="AJ34" s="6" t="inlineStr"/>
-      <c r="AK34" s="16" t="n"/>
+      <c r="AK34" s="17" t="n"/>
     </row>
     <row r="35">
       <c r="A35" s="5" t="inlineStr">
@@ -3172,12 +3184,12 @@
       <c r="AG35" s="9" t="n">
         <v>41.74</v>
       </c>
-      <c r="AH35" s="6" t="n">
+      <c r="AH35" s="10" t="n">
         <v>40.77</v>
       </c>
       <c r="AI35" s="6" t="inlineStr"/>
       <c r="AJ35" s="6" t="inlineStr"/>
-      <c r="AK35" s="16" t="n"/>
+      <c r="AK35" s="17" t="n"/>
     </row>
     <row r="36">
       <c r="A36" s="5" t="inlineStr">
@@ -3309,12 +3321,12 @@
       <c r="AG36" s="9" t="n">
         <v>33.06</v>
       </c>
-      <c r="AH36" s="6" t="n">
+      <c r="AH36" s="10" t="n">
         <v>33.69</v>
       </c>
       <c r="AI36" s="6" t="inlineStr"/>
       <c r="AJ36" s="6" t="inlineStr"/>
-      <c r="AK36" s="16" t="n"/>
+      <c r="AK36" s="17" t="n"/>
     </row>
     <row r="37">
       <c r="A37" s="5" t="inlineStr">
@@ -3446,12 +3458,12 @@
       <c r="AG37" s="9" t="n">
         <v>31.83</v>
       </c>
-      <c r="AH37" s="6" t="n">
+      <c r="AH37" s="10" t="n">
         <v>32.57</v>
       </c>
       <c r="AI37" s="6" t="inlineStr"/>
       <c r="AJ37" s="6" t="inlineStr"/>
-      <c r="AK37" s="16" t="n"/>
+      <c r="AK37" s="17" t="n"/>
     </row>
     <row r="38">
       <c r="A38" s="5" t="inlineStr">
@@ -3583,12 +3595,12 @@
       <c r="AG38" s="9" t="n">
         <v>30.7</v>
       </c>
-      <c r="AH38" s="6" t="n">
+      <c r="AH38" s="10" t="n">
         <v>31.16</v>
       </c>
       <c r="AI38" s="6" t="inlineStr"/>
       <c r="AJ38" s="6" t="inlineStr"/>
-      <c r="AK38" s="16" t="n"/>
+      <c r="AK38" s="17" t="n"/>
     </row>
     <row r="39">
       <c r="A39" s="5" t="inlineStr">
@@ -3720,12 +3732,12 @@
       <c r="AG39" s="9" t="n">
         <v>29.19</v>
       </c>
-      <c r="AH39" s="6" t="n">
+      <c r="AH39" s="10" t="n">
         <v>29.19</v>
       </c>
       <c r="AI39" s="6" t="inlineStr"/>
       <c r="AJ39" s="6" t="inlineStr"/>
-      <c r="AK39" s="16" t="n"/>
+      <c r="AK39" s="17" t="n"/>
     </row>
     <row r="40">
       <c r="A40" s="5" t="inlineStr">
@@ -3857,12 +3869,12 @@
       <c r="AG40" s="9" t="n">
         <v>26.69</v>
       </c>
-      <c r="AH40" s="6" t="n">
+      <c r="AH40" s="10" t="n">
         <v>26.81</v>
       </c>
       <c r="AI40" s="6" t="inlineStr"/>
       <c r="AJ40" s="6" t="inlineStr"/>
-      <c r="AK40" s="16" t="n"/>
+      <c r="AK40" s="17" t="n"/>
     </row>
     <row r="41">
       <c r="A41" s="5" t="inlineStr">
@@ -3994,12 +4006,12 @@
       <c r="AG41" s="9" t="n">
         <v>26.73</v>
       </c>
-      <c r="AH41" s="6" t="n">
+      <c r="AH41" s="10" t="n">
         <v>26.89</v>
       </c>
       <c r="AI41" s="6" t="inlineStr"/>
       <c r="AJ41" s="6" t="inlineStr"/>
-      <c r="AK41" s="16" t="n"/>
+      <c r="AK41" s="17" t="n"/>
     </row>
     <row r="42">
       <c r="A42" s="5" t="inlineStr">
@@ -4131,149 +4143,149 @@
       <c r="AG42" s="9" t="n">
         <v>27.53</v>
       </c>
-      <c r="AH42" s="6" t="n">
+      <c r="AH42" s="10" t="n">
         <v>27.64</v>
       </c>
       <c r="AI42" s="6" t="inlineStr"/>
       <c r="AJ42" s="6" t="inlineStr"/>
-      <c r="AK42" s="16" t="n"/>
+      <c r="AK42" s="17" t="n"/>
     </row>
     <row r="43">
-      <c r="A43" s="11" t="inlineStr">
+      <c r="A43" s="12" t="inlineStr">
         <is>
           <t>TELECIUDADANA</t>
         </is>
       </c>
-      <c r="B43" s="12" t="n">
+      <c r="B43" s="13" t="n">
         <v>681.25</v>
       </c>
-      <c r="C43" s="12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D43" s="12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E43" s="12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F43" s="12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G43" s="12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H43" s="12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I43" s="12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J43" s="12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K43" s="17" t="n">
+      <c r="C43" s="13" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D43" s="13" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E43" s="13" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F43" s="13" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G43" s="13" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H43" s="13" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I43" s="13" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J43" s="13" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K43" s="18" t="n">
         <v>27.51</v>
       </c>
-      <c r="L43" s="17" t="n">
+      <c r="L43" s="18" t="n">
         <v>27.51</v>
       </c>
-      <c r="M43" s="17" t="n">
+      <c r="M43" s="18" t="n">
         <v>27.42</v>
       </c>
-      <c r="N43" s="17" t="n">
+      <c r="N43" s="18" t="n">
         <v>27.63</v>
       </c>
-      <c r="O43" s="12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P43" s="17" t="n">
+      <c r="O43" s="13" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P43" s="18" t="n">
         <v>27.18</v>
       </c>
-      <c r="Q43" s="17" t="n">
+      <c r="Q43" s="18" t="n">
         <v>27.42</v>
       </c>
-      <c r="R43" s="17" t="n">
+      <c r="R43" s="18" t="n">
         <v>29.01</v>
       </c>
-      <c r="S43" s="17" t="n">
+      <c r="S43" s="18" t="n">
         <v>27.59</v>
       </c>
-      <c r="T43" s="17" t="n">
+      <c r="T43" s="18" t="n">
         <v>27.61</v>
       </c>
-      <c r="U43" s="12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="V43" s="12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="W43" s="12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="X43" s="17" t="n">
+      <c r="U43" s="13" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="V43" s="13" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="W43" s="13" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="X43" s="18" t="n">
         <v>27.49</v>
       </c>
-      <c r="Y43" s="17" t="n">
+      <c r="Y43" s="18" t="n">
         <v>27.51</v>
       </c>
-      <c r="Z43" s="12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AA43" s="17" t="n">
+      <c r="Z43" s="13" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AA43" s="18" t="n">
         <v>27.53</v>
       </c>
-      <c r="AB43" s="17" t="n">
+      <c r="AB43" s="18" t="n">
         <v>27.47</v>
       </c>
-      <c r="AC43" s="17" t="n">
+      <c r="AC43" s="18" t="n">
         <v>27.33</v>
       </c>
-      <c r="AD43" s="12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AE43" s="17" t="n">
+      <c r="AD43" s="13" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AE43" s="18" t="n">
         <v>27.68</v>
       </c>
-      <c r="AF43" s="17" t="n">
+      <c r="AF43" s="18" t="n">
         <v>27.72</v>
       </c>
-      <c r="AG43" s="17" t="n">
+      <c r="AG43" s="18" t="n">
         <v>27.44</v>
       </c>
-      <c r="AH43" s="12" t="n">
+      <c r="AH43" s="19" t="n">
         <v>27.59</v>
       </c>
-      <c r="AI43" s="12" t="inlineStr"/>
-      <c r="AJ43" s="12" t="inlineStr"/>
-      <c r="AK43" s="18" t="n"/>
+      <c r="AI43" s="13" t="inlineStr"/>
+      <c r="AJ43" s="13" t="inlineStr"/>
+      <c r="AK43" s="20" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="28">

--- a/ReportesUnificados/zamora_ReporteUnificado.xlsx
+++ b/ReportesUnificados/zamora_ReporteUnificado.xlsx
@@ -39,6 +39,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFFFFE9F"/>
+        <bgColor rgb="FFFFFE9F"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFC4A2C"/>
         <bgColor rgb="FFFC4A2C"/>
       </patternFill>
@@ -47,12 +53,6 @@
       <patternFill patternType="solid">
         <fgColor rgb="FFCDFECE"/>
         <bgColor rgb="FFCDFECE"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFE9F"/>
-        <bgColor rgb="FFFFFE9F"/>
       </patternFill>
     </fill>
     <fill>
@@ -197,16 +197,16 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -218,7 +218,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -229,7 +229,7 @@
     <xf numFmtId="0" fontId="0" fillId="5" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="13" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -804,7 +804,7 @@
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>FECHA PRESENTACIÓN: 01/09/2025</t>
+          <t>FECHA PRESENTACIÓN: 02/09/2025</t>
         </is>
       </c>
     </row>
@@ -1067,7 +1067,7 @@
       <c r="AG11" s="9" t="n">
         <v>41.92</v>
       </c>
-      <c r="AH11" s="10" t="n">
+      <c r="AH11" s="8" t="n">
         <v>44.5</v>
       </c>
       <c r="AI11" s="10" t="n">
@@ -1206,10 +1206,10 @@
       <c r="AG12" s="9" t="n">
         <v>41.96</v>
       </c>
-      <c r="AH12" s="6" t="n">
+      <c r="AH12" s="7" t="n">
         <v>73.26000000000001</v>
       </c>
-      <c r="AI12" s="6" t="n">
+      <c r="AI12" s="7" t="n">
         <v>101.16</v>
       </c>
       <c r="AJ12" s="6" t="inlineStr"/>
@@ -1345,10 +1345,10 @@
       <c r="AG13" s="7" t="n">
         <v>100.99</v>
       </c>
-      <c r="AH13" s="6" t="n">
+      <c r="AH13" s="7" t="n">
         <v>101.89</v>
       </c>
-      <c r="AI13" s="6" t="n">
+      <c r="AI13" s="7" t="n">
         <v>104.99</v>
       </c>
       <c r="AJ13" s="6" t="inlineStr"/>
@@ -1484,10 +1484,10 @@
       <c r="AG14" s="7" t="n">
         <v>90.73999999999999</v>
       </c>
-      <c r="AH14" s="6" t="n">
+      <c r="AH14" s="7" t="n">
         <v>90.89</v>
       </c>
-      <c r="AI14" s="6" t="n">
+      <c r="AI14" s="7" t="n">
         <v>119.83</v>
       </c>
       <c r="AJ14" s="6" t="inlineStr"/>
@@ -1623,10 +1623,10 @@
       <c r="AG15" s="7" t="n">
         <v>74.22</v>
       </c>
-      <c r="AH15" s="6" t="n">
+      <c r="AH15" s="7" t="n">
         <v>74.42</v>
       </c>
-      <c r="AI15" s="6" t="n">
+      <c r="AI15" s="7" t="n">
         <v>156.6</v>
       </c>
       <c r="AJ15" s="6" t="inlineStr"/>
@@ -1762,10 +1762,10 @@
       <c r="AG16" s="7" t="n">
         <v>88.94</v>
       </c>
-      <c r="AH16" s="6" t="n">
+      <c r="AH16" s="7" t="n">
         <v>89.45999999999999</v>
       </c>
-      <c r="AI16" s="6" t="n">
+      <c r="AI16" s="7" t="n">
         <v>138.26</v>
       </c>
       <c r="AJ16" s="6" t="inlineStr"/>
@@ -1901,7 +1901,7 @@
       <c r="AG17" s="7" t="n">
         <v>104.76</v>
       </c>
-      <c r="AH17" s="6" t="n">
+      <c r="AH17" s="7" t="n">
         <v>104.73</v>
       </c>
       <c r="AI17" s="10" t="n">
@@ -2040,10 +2040,10 @@
       <c r="AG18" s="7" t="n">
         <v>71.56999999999999</v>
       </c>
-      <c r="AH18" s="6" t="n">
+      <c r="AH18" s="7" t="n">
         <v>70.88</v>
       </c>
-      <c r="AI18" s="6" t="n">
+      <c r="AI18" s="7" t="n">
         <v>52.8</v>
       </c>
       <c r="AJ18" s="6" t="inlineStr"/>
@@ -2179,7 +2179,7 @@
       <c r="AG19" s="8" t="n">
         <v>45.74</v>
       </c>
-      <c r="AH19" s="10" t="n">
+      <c r="AH19" s="8" t="n">
         <v>46.25</v>
       </c>
       <c r="AI19" s="10" t="n">
@@ -2318,10 +2318,10 @@
       <c r="AG20" s="7" t="n">
         <v>80.31999999999999</v>
       </c>
-      <c r="AH20" s="6" t="n">
+      <c r="AH20" s="7" t="n">
         <v>81.38</v>
       </c>
-      <c r="AI20" s="6" t="n">
+      <c r="AI20" s="7" t="n">
         <v>149.08</v>
       </c>
       <c r="AJ20" s="6" t="inlineStr"/>
@@ -2457,10 +2457,10 @@
       <c r="AG21" s="7" t="n">
         <v>57.08</v>
       </c>
-      <c r="AH21" s="6" t="n">
+      <c r="AH21" s="7" t="n">
         <v>56.33</v>
       </c>
-      <c r="AI21" s="6" t="n">
+      <c r="AI21" s="7" t="n">
         <v>157.64</v>
       </c>
       <c r="AJ21" s="6" t="inlineStr"/>
@@ -2596,10 +2596,10 @@
       <c r="AG22" s="14" t="n">
         <v>96.37</v>
       </c>
-      <c r="AH22" s="13" t="n">
+      <c r="AH22" s="14" t="n">
         <v>96.06</v>
       </c>
-      <c r="AI22" s="13" t="n">
+      <c r="AI22" s="14" t="n">
         <v>127.1</v>
       </c>
       <c r="AJ22" s="13" t="inlineStr"/>
@@ -2652,7 +2652,7 @@
     <row r="31">
       <c r="A31" s="1" t="inlineStr">
         <is>
-          <t>FECHA PRESENTACIÓN: 01/09/2025</t>
+          <t>FECHA PRESENTACIÓN: 02/09/2025</t>
         </is>
       </c>
     </row>

--- a/ReportesUnificados/zamora_ReporteUnificado.xlsx
+++ b/ReportesUnificados/zamora_ReporteUnificado.xlsx
@@ -177,7 +177,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -203,9 +203,6 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -226,10 +223,10 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="16" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="12" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="13" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -1003,19 +1000,19 @@
           <t>-</t>
         </is>
       </c>
-      <c r="P11" s="9" t="n">
+      <c r="P11" s="8" t="n">
         <v>41.6</v>
       </c>
-      <c r="Q11" s="9" t="n">
+      <c r="Q11" s="8" t="n">
         <v>40.72</v>
       </c>
-      <c r="R11" s="9" t="n">
+      <c r="R11" s="8" t="n">
         <v>39.48</v>
       </c>
-      <c r="S11" s="9" t="n">
+      <c r="S11" s="8" t="n">
         <v>39</v>
       </c>
-      <c r="T11" s="9" t="n">
+      <c r="T11" s="8" t="n">
         <v>39.18</v>
       </c>
       <c r="U11" s="6" t="inlineStr">
@@ -1036,7 +1033,7 @@
       <c r="X11" s="8" t="n">
         <v>43.07</v>
       </c>
-      <c r="Y11" s="9" t="n">
+      <c r="Y11" s="8" t="n">
         <v>38.32</v>
       </c>
       <c r="Z11" s="6" t="inlineStr">
@@ -1050,7 +1047,7 @@
       <c r="AB11" s="8" t="n">
         <v>43.68</v>
       </c>
-      <c r="AC11" s="9" t="n">
+      <c r="AC11" s="8" t="n">
         <v>40.17</v>
       </c>
       <c r="AD11" s="6" t="inlineStr">
@@ -1058,23 +1055,23 @@
           <t>-</t>
         </is>
       </c>
-      <c r="AE11" s="9" t="n">
+      <c r="AE11" s="8" t="n">
         <v>42.11</v>
       </c>
-      <c r="AF11" s="9" t="n">
+      <c r="AF11" s="8" t="n">
         <v>40.11</v>
       </c>
-      <c r="AG11" s="9" t="n">
+      <c r="AG11" s="8" t="n">
         <v>41.92</v>
       </c>
       <c r="AH11" s="8" t="n">
         <v>44.5</v>
       </c>
-      <c r="AI11" s="10" t="n">
+      <c r="AI11" s="9" t="n">
         <v>485.74</v>
       </c>
       <c r="AJ11" s="6" t="inlineStr"/>
-      <c r="AK11" s="11" t="inlineStr"/>
+      <c r="AK11" s="10" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
@@ -1200,10 +1197,10 @@
       <c r="AE12" s="8" t="n">
         <v>46.82</v>
       </c>
-      <c r="AF12" s="9" t="n">
+      <c r="AF12" s="8" t="n">
         <v>40.81</v>
       </c>
-      <c r="AG12" s="9" t="n">
+      <c r="AG12" s="8" t="n">
         <v>41.96</v>
       </c>
       <c r="AH12" s="7" t="n">
@@ -1213,7 +1210,7 @@
         <v>101.16</v>
       </c>
       <c r="AJ12" s="6" t="inlineStr"/>
-      <c r="AK12" s="11" t="inlineStr"/>
+      <c r="AK12" s="10" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
@@ -1352,7 +1349,7 @@
         <v>104.99</v>
       </c>
       <c r="AJ13" s="6" t="inlineStr"/>
-      <c r="AK13" s="11" t="inlineStr"/>
+      <c r="AK13" s="10" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
@@ -1491,7 +1488,7 @@
         <v>119.83</v>
       </c>
       <c r="AJ14" s="6" t="inlineStr"/>
-      <c r="AK14" s="11" t="inlineStr"/>
+      <c r="AK14" s="10" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
@@ -1630,7 +1627,7 @@
         <v>156.6</v>
       </c>
       <c r="AJ15" s="6" t="inlineStr"/>
-      <c r="AK15" s="11" t="inlineStr"/>
+      <c r="AK15" s="10" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
@@ -1769,7 +1766,7 @@
         <v>138.26</v>
       </c>
       <c r="AJ16" s="6" t="inlineStr"/>
-      <c r="AK16" s="11" t="inlineStr"/>
+      <c r="AK16" s="10" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
@@ -1904,11 +1901,11 @@
       <c r="AH17" s="7" t="n">
         <v>104.73</v>
       </c>
-      <c r="AI17" s="10" t="n">
+      <c r="AI17" s="9" t="n">
         <v>246.97</v>
       </c>
       <c r="AJ17" s="6" t="inlineStr"/>
-      <c r="AK17" s="11" t="inlineStr"/>
+      <c r="AK17" s="10" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
@@ -2047,7 +2044,7 @@
         <v>52.8</v>
       </c>
       <c r="AJ18" s="6" t="inlineStr"/>
-      <c r="AK18" s="11" t="inlineStr"/>
+      <c r="AK18" s="10" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
@@ -2182,11 +2179,11 @@
       <c r="AH19" s="8" t="n">
         <v>46.25</v>
       </c>
-      <c r="AI19" s="10" t="n">
+      <c r="AI19" s="9" t="n">
         <v>477.49</v>
       </c>
       <c r="AJ19" s="6" t="inlineStr"/>
-      <c r="AK19" s="11" t="inlineStr"/>
+      <c r="AK19" s="10" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="5" t="inlineStr">
@@ -2325,7 +2322,7 @@
         <v>149.08</v>
       </c>
       <c r="AJ20" s="6" t="inlineStr"/>
-      <c r="AK20" s="11" t="inlineStr"/>
+      <c r="AK20" s="10" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
@@ -2464,146 +2461,146 @@
         <v>157.64</v>
       </c>
       <c r="AJ21" s="6" t="inlineStr"/>
-      <c r="AK21" s="11" t="inlineStr"/>
+      <c r="AK21" s="10" t="inlineStr"/>
     </row>
     <row r="22">
-      <c r="A22" s="12" t="inlineStr">
+      <c r="A22" s="11" t="inlineStr">
         <is>
           <t>ZETA</t>
         </is>
       </c>
-      <c r="B22" s="13" t="n">
+      <c r="B22" s="12" t="n">
         <v>106.9</v>
       </c>
-      <c r="C22" s="13" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D22" s="13" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E22" s="13" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F22" s="13" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G22" s="13" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H22" s="13" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I22" s="13" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J22" s="13" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K22" s="14" t="n">
+      <c r="C22" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D22" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E22" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F22" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G22" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H22" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I22" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J22" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K22" s="13" t="n">
         <v>94.18000000000001</v>
       </c>
-      <c r="L22" s="14" t="n">
+      <c r="L22" s="13" t="n">
         <v>93.93000000000001</v>
       </c>
-      <c r="M22" s="14" t="n">
+      <c r="M22" s="13" t="n">
         <v>95.51000000000001</v>
       </c>
-      <c r="N22" s="14" t="n">
+      <c r="N22" s="13" t="n">
         <v>94.7</v>
       </c>
-      <c r="O22" s="13" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P22" s="14" t="n">
+      <c r="O22" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P22" s="13" t="n">
         <v>96.44</v>
       </c>
-      <c r="Q22" s="14" t="n">
+      <c r="Q22" s="13" t="n">
         <v>96.55</v>
       </c>
-      <c r="R22" s="14" t="n">
+      <c r="R22" s="13" t="n">
         <v>96.68000000000001</v>
       </c>
-      <c r="S22" s="14" t="n">
+      <c r="S22" s="13" t="n">
         <v>95.59</v>
       </c>
-      <c r="T22" s="14" t="n">
+      <c r="T22" s="13" t="n">
         <v>95.16</v>
       </c>
-      <c r="U22" s="13" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="V22" s="13" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="W22" s="13" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="X22" s="14" t="n">
+      <c r="U22" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="V22" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="W22" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="X22" s="13" t="n">
         <v>96.52</v>
       </c>
-      <c r="Y22" s="14" t="n">
+      <c r="Y22" s="13" t="n">
         <v>96.81</v>
       </c>
-      <c r="Z22" s="13" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AA22" s="14" t="n">
+      <c r="Z22" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AA22" s="13" t="n">
         <v>96.84</v>
       </c>
-      <c r="AB22" s="14" t="n">
+      <c r="AB22" s="13" t="n">
         <v>97.22</v>
       </c>
-      <c r="AC22" s="14" t="n">
+      <c r="AC22" s="13" t="n">
         <v>96.81</v>
       </c>
-      <c r="AD22" s="13" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AE22" s="14" t="n">
+      <c r="AD22" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AE22" s="13" t="n">
         <v>96.48</v>
       </c>
-      <c r="AF22" s="14" t="n">
+      <c r="AF22" s="13" t="n">
         <v>97.16</v>
       </c>
-      <c r="AG22" s="14" t="n">
+      <c r="AG22" s="13" t="n">
         <v>96.37</v>
       </c>
-      <c r="AH22" s="14" t="n">
+      <c r="AH22" s="13" t="n">
         <v>96.06</v>
       </c>
-      <c r="AI22" s="14" t="n">
+      <c r="AI22" s="13" t="n">
         <v>127.1</v>
       </c>
-      <c r="AJ22" s="13" t="inlineStr"/>
-      <c r="AK22" s="15" t="inlineStr"/>
+      <c r="AJ22" s="12" t="inlineStr"/>
+      <c r="AK22" s="14" t="inlineStr"/>
     </row>
     <row r="23"/>
     <row r="24"/>
@@ -2778,7 +2775,7 @@
           <t>OBSERVACIONES</t>
         </is>
       </c>
-      <c r="AK32" s="16" t="n"/>
+      <c r="AK32" s="15" t="n"/>
     </row>
     <row r="33">
       <c r="A33" s="5" t="inlineStr">
@@ -2849,16 +2846,16 @@
       <c r="P33" s="8" t="n">
         <v>56.76</v>
       </c>
-      <c r="Q33" s="9" t="n">
+      <c r="Q33" s="8" t="n">
         <v>55.79</v>
       </c>
-      <c r="R33" s="9" t="n">
+      <c r="R33" s="8" t="n">
         <v>54.35</v>
       </c>
       <c r="S33" s="8" t="n">
         <v>56.31</v>
       </c>
-      <c r="T33" s="9" t="n">
+      <c r="T33" s="8" t="n">
         <v>55.88</v>
       </c>
       <c r="U33" s="6" t="inlineStr">
@@ -2876,10 +2873,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="X33" s="9" t="n">
+      <c r="X33" s="8" t="n">
         <v>55.13</v>
       </c>
-      <c r="Y33" s="9" t="n">
+      <c r="Y33" s="8" t="n">
         <v>54.41</v>
       </c>
       <c r="Z33" s="6" t="inlineStr">
@@ -2887,13 +2884,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="AA33" s="9" t="n">
+      <c r="AA33" s="8" t="n">
         <v>55</v>
       </c>
-      <c r="AB33" s="9" t="n">
+      <c r="AB33" s="8" t="n">
         <v>55.06</v>
       </c>
-      <c r="AC33" s="9" t="n">
+      <c r="AC33" s="8" t="n">
         <v>54.2</v>
       </c>
       <c r="AD33" s="6" t="inlineStr">
@@ -2901,21 +2898,21 @@
           <t>-</t>
         </is>
       </c>
-      <c r="AE33" s="9" t="n">
+      <c r="AE33" s="8" t="n">
         <v>54.14</v>
       </c>
-      <c r="AF33" s="9" t="n">
+      <c r="AF33" s="8" t="n">
         <v>54.39</v>
       </c>
-      <c r="AG33" s="9" t="n">
+      <c r="AG33" s="8" t="n">
         <v>54.92</v>
       </c>
-      <c r="AH33" s="10" t="n">
+      <c r="AH33" s="8" t="n">
         <v>55.67</v>
       </c>
       <c r="AI33" s="6" t="inlineStr"/>
       <c r="AJ33" s="6" t="inlineStr"/>
-      <c r="AK33" s="17" t="n"/>
+      <c r="AK33" s="16" t="n"/>
     </row>
     <row r="34">
       <c r="A34" s="5" t="inlineStr">
@@ -2966,16 +2963,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="K34" s="9" t="n">
+      <c r="K34" s="17" t="n">
         <v>38.7</v>
       </c>
-      <c r="L34" s="9" t="n">
+      <c r="L34" s="17" t="n">
         <v>40.12</v>
       </c>
-      <c r="M34" s="9" t="n">
+      <c r="M34" s="17" t="n">
         <v>39.56</v>
       </c>
-      <c r="N34" s="9" t="n">
+      <c r="N34" s="17" t="n">
         <v>38.39</v>
       </c>
       <c r="O34" s="6" t="inlineStr">
@@ -2983,19 +2980,19 @@
           <t>-</t>
         </is>
       </c>
-      <c r="P34" s="9" t="n">
+      <c r="P34" s="17" t="n">
         <v>39.4</v>
       </c>
-      <c r="Q34" s="9" t="n">
+      <c r="Q34" s="17" t="n">
         <v>38.11</v>
       </c>
-      <c r="R34" s="9" t="n">
+      <c r="R34" s="17" t="n">
         <v>39.07</v>
       </c>
-      <c r="S34" s="9" t="n">
+      <c r="S34" s="17" t="n">
         <v>38.31</v>
       </c>
-      <c r="T34" s="9" t="n">
+      <c r="T34" s="17" t="n">
         <v>38.94</v>
       </c>
       <c r="U34" s="6" t="inlineStr">
@@ -3013,10 +3010,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="X34" s="9" t="n">
+      <c r="X34" s="17" t="n">
         <v>39.57</v>
       </c>
-      <c r="Y34" s="9" t="n">
+      <c r="Y34" s="17" t="n">
         <v>38.75</v>
       </c>
       <c r="Z34" s="6" t="inlineStr">
@@ -3024,13 +3021,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="AA34" s="9" t="n">
+      <c r="AA34" s="17" t="n">
         <v>39.83</v>
       </c>
-      <c r="AB34" s="9" t="n">
+      <c r="AB34" s="17" t="n">
         <v>39.13</v>
       </c>
-      <c r="AC34" s="9" t="n">
+      <c r="AC34" s="17" t="n">
         <v>38.66</v>
       </c>
       <c r="AD34" s="6" t="inlineStr">
@@ -3038,21 +3035,21 @@
           <t>-</t>
         </is>
       </c>
-      <c r="AE34" s="9" t="n">
+      <c r="AE34" s="17" t="n">
         <v>40.58</v>
       </c>
-      <c r="AF34" s="9" t="n">
+      <c r="AF34" s="17" t="n">
         <v>40.04</v>
       </c>
-      <c r="AG34" s="9" t="n">
+      <c r="AG34" s="17" t="n">
         <v>39.34</v>
       </c>
-      <c r="AH34" s="10" t="n">
+      <c r="AH34" s="17" t="n">
         <v>39.21</v>
       </c>
       <c r="AI34" s="6" t="inlineStr"/>
       <c r="AJ34" s="6" t="inlineStr"/>
-      <c r="AK34" s="17" t="n"/>
+      <c r="AK34" s="16" t="n"/>
     </row>
     <row r="35">
       <c r="A35" s="5" t="inlineStr">
@@ -3103,16 +3100,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="K35" s="9" t="n">
+      <c r="K35" s="17" t="n">
         <v>42.34</v>
       </c>
-      <c r="L35" s="9" t="n">
+      <c r="L35" s="17" t="n">
         <v>40.07</v>
       </c>
-      <c r="M35" s="9" t="n">
+      <c r="M35" s="17" t="n">
         <v>41.68</v>
       </c>
-      <c r="N35" s="9" t="n">
+      <c r="N35" s="17" t="n">
         <v>39.71</v>
       </c>
       <c r="O35" s="6" t="inlineStr">
@@ -3120,19 +3117,19 @@
           <t>-</t>
         </is>
       </c>
-      <c r="P35" s="9" t="n">
+      <c r="P35" s="17" t="n">
         <v>42.02</v>
       </c>
-      <c r="Q35" s="9" t="n">
+      <c r="Q35" s="17" t="n">
         <v>40.85</v>
       </c>
-      <c r="R35" s="9" t="n">
+      <c r="R35" s="17" t="n">
         <v>42.52</v>
       </c>
-      <c r="S35" s="9" t="n">
+      <c r="S35" s="17" t="n">
         <v>40.18</v>
       </c>
-      <c r="T35" s="9" t="n">
+      <c r="T35" s="17" t="n">
         <v>42.59</v>
       </c>
       <c r="U35" s="6" t="inlineStr">
@@ -3150,10 +3147,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="X35" s="9" t="n">
+      <c r="X35" s="17" t="n">
         <v>40.06</v>
       </c>
-      <c r="Y35" s="9" t="n">
+      <c r="Y35" s="17" t="n">
         <v>37.89</v>
       </c>
       <c r="Z35" s="6" t="inlineStr">
@@ -3161,13 +3158,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="AA35" s="9" t="n">
+      <c r="AA35" s="17" t="n">
         <v>41.15</v>
       </c>
-      <c r="AB35" s="9" t="n">
+      <c r="AB35" s="17" t="n">
         <v>38.92</v>
       </c>
-      <c r="AC35" s="9" t="n">
+      <c r="AC35" s="17" t="n">
         <v>39.38</v>
       </c>
       <c r="AD35" s="6" t="inlineStr">
@@ -3175,21 +3172,21 @@
           <t>-</t>
         </is>
       </c>
-      <c r="AE35" s="9" t="n">
+      <c r="AE35" s="17" t="n">
         <v>40.89</v>
       </c>
-      <c r="AF35" s="9" t="n">
+      <c r="AF35" s="17" t="n">
         <v>41.14</v>
       </c>
-      <c r="AG35" s="9" t="n">
+      <c r="AG35" s="17" t="n">
         <v>41.74</v>
       </c>
-      <c r="AH35" s="10" t="n">
+      <c r="AH35" s="17" t="n">
         <v>40.77</v>
       </c>
       <c r="AI35" s="6" t="inlineStr"/>
       <c r="AJ35" s="6" t="inlineStr"/>
-      <c r="AK35" s="17" t="n"/>
+      <c r="AK35" s="16" t="n"/>
     </row>
     <row r="36">
       <c r="A36" s="5" t="inlineStr">
@@ -3240,16 +3237,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="K36" s="9" t="n">
+      <c r="K36" s="17" t="n">
         <v>32.85</v>
       </c>
-      <c r="L36" s="9" t="n">
+      <c r="L36" s="17" t="n">
         <v>34.68</v>
       </c>
-      <c r="M36" s="9" t="n">
+      <c r="M36" s="17" t="n">
         <v>34.93</v>
       </c>
-      <c r="N36" s="9" t="n">
+      <c r="N36" s="17" t="n">
         <v>32.62</v>
       </c>
       <c r="O36" s="6" t="inlineStr">
@@ -3257,19 +3254,19 @@
           <t>-</t>
         </is>
       </c>
-      <c r="P36" s="9" t="n">
+      <c r="P36" s="17" t="n">
         <v>35.57</v>
       </c>
-      <c r="Q36" s="9" t="n">
+      <c r="Q36" s="17" t="n">
         <v>33.22</v>
       </c>
-      <c r="R36" s="9" t="n">
+      <c r="R36" s="17" t="n">
         <v>33.28</v>
       </c>
-      <c r="S36" s="9" t="n">
+      <c r="S36" s="17" t="n">
         <v>33.37</v>
       </c>
-      <c r="T36" s="9" t="n">
+      <c r="T36" s="17" t="n">
         <v>33.94</v>
       </c>
       <c r="U36" s="6" t="inlineStr">
@@ -3287,10 +3284,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="X36" s="9" t="n">
+      <c r="X36" s="17" t="n">
         <v>33.7</v>
       </c>
-      <c r="Y36" s="9" t="n">
+      <c r="Y36" s="17" t="n">
         <v>32.97</v>
       </c>
       <c r="Z36" s="6" t="inlineStr">
@@ -3298,13 +3295,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="AA36" s="9" t="n">
+      <c r="AA36" s="17" t="n">
         <v>33.07</v>
       </c>
-      <c r="AB36" s="9" t="n">
+      <c r="AB36" s="17" t="n">
         <v>33.43</v>
       </c>
-      <c r="AC36" s="9" t="n">
+      <c r="AC36" s="17" t="n">
         <v>33.04</v>
       </c>
       <c r="AD36" s="6" t="inlineStr">
@@ -3312,21 +3309,21 @@
           <t>-</t>
         </is>
       </c>
-      <c r="AE36" s="9" t="n">
+      <c r="AE36" s="17" t="n">
         <v>33.12</v>
       </c>
-      <c r="AF36" s="9" t="n">
+      <c r="AF36" s="17" t="n">
         <v>35.94</v>
       </c>
-      <c r="AG36" s="9" t="n">
+      <c r="AG36" s="17" t="n">
         <v>33.06</v>
       </c>
-      <c r="AH36" s="10" t="n">
+      <c r="AH36" s="17" t="n">
         <v>33.69</v>
       </c>
       <c r="AI36" s="6" t="inlineStr"/>
       <c r="AJ36" s="6" t="inlineStr"/>
-      <c r="AK36" s="17" t="n"/>
+      <c r="AK36" s="16" t="n"/>
     </row>
     <row r="37">
       <c r="A37" s="5" t="inlineStr">
@@ -3377,16 +3374,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="K37" s="9" t="n">
+      <c r="K37" s="17" t="n">
         <v>31.68</v>
       </c>
-      <c r="L37" s="9" t="n">
+      <c r="L37" s="17" t="n">
         <v>34.34</v>
       </c>
-      <c r="M37" s="9" t="n">
+      <c r="M37" s="17" t="n">
         <v>34.12</v>
       </c>
-      <c r="N37" s="9" t="n">
+      <c r="N37" s="17" t="n">
         <v>31.96</v>
       </c>
       <c r="O37" s="6" t="inlineStr">
@@ -3394,19 +3391,19 @@
           <t>-</t>
         </is>
       </c>
-      <c r="P37" s="9" t="n">
+      <c r="P37" s="17" t="n">
         <v>32.38</v>
       </c>
-      <c r="Q37" s="9" t="n">
+      <c r="Q37" s="17" t="n">
         <v>33.12</v>
       </c>
-      <c r="R37" s="9" t="n">
+      <c r="R37" s="17" t="n">
         <v>33.15</v>
       </c>
-      <c r="S37" s="9" t="n">
+      <c r="S37" s="17" t="n">
         <v>31.32</v>
       </c>
-      <c r="T37" s="9" t="n">
+      <c r="T37" s="17" t="n">
         <v>31.71</v>
       </c>
       <c r="U37" s="6" t="inlineStr">
@@ -3424,10 +3421,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="X37" s="9" t="n">
+      <c r="X37" s="17" t="n">
         <v>32.34</v>
       </c>
-      <c r="Y37" s="9" t="n">
+      <c r="Y37" s="17" t="n">
         <v>32.37</v>
       </c>
       <c r="Z37" s="6" t="inlineStr">
@@ -3435,13 +3432,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="AA37" s="9" t="n">
+      <c r="AA37" s="17" t="n">
         <v>32.65</v>
       </c>
-      <c r="AB37" s="9" t="n">
+      <c r="AB37" s="17" t="n">
         <v>33.45</v>
       </c>
-      <c r="AC37" s="9" t="n">
+      <c r="AC37" s="17" t="n">
         <v>31.78</v>
       </c>
       <c r="AD37" s="6" t="inlineStr">
@@ -3449,21 +3446,21 @@
           <t>-</t>
         </is>
       </c>
-      <c r="AE37" s="9" t="n">
+      <c r="AE37" s="17" t="n">
         <v>31.59</v>
       </c>
-      <c r="AF37" s="9" t="n">
+      <c r="AF37" s="17" t="n">
         <v>33.82</v>
       </c>
-      <c r="AG37" s="9" t="n">
+      <c r="AG37" s="17" t="n">
         <v>31.83</v>
       </c>
-      <c r="AH37" s="10" t="n">
+      <c r="AH37" s="17" t="n">
         <v>32.57</v>
       </c>
       <c r="AI37" s="6" t="inlineStr"/>
       <c r="AJ37" s="6" t="inlineStr"/>
-      <c r="AK37" s="17" t="n"/>
+      <c r="AK37" s="16" t="n"/>
     </row>
     <row r="38">
       <c r="A38" s="5" t="inlineStr">
@@ -3514,16 +3511,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="K38" s="9" t="n">
+      <c r="K38" s="17" t="n">
         <v>30.38</v>
       </c>
-      <c r="L38" s="9" t="n">
+      <c r="L38" s="17" t="n">
         <v>33.09</v>
       </c>
-      <c r="M38" s="9" t="n">
+      <c r="M38" s="17" t="n">
         <v>32.21</v>
       </c>
-      <c r="N38" s="9" t="n">
+      <c r="N38" s="17" t="n">
         <v>30.17</v>
       </c>
       <c r="O38" s="6" t="inlineStr">
@@ -3531,19 +3528,19 @@
           <t>-</t>
         </is>
       </c>
-      <c r="P38" s="9" t="n">
+      <c r="P38" s="17" t="n">
         <v>32.04</v>
       </c>
-      <c r="Q38" s="9" t="n">
+      <c r="Q38" s="17" t="n">
         <v>30.86</v>
       </c>
-      <c r="R38" s="9" t="n">
+      <c r="R38" s="17" t="n">
         <v>30.69</v>
       </c>
-      <c r="S38" s="9" t="n">
+      <c r="S38" s="17" t="n">
         <v>30.45</v>
       </c>
-      <c r="T38" s="9" t="n">
+      <c r="T38" s="17" t="n">
         <v>30.94</v>
       </c>
       <c r="U38" s="6" t="inlineStr">
@@ -3561,10 +3558,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="X38" s="9" t="n">
+      <c r="X38" s="17" t="n">
         <v>31.18</v>
       </c>
-      <c r="Y38" s="9" t="n">
+      <c r="Y38" s="17" t="n">
         <v>30.95</v>
       </c>
       <c r="Z38" s="6" t="inlineStr">
@@ -3572,13 +3569,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="AA38" s="9" t="n">
+      <c r="AA38" s="17" t="n">
         <v>30.83</v>
       </c>
-      <c r="AB38" s="9" t="n">
+      <c r="AB38" s="17" t="n">
         <v>31.03</v>
       </c>
-      <c r="AC38" s="9" t="n">
+      <c r="AC38" s="17" t="n">
         <v>30.71</v>
       </c>
       <c r="AD38" s="6" t="inlineStr">
@@ -3586,21 +3583,21 @@
           <t>-</t>
         </is>
       </c>
-      <c r="AE38" s="9" t="n">
+      <c r="AE38" s="17" t="n">
         <v>30.44</v>
       </c>
-      <c r="AF38" s="9" t="n">
+      <c r="AF38" s="17" t="n">
         <v>33.05</v>
       </c>
-      <c r="AG38" s="9" t="n">
+      <c r="AG38" s="17" t="n">
         <v>30.7</v>
       </c>
-      <c r="AH38" s="10" t="n">
+      <c r="AH38" s="17" t="n">
         <v>31.16</v>
       </c>
       <c r="AI38" s="6" t="inlineStr"/>
       <c r="AJ38" s="6" t="inlineStr"/>
-      <c r="AK38" s="17" t="n"/>
+      <c r="AK38" s="16" t="n"/>
     </row>
     <row r="39">
       <c r="A39" s="5" t="inlineStr">
@@ -3651,16 +3648,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="K39" s="9" t="n">
+      <c r="K39" s="17" t="n">
         <v>29.23</v>
       </c>
-      <c r="L39" s="9" t="n">
+      <c r="L39" s="17" t="n">
         <v>29.27</v>
       </c>
-      <c r="M39" s="9" t="n">
+      <c r="M39" s="17" t="n">
         <v>29.72</v>
       </c>
-      <c r="N39" s="9" t="n">
+      <c r="N39" s="17" t="n">
         <v>28.44</v>
       </c>
       <c r="O39" s="6" t="inlineStr">
@@ -3668,19 +3665,19 @@
           <t>-</t>
         </is>
       </c>
-      <c r="P39" s="9" t="n">
+      <c r="P39" s="17" t="n">
         <v>29.66</v>
       </c>
-      <c r="Q39" s="9" t="n">
+      <c r="Q39" s="17" t="n">
         <v>28.68</v>
       </c>
-      <c r="R39" s="9" t="n">
+      <c r="R39" s="17" t="n">
         <v>29.01</v>
       </c>
-      <c r="S39" s="9" t="n">
+      <c r="S39" s="17" t="n">
         <v>28.72</v>
       </c>
-      <c r="T39" s="9" t="n">
+      <c r="T39" s="17" t="n">
         <v>29.25</v>
       </c>
       <c r="U39" s="6" t="inlineStr">
@@ -3698,10 +3695,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="X39" s="9" t="n">
+      <c r="X39" s="17" t="n">
         <v>29.75</v>
       </c>
-      <c r="Y39" s="9" t="n">
+      <c r="Y39" s="17" t="n">
         <v>29.47</v>
       </c>
       <c r="Z39" s="6" t="inlineStr">
@@ -3709,13 +3706,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="AA39" s="9" t="n">
+      <c r="AA39" s="17" t="n">
         <v>29.05</v>
       </c>
-      <c r="AB39" s="9" t="n">
+      <c r="AB39" s="17" t="n">
         <v>29.35</v>
       </c>
-      <c r="AC39" s="9" t="n">
+      <c r="AC39" s="17" t="n">
         <v>28.38</v>
       </c>
       <c r="AD39" s="6" t="inlineStr">
@@ -3723,21 +3720,21 @@
           <t>-</t>
         </is>
       </c>
-      <c r="AE39" s="9" t="n">
+      <c r="AE39" s="17" t="n">
         <v>29.33</v>
       </c>
-      <c r="AF39" s="9" t="n">
+      <c r="AF39" s="17" t="n">
         <v>29.64</v>
       </c>
-      <c r="AG39" s="9" t="n">
+      <c r="AG39" s="17" t="n">
         <v>29.19</v>
       </c>
-      <c r="AH39" s="10" t="n">
+      <c r="AH39" s="17" t="n">
         <v>29.19</v>
       </c>
       <c r="AI39" s="6" t="inlineStr"/>
       <c r="AJ39" s="6" t="inlineStr"/>
-      <c r="AK39" s="17" t="n"/>
+      <c r="AK39" s="16" t="n"/>
     </row>
     <row r="40">
       <c r="A40" s="5" t="inlineStr">
@@ -3788,16 +3785,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="K40" s="9" t="n">
+      <c r="K40" s="17" t="n">
         <v>26.49</v>
       </c>
-      <c r="L40" s="9" t="n">
+      <c r="L40" s="17" t="n">
         <v>26.61</v>
       </c>
-      <c r="M40" s="9" t="n">
+      <c r="M40" s="17" t="n">
         <v>26.76</v>
       </c>
-      <c r="N40" s="9" t="n">
+      <c r="N40" s="17" t="n">
         <v>26.86</v>
       </c>
       <c r="O40" s="6" t="inlineStr">
@@ -3805,19 +3802,19 @@
           <t>-</t>
         </is>
       </c>
-      <c r="P40" s="9" t="n">
+      <c r="P40" s="17" t="n">
         <v>26.77</v>
       </c>
-      <c r="Q40" s="9" t="n">
+      <c r="Q40" s="17" t="n">
         <v>26.84</v>
       </c>
-      <c r="R40" s="9" t="n">
+      <c r="R40" s="17" t="n">
         <v>27.65</v>
       </c>
-      <c r="S40" s="9" t="n">
+      <c r="S40" s="17" t="n">
         <v>26.75</v>
       </c>
-      <c r="T40" s="9" t="n">
+      <c r="T40" s="17" t="n">
         <v>26.91</v>
       </c>
       <c r="U40" s="6" t="inlineStr">
@@ -3835,10 +3832,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="X40" s="9" t="n">
+      <c r="X40" s="17" t="n">
         <v>26.82</v>
       </c>
-      <c r="Y40" s="9" t="n">
+      <c r="Y40" s="17" t="n">
         <v>26.87</v>
       </c>
       <c r="Z40" s="6" t="inlineStr">
@@ -3846,13 +3843,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="AA40" s="9" t="n">
+      <c r="AA40" s="17" t="n">
         <v>26.65</v>
       </c>
-      <c r="AB40" s="9" t="n">
+      <c r="AB40" s="17" t="n">
         <v>26.82</v>
       </c>
-      <c r="AC40" s="9" t="n">
+      <c r="AC40" s="17" t="n">
         <v>26.56</v>
       </c>
       <c r="AD40" s="6" t="inlineStr">
@@ -3860,21 +3857,21 @@
           <t>-</t>
         </is>
       </c>
-      <c r="AE40" s="9" t="n">
+      <c r="AE40" s="17" t="n">
         <v>26.93</v>
       </c>
-      <c r="AF40" s="9" t="n">
+      <c r="AF40" s="17" t="n">
         <v>26.84</v>
       </c>
-      <c r="AG40" s="9" t="n">
+      <c r="AG40" s="17" t="n">
         <v>26.69</v>
       </c>
-      <c r="AH40" s="10" t="n">
+      <c r="AH40" s="17" t="n">
         <v>26.81</v>
       </c>
       <c r="AI40" s="6" t="inlineStr"/>
       <c r="AJ40" s="6" t="inlineStr"/>
-      <c r="AK40" s="17" t="n"/>
+      <c r="AK40" s="16" t="n"/>
     </row>
     <row r="41">
       <c r="A41" s="5" t="inlineStr">
@@ -3925,16 +3922,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="K41" s="9" t="n">
+      <c r="K41" s="17" t="n">
         <v>26.63</v>
       </c>
-      <c r="L41" s="9" t="n">
+      <c r="L41" s="17" t="n">
         <v>26.96</v>
       </c>
-      <c r="M41" s="9" t="n">
+      <c r="M41" s="17" t="n">
         <v>26.84</v>
       </c>
-      <c r="N41" s="9" t="n">
+      <c r="N41" s="17" t="n">
         <v>26.93</v>
       </c>
       <c r="O41" s="6" t="inlineStr">
@@ -3942,19 +3939,19 @@
           <t>-</t>
         </is>
       </c>
-      <c r="P41" s="9" t="n">
+      <c r="P41" s="17" t="n">
         <v>27.04</v>
       </c>
-      <c r="Q41" s="9" t="n">
+      <c r="Q41" s="17" t="n">
         <v>26.67</v>
       </c>
-      <c r="R41" s="9" t="n">
+      <c r="R41" s="17" t="n">
         <v>26.77</v>
       </c>
-      <c r="S41" s="9" t="n">
+      <c r="S41" s="17" t="n">
         <v>26.6</v>
       </c>
-      <c r="T41" s="9" t="n">
+      <c r="T41" s="17" t="n">
         <v>27.2</v>
       </c>
       <c r="U41" s="6" t="inlineStr">
@@ -3972,10 +3969,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="X41" s="9" t="n">
+      <c r="X41" s="17" t="n">
         <v>26.92</v>
       </c>
-      <c r="Y41" s="9" t="n">
+      <c r="Y41" s="17" t="n">
         <v>27.06</v>
       </c>
       <c r="Z41" s="6" t="inlineStr">
@@ -3983,13 +3980,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="AA41" s="9" t="n">
+      <c r="AA41" s="17" t="n">
         <v>26.83</v>
       </c>
-      <c r="AB41" s="9" t="n">
+      <c r="AB41" s="17" t="n">
         <v>26.85</v>
       </c>
-      <c r="AC41" s="9" t="n">
+      <c r="AC41" s="17" t="n">
         <v>26.68</v>
       </c>
       <c r="AD41" s="6" t="inlineStr">
@@ -3997,21 +3994,21 @@
           <t>-</t>
         </is>
       </c>
-      <c r="AE41" s="9" t="n">
+      <c r="AE41" s="17" t="n">
         <v>27.21</v>
       </c>
-      <c r="AF41" s="9" t="n">
+      <c r="AF41" s="17" t="n">
         <v>27.19</v>
       </c>
-      <c r="AG41" s="9" t="n">
+      <c r="AG41" s="17" t="n">
         <v>26.73</v>
       </c>
-      <c r="AH41" s="10" t="n">
+      <c r="AH41" s="17" t="n">
         <v>26.89</v>
       </c>
       <c r="AI41" s="6" t="inlineStr"/>
       <c r="AJ41" s="6" t="inlineStr"/>
-      <c r="AK41" s="17" t="n"/>
+      <c r="AK41" s="16" t="n"/>
     </row>
     <row r="42">
       <c r="A42" s="5" t="inlineStr">
@@ -4062,16 +4059,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="K42" s="9" t="n">
+      <c r="K42" s="17" t="n">
         <v>27.35</v>
       </c>
-      <c r="L42" s="9" t="n">
+      <c r="L42" s="17" t="n">
         <v>27.68</v>
       </c>
-      <c r="M42" s="9" t="n">
+      <c r="M42" s="17" t="n">
         <v>26.97</v>
       </c>
-      <c r="N42" s="9" t="n">
+      <c r="N42" s="17" t="n">
         <v>27.55</v>
       </c>
       <c r="O42" s="6" t="inlineStr">
@@ -4079,19 +4076,19 @@
           <t>-</t>
         </is>
       </c>
-      <c r="P42" s="9" t="n">
+      <c r="P42" s="17" t="n">
         <v>28.86</v>
       </c>
-      <c r="Q42" s="9" t="n">
+      <c r="Q42" s="17" t="n">
         <v>27.39</v>
       </c>
-      <c r="R42" s="9" t="n">
+      <c r="R42" s="17" t="n">
         <v>29.27</v>
       </c>
-      <c r="S42" s="9" t="n">
+      <c r="S42" s="17" t="n">
         <v>27.56</v>
       </c>
-      <c r="T42" s="9" t="n">
+      <c r="T42" s="17" t="n">
         <v>28.35</v>
       </c>
       <c r="U42" s="6" t="inlineStr">
@@ -4109,10 +4106,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="X42" s="9" t="n">
+      <c r="X42" s="17" t="n">
         <v>27.35</v>
       </c>
-      <c r="Y42" s="9" t="n">
+      <c r="Y42" s="17" t="n">
         <v>27.39</v>
       </c>
       <c r="Z42" s="6" t="inlineStr">
@@ -4120,13 +4117,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="AA42" s="9" t="n">
+      <c r="AA42" s="17" t="n">
         <v>27.07</v>
       </c>
-      <c r="AB42" s="9" t="n">
+      <c r="AB42" s="17" t="n">
         <v>27.45</v>
       </c>
-      <c r="AC42" s="9" t="n">
+      <c r="AC42" s="17" t="n">
         <v>27.13</v>
       </c>
       <c r="AD42" s="6" t="inlineStr">
@@ -4134,67 +4131,67 @@
           <t>-</t>
         </is>
       </c>
-      <c r="AE42" s="9" t="n">
+      <c r="AE42" s="17" t="n">
         <v>27.25</v>
       </c>
-      <c r="AF42" s="9" t="n">
+      <c r="AF42" s="17" t="n">
         <v>27.71</v>
       </c>
-      <c r="AG42" s="9" t="n">
+      <c r="AG42" s="17" t="n">
         <v>27.53</v>
       </c>
-      <c r="AH42" s="10" t="n">
+      <c r="AH42" s="17" t="n">
         <v>27.64</v>
       </c>
       <c r="AI42" s="6" t="inlineStr"/>
       <c r="AJ42" s="6" t="inlineStr"/>
-      <c r="AK42" s="17" t="n"/>
+      <c r="AK42" s="16" t="n"/>
     </row>
     <row r="43">
-      <c r="A43" s="12" t="inlineStr">
+      <c r="A43" s="11" t="inlineStr">
         <is>
           <t>TELECIUDADANA</t>
         </is>
       </c>
-      <c r="B43" s="13" t="n">
+      <c r="B43" s="12" t="n">
         <v>681.25</v>
       </c>
-      <c r="C43" s="13" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D43" s="13" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E43" s="13" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F43" s="13" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G43" s="13" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H43" s="13" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I43" s="13" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J43" s="13" t="inlineStr">
+      <c r="C43" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D43" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E43" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F43" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G43" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H43" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I43" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J43" s="12" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -4211,7 +4208,7 @@
       <c r="N43" s="18" t="n">
         <v>27.63</v>
       </c>
-      <c r="O43" s="13" t="inlineStr">
+      <c r="O43" s="12" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -4231,17 +4228,17 @@
       <c r="T43" s="18" t="n">
         <v>27.61</v>
       </c>
-      <c r="U43" s="13" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="V43" s="13" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="W43" s="13" t="inlineStr">
+      <c r="U43" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="V43" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="W43" s="12" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -4252,7 +4249,7 @@
       <c r="Y43" s="18" t="n">
         <v>27.51</v>
       </c>
-      <c r="Z43" s="13" t="inlineStr">
+      <c r="Z43" s="12" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -4266,7 +4263,7 @@
       <c r="AC43" s="18" t="n">
         <v>27.33</v>
       </c>
-      <c r="AD43" s="13" t="inlineStr">
+      <c r="AD43" s="12" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -4280,12 +4277,12 @@
       <c r="AG43" s="18" t="n">
         <v>27.44</v>
       </c>
-      <c r="AH43" s="19" t="n">
+      <c r="AH43" s="18" t="n">
         <v>27.59</v>
       </c>
-      <c r="AI43" s="13" t="inlineStr"/>
-      <c r="AJ43" s="13" t="inlineStr"/>
-      <c r="AK43" s="20" t="n"/>
+      <c r="AI43" s="12" t="inlineStr"/>
+      <c r="AJ43" s="12" t="inlineStr"/>
+      <c r="AK43" s="19" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="28">

--- a/ReportesUnificados/zamora_ReporteUnificado.xlsx
+++ b/ReportesUnificados/zamora_ReporteUnificado.xlsx
@@ -177,7 +177,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -207,6 +207,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -226,8 +229,14 @@
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="13" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
@@ -1071,7 +1080,12 @@
         <v>485.74</v>
       </c>
       <c r="AJ11" s="6" t="inlineStr"/>
-      <c r="AK11" s="10" t="inlineStr"/>
+      <c r="AK11" s="10" t="inlineStr">
+        <is>
+          <t>Opera con ancho de banda mayor a lo
+autorizado(medición automática)</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
@@ -1210,7 +1224,7 @@
         <v>101.16</v>
       </c>
       <c r="AJ12" s="6" t="inlineStr"/>
-      <c r="AK12" s="10" t="inlineStr"/>
+      <c r="AK12" s="11" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
@@ -1349,7 +1363,7 @@
         <v>104.99</v>
       </c>
       <c r="AJ13" s="6" t="inlineStr"/>
-      <c r="AK13" s="10" t="inlineStr"/>
+      <c r="AK13" s="11" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
@@ -1488,7 +1502,7 @@
         <v>119.83</v>
       </c>
       <c r="AJ14" s="6" t="inlineStr"/>
-      <c r="AK14" s="10" t="inlineStr"/>
+      <c r="AK14" s="11" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
@@ -1627,7 +1641,7 @@
         <v>156.6</v>
       </c>
       <c r="AJ15" s="6" t="inlineStr"/>
-      <c r="AK15" s="10" t="inlineStr"/>
+      <c r="AK15" s="11" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
@@ -1766,7 +1780,7 @@
         <v>138.26</v>
       </c>
       <c r="AJ16" s="6" t="inlineStr"/>
-      <c r="AK16" s="10" t="inlineStr"/>
+      <c r="AK16" s="11" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
@@ -1905,7 +1919,12 @@
         <v>246.97</v>
       </c>
       <c r="AJ17" s="6" t="inlineStr"/>
-      <c r="AK17" s="10" t="inlineStr"/>
+      <c r="AK17" s="10" t="inlineStr">
+        <is>
+          <t>Opera con ancho de banda mayor a lo
+autorizado(medición automática)</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
@@ -2044,7 +2063,7 @@
         <v>52.8</v>
       </c>
       <c r="AJ18" s="6" t="inlineStr"/>
-      <c r="AK18" s="10" t="inlineStr"/>
+      <c r="AK18" s="11" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
@@ -2183,7 +2202,12 @@
         <v>477.49</v>
       </c>
       <c r="AJ19" s="6" t="inlineStr"/>
-      <c r="AK19" s="10" t="inlineStr"/>
+      <c r="AK19" s="10" t="inlineStr">
+        <is>
+          <t>Opera con ancho de banda mayor a lo
+autorizado(medición automática)</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="5" t="inlineStr">
@@ -2322,7 +2346,7 @@
         <v>149.08</v>
       </c>
       <c r="AJ20" s="6" t="inlineStr"/>
-      <c r="AK20" s="10" t="inlineStr"/>
+      <c r="AK20" s="11" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
@@ -2461,146 +2485,146 @@
         <v>157.64</v>
       </c>
       <c r="AJ21" s="6" t="inlineStr"/>
-      <c r="AK21" s="10" t="inlineStr"/>
+      <c r="AK21" s="11" t="inlineStr"/>
     </row>
     <row r="22">
-      <c r="A22" s="11" t="inlineStr">
+      <c r="A22" s="12" t="inlineStr">
         <is>
           <t>ZETA</t>
         </is>
       </c>
-      <c r="B22" s="12" t="n">
+      <c r="B22" s="13" t="n">
         <v>106.9</v>
       </c>
-      <c r="C22" s="12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D22" s="12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E22" s="12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F22" s="12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G22" s="12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H22" s="12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I22" s="12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J22" s="12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K22" s="13" t="n">
+      <c r="C22" s="13" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D22" s="13" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E22" s="13" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F22" s="13" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G22" s="13" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H22" s="13" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I22" s="13" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J22" s="13" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K22" s="14" t="n">
         <v>94.18000000000001</v>
       </c>
-      <c r="L22" s="13" t="n">
+      <c r="L22" s="14" t="n">
         <v>93.93000000000001</v>
       </c>
-      <c r="M22" s="13" t="n">
+      <c r="M22" s="14" t="n">
         <v>95.51000000000001</v>
       </c>
-      <c r="N22" s="13" t="n">
+      <c r="N22" s="14" t="n">
         <v>94.7</v>
       </c>
-      <c r="O22" s="12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P22" s="13" t="n">
+      <c r="O22" s="13" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P22" s="14" t="n">
         <v>96.44</v>
       </c>
-      <c r="Q22" s="13" t="n">
+      <c r="Q22" s="14" t="n">
         <v>96.55</v>
       </c>
-      <c r="R22" s="13" t="n">
+      <c r="R22" s="14" t="n">
         <v>96.68000000000001</v>
       </c>
-      <c r="S22" s="13" t="n">
+      <c r="S22" s="14" t="n">
         <v>95.59</v>
       </c>
-      <c r="T22" s="13" t="n">
+      <c r="T22" s="14" t="n">
         <v>95.16</v>
       </c>
-      <c r="U22" s="12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="V22" s="12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="W22" s="12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="X22" s="13" t="n">
+      <c r="U22" s="13" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="V22" s="13" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="W22" s="13" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="X22" s="14" t="n">
         <v>96.52</v>
       </c>
-      <c r="Y22" s="13" t="n">
+      <c r="Y22" s="14" t="n">
         <v>96.81</v>
       </c>
-      <c r="Z22" s="12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AA22" s="13" t="n">
+      <c r="Z22" s="13" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AA22" s="14" t="n">
         <v>96.84</v>
       </c>
-      <c r="AB22" s="13" t="n">
+      <c r="AB22" s="14" t="n">
         <v>97.22</v>
       </c>
-      <c r="AC22" s="13" t="n">
+      <c r="AC22" s="14" t="n">
         <v>96.81</v>
       </c>
-      <c r="AD22" s="12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AE22" s="13" t="n">
+      <c r="AD22" s="13" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AE22" s="14" t="n">
         <v>96.48</v>
       </c>
-      <c r="AF22" s="13" t="n">
+      <c r="AF22" s="14" t="n">
         <v>97.16</v>
       </c>
-      <c r="AG22" s="13" t="n">
+      <c r="AG22" s="14" t="n">
         <v>96.37</v>
       </c>
-      <c r="AH22" s="13" t="n">
+      <c r="AH22" s="14" t="n">
         <v>96.06</v>
       </c>
-      <c r="AI22" s="13" t="n">
+      <c r="AI22" s="14" t="n">
         <v>127.1</v>
       </c>
-      <c r="AJ22" s="12" t="inlineStr"/>
-      <c r="AK22" s="14" t="inlineStr"/>
+      <c r="AJ22" s="13" t="inlineStr"/>
+      <c r="AK22" s="15" t="inlineStr"/>
     </row>
     <row r="23"/>
     <row r="24"/>
@@ -2775,7 +2799,7 @@
           <t>OBSERVACIONES</t>
         </is>
       </c>
-      <c r="AK32" s="15" t="n"/>
+      <c r="AK32" s="16" t="n"/>
     </row>
     <row r="33">
       <c r="A33" s="5" t="inlineStr">
@@ -2912,9 +2936,9 @@
       </c>
       <c r="AI33" s="6" t="inlineStr"/>
       <c r="AJ33" s="6" t="inlineStr"/>
-      <c r="AK33" s="16" t="n"/>
+      <c r="AK33" s="17" t="n"/>
     </row>
-    <row r="34">
+    <row r="34" ht="15" customHeight="1">
       <c r="A34" s="5" t="inlineStr">
         <is>
           <t>TELEVISION DEL PACIFICO</t>
@@ -2963,16 +2987,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="K34" s="17" t="n">
+      <c r="K34" s="18" t="n">
         <v>38.7</v>
       </c>
-      <c r="L34" s="17" t="n">
+      <c r="L34" s="18" t="n">
         <v>40.12</v>
       </c>
-      <c r="M34" s="17" t="n">
+      <c r="M34" s="18" t="n">
         <v>39.56</v>
       </c>
-      <c r="N34" s="17" t="n">
+      <c r="N34" s="18" t="n">
         <v>38.39</v>
       </c>
       <c r="O34" s="6" t="inlineStr">
@@ -2980,19 +3004,19 @@
           <t>-</t>
         </is>
       </c>
-      <c r="P34" s="17" t="n">
+      <c r="P34" s="18" t="n">
         <v>39.4</v>
       </c>
-      <c r="Q34" s="17" t="n">
+      <c r="Q34" s="18" t="n">
         <v>38.11</v>
       </c>
-      <c r="R34" s="17" t="n">
+      <c r="R34" s="18" t="n">
         <v>39.07</v>
       </c>
-      <c r="S34" s="17" t="n">
+      <c r="S34" s="18" t="n">
         <v>38.31</v>
       </c>
-      <c r="T34" s="17" t="n">
+      <c r="T34" s="18" t="n">
         <v>38.94</v>
       </c>
       <c r="U34" s="6" t="inlineStr">
@@ -3010,10 +3034,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="X34" s="17" t="n">
+      <c r="X34" s="18" t="n">
         <v>39.57</v>
       </c>
-      <c r="Y34" s="17" t="n">
+      <c r="Y34" s="18" t="n">
         <v>38.75</v>
       </c>
       <c r="Z34" s="6" t="inlineStr">
@@ -3021,13 +3045,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="AA34" s="17" t="n">
+      <c r="AA34" s="18" t="n">
         <v>39.83</v>
       </c>
-      <c r="AB34" s="17" t="n">
+      <c r="AB34" s="18" t="n">
         <v>39.13</v>
       </c>
-      <c r="AC34" s="17" t="n">
+      <c r="AC34" s="18" t="n">
         <v>38.66</v>
       </c>
       <c r="AD34" s="6" t="inlineStr">
@@ -3035,23 +3059,27 @@
           <t>-</t>
         </is>
       </c>
-      <c r="AE34" s="17" t="n">
+      <c r="AE34" s="18" t="n">
         <v>40.58</v>
       </c>
-      <c r="AF34" s="17" t="n">
+      <c r="AF34" s="18" t="n">
         <v>40.04</v>
       </c>
-      <c r="AG34" s="17" t="n">
+      <c r="AG34" s="18" t="n">
         <v>39.34</v>
       </c>
-      <c r="AH34" s="17" t="n">
+      <c r="AH34" s="18" t="n">
         <v>39.21</v>
       </c>
       <c r="AI34" s="6" t="inlineStr"/>
-      <c r="AJ34" s="6" t="inlineStr"/>
-      <c r="AK34" s="16" t="n"/>
+      <c r="AJ34" s="19" t="inlineStr">
+        <is>
+          <t>Niveles por debajo del borde del área de cobertura principal y secundaria</t>
+        </is>
+      </c>
+      <c r="AK34" s="17" t="n"/>
     </row>
-    <row r="35">
+    <row r="35" ht="15" customHeight="1">
       <c r="A35" s="5" t="inlineStr">
         <is>
           <t>TV CATOLICA LOS ENCUENTROS</t>
@@ -3100,16 +3128,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="K35" s="17" t="n">
+      <c r="K35" s="18" t="n">
         <v>42.34</v>
       </c>
-      <c r="L35" s="17" t="n">
+      <c r="L35" s="18" t="n">
         <v>40.07</v>
       </c>
-      <c r="M35" s="17" t="n">
+      <c r="M35" s="18" t="n">
         <v>41.68</v>
       </c>
-      <c r="N35" s="17" t="n">
+      <c r="N35" s="18" t="n">
         <v>39.71</v>
       </c>
       <c r="O35" s="6" t="inlineStr">
@@ -3117,19 +3145,19 @@
           <t>-</t>
         </is>
       </c>
-      <c r="P35" s="17" t="n">
+      <c r="P35" s="18" t="n">
         <v>42.02</v>
       </c>
-      <c r="Q35" s="17" t="n">
+      <c r="Q35" s="18" t="n">
         <v>40.85</v>
       </c>
-      <c r="R35" s="17" t="n">
+      <c r="R35" s="18" t="n">
         <v>42.52</v>
       </c>
-      <c r="S35" s="17" t="n">
+      <c r="S35" s="18" t="n">
         <v>40.18</v>
       </c>
-      <c r="T35" s="17" t="n">
+      <c r="T35" s="18" t="n">
         <v>42.59</v>
       </c>
       <c r="U35" s="6" t="inlineStr">
@@ -3147,10 +3175,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="X35" s="17" t="n">
+      <c r="X35" s="18" t="n">
         <v>40.06</v>
       </c>
-      <c r="Y35" s="17" t="n">
+      <c r="Y35" s="18" t="n">
         <v>37.89</v>
       </c>
       <c r="Z35" s="6" t="inlineStr">
@@ -3158,13 +3186,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="AA35" s="17" t="n">
+      <c r="AA35" s="18" t="n">
         <v>41.15</v>
       </c>
-      <c r="AB35" s="17" t="n">
+      <c r="AB35" s="18" t="n">
         <v>38.92</v>
       </c>
-      <c r="AC35" s="17" t="n">
+      <c r="AC35" s="18" t="n">
         <v>39.38</v>
       </c>
       <c r="AD35" s="6" t="inlineStr">
@@ -3172,23 +3200,27 @@
           <t>-</t>
         </is>
       </c>
-      <c r="AE35" s="17" t="n">
+      <c r="AE35" s="18" t="n">
         <v>40.89</v>
       </c>
-      <c r="AF35" s="17" t="n">
+      <c r="AF35" s="18" t="n">
         <v>41.14</v>
       </c>
-      <c r="AG35" s="17" t="n">
+      <c r="AG35" s="18" t="n">
         <v>41.74</v>
       </c>
-      <c r="AH35" s="17" t="n">
+      <c r="AH35" s="18" t="n">
         <v>40.77</v>
       </c>
       <c r="AI35" s="6" t="inlineStr"/>
-      <c r="AJ35" s="6" t="inlineStr"/>
-      <c r="AK35" s="16" t="n"/>
+      <c r="AJ35" s="19" t="inlineStr">
+        <is>
+          <t>Niveles por debajo del borde del área de cobertura principal y secundaria</t>
+        </is>
+      </c>
+      <c r="AK35" s="17" t="n"/>
     </row>
-    <row r="36">
+    <row r="36" ht="15" customHeight="1">
       <c r="A36" s="5" t="inlineStr">
         <is>
           <t>ECUADOR TV</t>
@@ -3237,16 +3269,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="K36" s="17" t="n">
+      <c r="K36" s="18" t="n">
         <v>32.85</v>
       </c>
-      <c r="L36" s="17" t="n">
+      <c r="L36" s="18" t="n">
         <v>34.68</v>
       </c>
-      <c r="M36" s="17" t="n">
+      <c r="M36" s="18" t="n">
         <v>34.93</v>
       </c>
-      <c r="N36" s="17" t="n">
+      <c r="N36" s="18" t="n">
         <v>32.62</v>
       </c>
       <c r="O36" s="6" t="inlineStr">
@@ -3254,19 +3286,19 @@
           <t>-</t>
         </is>
       </c>
-      <c r="P36" s="17" t="n">
+      <c r="P36" s="18" t="n">
         <v>35.57</v>
       </c>
-      <c r="Q36" s="17" t="n">
+      <c r="Q36" s="18" t="n">
         <v>33.22</v>
       </c>
-      <c r="R36" s="17" t="n">
+      <c r="R36" s="18" t="n">
         <v>33.28</v>
       </c>
-      <c r="S36" s="17" t="n">
+      <c r="S36" s="18" t="n">
         <v>33.37</v>
       </c>
-      <c r="T36" s="17" t="n">
+      <c r="T36" s="18" t="n">
         <v>33.94</v>
       </c>
       <c r="U36" s="6" t="inlineStr">
@@ -3284,10 +3316,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="X36" s="17" t="n">
+      <c r="X36" s="18" t="n">
         <v>33.7</v>
       </c>
-      <c r="Y36" s="17" t="n">
+      <c r="Y36" s="18" t="n">
         <v>32.97</v>
       </c>
       <c r="Z36" s="6" t="inlineStr">
@@ -3295,13 +3327,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="AA36" s="17" t="n">
+      <c r="AA36" s="18" t="n">
         <v>33.07</v>
       </c>
-      <c r="AB36" s="17" t="n">
+      <c r="AB36" s="18" t="n">
         <v>33.43</v>
       </c>
-      <c r="AC36" s="17" t="n">
+      <c r="AC36" s="18" t="n">
         <v>33.04</v>
       </c>
       <c r="AD36" s="6" t="inlineStr">
@@ -3309,23 +3341,27 @@
           <t>-</t>
         </is>
       </c>
-      <c r="AE36" s="17" t="n">
+      <c r="AE36" s="18" t="n">
         <v>33.12</v>
       </c>
-      <c r="AF36" s="17" t="n">
+      <c r="AF36" s="18" t="n">
         <v>35.94</v>
       </c>
-      <c r="AG36" s="17" t="n">
+      <c r="AG36" s="18" t="n">
         <v>33.06</v>
       </c>
-      <c r="AH36" s="17" t="n">
+      <c r="AH36" s="18" t="n">
         <v>33.69</v>
       </c>
       <c r="AI36" s="6" t="inlineStr"/>
-      <c r="AJ36" s="6" t="inlineStr"/>
-      <c r="AK36" s="16" t="n"/>
+      <c r="AJ36" s="19" t="inlineStr">
+        <is>
+          <t>Niveles por debajo del borde del área de cobertura principal y secundaria</t>
+        </is>
+      </c>
+      <c r="AK36" s="17" t="n"/>
     </row>
-    <row r="37">
+    <row r="37" ht="15" customHeight="1">
       <c r="A37" s="5" t="inlineStr">
         <is>
           <t>UV TELEVISION</t>
@@ -3374,16 +3410,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="K37" s="17" t="n">
+      <c r="K37" s="18" t="n">
         <v>31.68</v>
       </c>
-      <c r="L37" s="17" t="n">
+      <c r="L37" s="18" t="n">
         <v>34.34</v>
       </c>
-      <c r="M37" s="17" t="n">
+      <c r="M37" s="18" t="n">
         <v>34.12</v>
       </c>
-      <c r="N37" s="17" t="n">
+      <c r="N37" s="18" t="n">
         <v>31.96</v>
       </c>
       <c r="O37" s="6" t="inlineStr">
@@ -3391,19 +3427,19 @@
           <t>-</t>
         </is>
       </c>
-      <c r="P37" s="17" t="n">
+      <c r="P37" s="18" t="n">
         <v>32.38</v>
       </c>
-      <c r="Q37" s="17" t="n">
+      <c r="Q37" s="18" t="n">
         <v>33.12</v>
       </c>
-      <c r="R37" s="17" t="n">
+      <c r="R37" s="18" t="n">
         <v>33.15</v>
       </c>
-      <c r="S37" s="17" t="n">
+      <c r="S37" s="18" t="n">
         <v>31.32</v>
       </c>
-      <c r="T37" s="17" t="n">
+      <c r="T37" s="18" t="n">
         <v>31.71</v>
       </c>
       <c r="U37" s="6" t="inlineStr">
@@ -3421,10 +3457,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="X37" s="17" t="n">
+      <c r="X37" s="18" t="n">
         <v>32.34</v>
       </c>
-      <c r="Y37" s="17" t="n">
+      <c r="Y37" s="18" t="n">
         <v>32.37</v>
       </c>
       <c r="Z37" s="6" t="inlineStr">
@@ -3432,13 +3468,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="AA37" s="17" t="n">
+      <c r="AA37" s="18" t="n">
         <v>32.65</v>
       </c>
-      <c r="AB37" s="17" t="n">
+      <c r="AB37" s="18" t="n">
         <v>33.45</v>
       </c>
-      <c r="AC37" s="17" t="n">
+      <c r="AC37" s="18" t="n">
         <v>31.78</v>
       </c>
       <c r="AD37" s="6" t="inlineStr">
@@ -3446,23 +3482,27 @@
           <t>-</t>
         </is>
       </c>
-      <c r="AE37" s="17" t="n">
+      <c r="AE37" s="18" t="n">
         <v>31.59</v>
       </c>
-      <c r="AF37" s="17" t="n">
+      <c r="AF37" s="18" t="n">
         <v>33.82</v>
       </c>
-      <c r="AG37" s="17" t="n">
+      <c r="AG37" s="18" t="n">
         <v>31.83</v>
       </c>
-      <c r="AH37" s="17" t="n">
+      <c r="AH37" s="18" t="n">
         <v>32.57</v>
       </c>
       <c r="AI37" s="6" t="inlineStr"/>
-      <c r="AJ37" s="6" t="inlineStr"/>
-      <c r="AK37" s="16" t="n"/>
+      <c r="AJ37" s="19" t="inlineStr">
+        <is>
+          <t>Niveles por debajo del borde del área de cobertura principal y secundaria</t>
+        </is>
+      </c>
+      <c r="AK37" s="17" t="n"/>
     </row>
-    <row r="38">
+    <row r="38" ht="15" customHeight="1">
       <c r="A38" s="5" t="inlineStr">
         <is>
           <t>TELEAMAZONAS</t>
@@ -3511,16 +3551,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="K38" s="17" t="n">
+      <c r="K38" s="18" t="n">
         <v>30.38</v>
       </c>
-      <c r="L38" s="17" t="n">
+      <c r="L38" s="18" t="n">
         <v>33.09</v>
       </c>
-      <c r="M38" s="17" t="n">
+      <c r="M38" s="18" t="n">
         <v>32.21</v>
       </c>
-      <c r="N38" s="17" t="n">
+      <c r="N38" s="18" t="n">
         <v>30.17</v>
       </c>
       <c r="O38" s="6" t="inlineStr">
@@ -3528,19 +3568,19 @@
           <t>-</t>
         </is>
       </c>
-      <c r="P38" s="17" t="n">
+      <c r="P38" s="18" t="n">
         <v>32.04</v>
       </c>
-      <c r="Q38" s="17" t="n">
+      <c r="Q38" s="18" t="n">
         <v>30.86</v>
       </c>
-      <c r="R38" s="17" t="n">
+      <c r="R38" s="18" t="n">
         <v>30.69</v>
       </c>
-      <c r="S38" s="17" t="n">
+      <c r="S38" s="18" t="n">
         <v>30.45</v>
       </c>
-      <c r="T38" s="17" t="n">
+      <c r="T38" s="18" t="n">
         <v>30.94</v>
       </c>
       <c r="U38" s="6" t="inlineStr">
@@ -3558,10 +3598,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="X38" s="17" t="n">
+      <c r="X38" s="18" t="n">
         <v>31.18</v>
       </c>
-      <c r="Y38" s="17" t="n">
+      <c r="Y38" s="18" t="n">
         <v>30.95</v>
       </c>
       <c r="Z38" s="6" t="inlineStr">
@@ -3569,13 +3609,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="AA38" s="17" t="n">
+      <c r="AA38" s="18" t="n">
         <v>30.83</v>
       </c>
-      <c r="AB38" s="17" t="n">
+      <c r="AB38" s="18" t="n">
         <v>31.03</v>
       </c>
-      <c r="AC38" s="17" t="n">
+      <c r="AC38" s="18" t="n">
         <v>30.71</v>
       </c>
       <c r="AD38" s="6" t="inlineStr">
@@ -3583,23 +3623,27 @@
           <t>-</t>
         </is>
       </c>
-      <c r="AE38" s="17" t="n">
+      <c r="AE38" s="18" t="n">
         <v>30.44</v>
       </c>
-      <c r="AF38" s="17" t="n">
+      <c r="AF38" s="18" t="n">
         <v>33.05</v>
       </c>
-      <c r="AG38" s="17" t="n">
+      <c r="AG38" s="18" t="n">
         <v>30.7</v>
       </c>
-      <c r="AH38" s="17" t="n">
+      <c r="AH38" s="18" t="n">
         <v>31.16</v>
       </c>
       <c r="AI38" s="6" t="inlineStr"/>
-      <c r="AJ38" s="6" t="inlineStr"/>
-      <c r="AK38" s="16" t="n"/>
+      <c r="AJ38" s="19" t="inlineStr">
+        <is>
+          <t>Niveles por debajo del borde del área de cobertura principal y secundaria</t>
+        </is>
+      </c>
+      <c r="AK38" s="17" t="n"/>
     </row>
-    <row r="39">
+    <row r="39" ht="15" customHeight="1">
       <c r="A39" s="5" t="inlineStr">
         <is>
           <t>CADENA ECUATORIANA DE TELE</t>
@@ -3648,16 +3692,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="K39" s="17" t="n">
+      <c r="K39" s="18" t="n">
         <v>29.23</v>
       </c>
-      <c r="L39" s="17" t="n">
+      <c r="L39" s="18" t="n">
         <v>29.27</v>
       </c>
-      <c r="M39" s="17" t="n">
+      <c r="M39" s="18" t="n">
         <v>29.72</v>
       </c>
-      <c r="N39" s="17" t="n">
+      <c r="N39" s="18" t="n">
         <v>28.44</v>
       </c>
       <c r="O39" s="6" t="inlineStr">
@@ -3665,19 +3709,19 @@
           <t>-</t>
         </is>
       </c>
-      <c r="P39" s="17" t="n">
+      <c r="P39" s="18" t="n">
         <v>29.66</v>
       </c>
-      <c r="Q39" s="17" t="n">
+      <c r="Q39" s="18" t="n">
         <v>28.68</v>
       </c>
-      <c r="R39" s="17" t="n">
+      <c r="R39" s="18" t="n">
         <v>29.01</v>
       </c>
-      <c r="S39" s="17" t="n">
+      <c r="S39" s="18" t="n">
         <v>28.72</v>
       </c>
-      <c r="T39" s="17" t="n">
+      <c r="T39" s="18" t="n">
         <v>29.25</v>
       </c>
       <c r="U39" s="6" t="inlineStr">
@@ -3695,10 +3739,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="X39" s="17" t="n">
+      <c r="X39" s="18" t="n">
         <v>29.75</v>
       </c>
-      <c r="Y39" s="17" t="n">
+      <c r="Y39" s="18" t="n">
         <v>29.47</v>
       </c>
       <c r="Z39" s="6" t="inlineStr">
@@ -3706,13 +3750,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="AA39" s="17" t="n">
+      <c r="AA39" s="18" t="n">
         <v>29.05</v>
       </c>
-      <c r="AB39" s="17" t="n">
+      <c r="AB39" s="18" t="n">
         <v>29.35</v>
       </c>
-      <c r="AC39" s="17" t="n">
+      <c r="AC39" s="18" t="n">
         <v>28.38</v>
       </c>
       <c r="AD39" s="6" t="inlineStr">
@@ -3720,23 +3764,27 @@
           <t>-</t>
         </is>
       </c>
-      <c r="AE39" s="17" t="n">
+      <c r="AE39" s="18" t="n">
         <v>29.33</v>
       </c>
-      <c r="AF39" s="17" t="n">
+      <c r="AF39" s="18" t="n">
         <v>29.64</v>
       </c>
-      <c r="AG39" s="17" t="n">
+      <c r="AG39" s="18" t="n">
         <v>29.19</v>
       </c>
-      <c r="AH39" s="17" t="n">
+      <c r="AH39" s="18" t="n">
         <v>29.19</v>
       </c>
       <c r="AI39" s="6" t="inlineStr"/>
-      <c r="AJ39" s="6" t="inlineStr"/>
-      <c r="AK39" s="16" t="n"/>
+      <c r="AJ39" s="19" t="inlineStr">
+        <is>
+          <t>Niveles por debajo del borde del área de cobertura principal y secundaria</t>
+        </is>
+      </c>
+      <c r="AK39" s="17" t="n"/>
     </row>
-    <row r="40">
+    <row r="40" ht="15" customHeight="1">
       <c r="A40" s="5" t="inlineStr">
         <is>
           <t>UCSG TELEVISION</t>
@@ -3785,16 +3833,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="K40" s="17" t="n">
+      <c r="K40" s="18" t="n">
         <v>26.49</v>
       </c>
-      <c r="L40" s="17" t="n">
+      <c r="L40" s="18" t="n">
         <v>26.61</v>
       </c>
-      <c r="M40" s="17" t="n">
+      <c r="M40" s="18" t="n">
         <v>26.76</v>
       </c>
-      <c r="N40" s="17" t="n">
+      <c r="N40" s="18" t="n">
         <v>26.86</v>
       </c>
       <c r="O40" s="6" t="inlineStr">
@@ -3802,19 +3850,19 @@
           <t>-</t>
         </is>
       </c>
-      <c r="P40" s="17" t="n">
+      <c r="P40" s="18" t="n">
         <v>26.77</v>
       </c>
-      <c r="Q40" s="17" t="n">
+      <c r="Q40" s="18" t="n">
         <v>26.84</v>
       </c>
-      <c r="R40" s="17" t="n">
+      <c r="R40" s="18" t="n">
         <v>27.65</v>
       </c>
-      <c r="S40" s="17" t="n">
+      <c r="S40" s="18" t="n">
         <v>26.75</v>
       </c>
-      <c r="T40" s="17" t="n">
+      <c r="T40" s="18" t="n">
         <v>26.91</v>
       </c>
       <c r="U40" s="6" t="inlineStr">
@@ -3832,10 +3880,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="X40" s="17" t="n">
+      <c r="X40" s="18" t="n">
         <v>26.82</v>
       </c>
-      <c r="Y40" s="17" t="n">
+      <c r="Y40" s="18" t="n">
         <v>26.87</v>
       </c>
       <c r="Z40" s="6" t="inlineStr">
@@ -3843,13 +3891,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="AA40" s="17" t="n">
+      <c r="AA40" s="18" t="n">
         <v>26.65</v>
       </c>
-      <c r="AB40" s="17" t="n">
+      <c r="AB40" s="18" t="n">
         <v>26.82</v>
       </c>
-      <c r="AC40" s="17" t="n">
+      <c r="AC40" s="18" t="n">
         <v>26.56</v>
       </c>
       <c r="AD40" s="6" t="inlineStr">
@@ -3857,23 +3905,27 @@
           <t>-</t>
         </is>
       </c>
-      <c r="AE40" s="17" t="n">
+      <c r="AE40" s="18" t="n">
         <v>26.93</v>
       </c>
-      <c r="AF40" s="17" t="n">
+      <c r="AF40" s="18" t="n">
         <v>26.84</v>
       </c>
-      <c r="AG40" s="17" t="n">
+      <c r="AG40" s="18" t="n">
         <v>26.69</v>
       </c>
-      <c r="AH40" s="17" t="n">
+      <c r="AH40" s="18" t="n">
         <v>26.81</v>
       </c>
       <c r="AI40" s="6" t="inlineStr"/>
-      <c r="AJ40" s="6" t="inlineStr"/>
-      <c r="AK40" s="16" t="n"/>
+      <c r="AJ40" s="19" t="inlineStr">
+        <is>
+          <t>Niveles por debajo del borde del área de cobertura principal y secundaria</t>
+        </is>
+      </c>
+      <c r="AK40" s="17" t="n"/>
     </row>
-    <row r="41">
+    <row r="41" ht="15" customHeight="1">
       <c r="A41" s="5" t="inlineStr">
         <is>
           <t>OROMAR</t>
@@ -3922,16 +3974,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="K41" s="17" t="n">
+      <c r="K41" s="18" t="n">
         <v>26.63</v>
       </c>
-      <c r="L41" s="17" t="n">
+      <c r="L41" s="18" t="n">
         <v>26.96</v>
       </c>
-      <c r="M41" s="17" t="n">
+      <c r="M41" s="18" t="n">
         <v>26.84</v>
       </c>
-      <c r="N41" s="17" t="n">
+      <c r="N41" s="18" t="n">
         <v>26.93</v>
       </c>
       <c r="O41" s="6" t="inlineStr">
@@ -3939,19 +3991,19 @@
           <t>-</t>
         </is>
       </c>
-      <c r="P41" s="17" t="n">
+      <c r="P41" s="18" t="n">
         <v>27.04</v>
       </c>
-      <c r="Q41" s="17" t="n">
+      <c r="Q41" s="18" t="n">
         <v>26.67</v>
       </c>
-      <c r="R41" s="17" t="n">
+      <c r="R41" s="18" t="n">
         <v>26.77</v>
       </c>
-      <c r="S41" s="17" t="n">
+      <c r="S41" s="18" t="n">
         <v>26.6</v>
       </c>
-      <c r="T41" s="17" t="n">
+      <c r="T41" s="18" t="n">
         <v>27.2</v>
       </c>
       <c r="U41" s="6" t="inlineStr">
@@ -3969,10 +4021,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="X41" s="17" t="n">
+      <c r="X41" s="18" t="n">
         <v>26.92</v>
       </c>
-      <c r="Y41" s="17" t="n">
+      <c r="Y41" s="18" t="n">
         <v>27.06</v>
       </c>
       <c r="Z41" s="6" t="inlineStr">
@@ -3980,13 +4032,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="AA41" s="17" t="n">
+      <c r="AA41" s="18" t="n">
         <v>26.83</v>
       </c>
-      <c r="AB41" s="17" t="n">
+      <c r="AB41" s="18" t="n">
         <v>26.85</v>
       </c>
-      <c r="AC41" s="17" t="n">
+      <c r="AC41" s="18" t="n">
         <v>26.68</v>
       </c>
       <c r="AD41" s="6" t="inlineStr">
@@ -3994,23 +4046,27 @@
           <t>-</t>
         </is>
       </c>
-      <c r="AE41" s="17" t="n">
+      <c r="AE41" s="18" t="n">
         <v>27.21</v>
       </c>
-      <c r="AF41" s="17" t="n">
+      <c r="AF41" s="18" t="n">
         <v>27.19</v>
       </c>
-      <c r="AG41" s="17" t="n">
+      <c r="AG41" s="18" t="n">
         <v>26.73</v>
       </c>
-      <c r="AH41" s="17" t="n">
+      <c r="AH41" s="18" t="n">
         <v>26.89</v>
       </c>
       <c r="AI41" s="6" t="inlineStr"/>
-      <c r="AJ41" s="6" t="inlineStr"/>
-      <c r="AK41" s="16" t="n"/>
+      <c r="AJ41" s="19" t="inlineStr">
+        <is>
+          <t>Niveles por debajo del borde del área de cobertura principal y secundaria</t>
+        </is>
+      </c>
+      <c r="AK41" s="17" t="n"/>
     </row>
-    <row r="42">
+    <row r="42" ht="15" customHeight="1">
       <c r="A42" s="5" t="inlineStr">
         <is>
           <t>TV LEGISLATIVA</t>
@@ -4059,16 +4115,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="K42" s="17" t="n">
+      <c r="K42" s="18" t="n">
         <v>27.35</v>
       </c>
-      <c r="L42" s="17" t="n">
+      <c r="L42" s="18" t="n">
         <v>27.68</v>
       </c>
-      <c r="M42" s="17" t="n">
+      <c r="M42" s="18" t="n">
         <v>26.97</v>
       </c>
-      <c r="N42" s="17" t="n">
+      <c r="N42" s="18" t="n">
         <v>27.55</v>
       </c>
       <c r="O42" s="6" t="inlineStr">
@@ -4076,19 +4132,19 @@
           <t>-</t>
         </is>
       </c>
-      <c r="P42" s="17" t="n">
+      <c r="P42" s="18" t="n">
         <v>28.86</v>
       </c>
-      <c r="Q42" s="17" t="n">
+      <c r="Q42" s="18" t="n">
         <v>27.39</v>
       </c>
-      <c r="R42" s="17" t="n">
+      <c r="R42" s="18" t="n">
         <v>29.27</v>
       </c>
-      <c r="S42" s="17" t="n">
+      <c r="S42" s="18" t="n">
         <v>27.56</v>
       </c>
-      <c r="T42" s="17" t="n">
+      <c r="T42" s="18" t="n">
         <v>28.35</v>
       </c>
       <c r="U42" s="6" t="inlineStr">
@@ -4106,10 +4162,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="X42" s="17" t="n">
+      <c r="X42" s="18" t="n">
         <v>27.35</v>
       </c>
-      <c r="Y42" s="17" t="n">
+      <c r="Y42" s="18" t="n">
         <v>27.39</v>
       </c>
       <c r="Z42" s="6" t="inlineStr">
@@ -4117,13 +4173,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="AA42" s="17" t="n">
+      <c r="AA42" s="18" t="n">
         <v>27.07</v>
       </c>
-      <c r="AB42" s="17" t="n">
+      <c r="AB42" s="18" t="n">
         <v>27.45</v>
       </c>
-      <c r="AC42" s="17" t="n">
+      <c r="AC42" s="18" t="n">
         <v>27.13</v>
       </c>
       <c r="AD42" s="6" t="inlineStr">
@@ -4131,158 +4187,166 @@
           <t>-</t>
         </is>
       </c>
-      <c r="AE42" s="17" t="n">
+      <c r="AE42" s="18" t="n">
         <v>27.25</v>
       </c>
-      <c r="AF42" s="17" t="n">
+      <c r="AF42" s="18" t="n">
         <v>27.71</v>
       </c>
-      <c r="AG42" s="17" t="n">
+      <c r="AG42" s="18" t="n">
         <v>27.53</v>
       </c>
-      <c r="AH42" s="17" t="n">
+      <c r="AH42" s="18" t="n">
         <v>27.64</v>
       </c>
       <c r="AI42" s="6" t="inlineStr"/>
-      <c r="AJ42" s="6" t="inlineStr"/>
-      <c r="AK42" s="16" t="n"/>
+      <c r="AJ42" s="19" t="inlineStr">
+        <is>
+          <t>Niveles por debajo del borde del área de cobertura principal y secundaria</t>
+        </is>
+      </c>
+      <c r="AK42" s="17" t="n"/>
     </row>
-    <row r="43">
-      <c r="A43" s="11" t="inlineStr">
+    <row r="43" ht="15" customHeight="1">
+      <c r="A43" s="12" t="inlineStr">
         <is>
           <t>TELECIUDADANA</t>
         </is>
       </c>
-      <c r="B43" s="12" t="n">
+      <c r="B43" s="13" t="n">
         <v>681.25</v>
       </c>
-      <c r="C43" s="12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D43" s="12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E43" s="12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F43" s="12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G43" s="12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H43" s="12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I43" s="12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J43" s="12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K43" s="18" t="n">
+      <c r="C43" s="13" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D43" s="13" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E43" s="13" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F43" s="13" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G43" s="13" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H43" s="13" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I43" s="13" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J43" s="13" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K43" s="20" t="n">
         <v>27.51</v>
       </c>
-      <c r="L43" s="18" t="n">
+      <c r="L43" s="20" t="n">
         <v>27.51</v>
       </c>
-      <c r="M43" s="18" t="n">
+      <c r="M43" s="20" t="n">
         <v>27.42</v>
       </c>
-      <c r="N43" s="18" t="n">
+      <c r="N43" s="20" t="n">
         <v>27.63</v>
       </c>
-      <c r="O43" s="12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P43" s="18" t="n">
+      <c r="O43" s="13" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P43" s="20" t="n">
         <v>27.18</v>
       </c>
-      <c r="Q43" s="18" t="n">
+      <c r="Q43" s="20" t="n">
         <v>27.42</v>
       </c>
-      <c r="R43" s="18" t="n">
+      <c r="R43" s="20" t="n">
         <v>29.01</v>
       </c>
-      <c r="S43" s="18" t="n">
+      <c r="S43" s="20" t="n">
         <v>27.59</v>
       </c>
-      <c r="T43" s="18" t="n">
+      <c r="T43" s="20" t="n">
         <v>27.61</v>
       </c>
-      <c r="U43" s="12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="V43" s="12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="W43" s="12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="X43" s="18" t="n">
+      <c r="U43" s="13" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="V43" s="13" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="W43" s="13" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="X43" s="20" t="n">
         <v>27.49</v>
       </c>
-      <c r="Y43" s="18" t="n">
+      <c r="Y43" s="20" t="n">
         <v>27.51</v>
       </c>
-      <c r="Z43" s="12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AA43" s="18" t="n">
+      <c r="Z43" s="13" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AA43" s="20" t="n">
         <v>27.53</v>
       </c>
-      <c r="AB43" s="18" t="n">
+      <c r="AB43" s="20" t="n">
         <v>27.47</v>
       </c>
-      <c r="AC43" s="18" t="n">
+      <c r="AC43" s="20" t="n">
         <v>27.33</v>
       </c>
-      <c r="AD43" s="12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AE43" s="18" t="n">
+      <c r="AD43" s="13" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AE43" s="20" t="n">
         <v>27.68</v>
       </c>
-      <c r="AF43" s="18" t="n">
+      <c r="AF43" s="20" t="n">
         <v>27.72</v>
       </c>
-      <c r="AG43" s="18" t="n">
+      <c r="AG43" s="20" t="n">
         <v>27.44</v>
       </c>
-      <c r="AH43" s="18" t="n">
+      <c r="AH43" s="20" t="n">
         <v>27.59</v>
       </c>
-      <c r="AI43" s="12" t="inlineStr"/>
-      <c r="AJ43" s="12" t="inlineStr"/>
-      <c r="AK43" s="19" t="n"/>
+      <c r="AI43" s="13" t="inlineStr"/>
+      <c r="AJ43" s="21" t="inlineStr">
+        <is>
+          <t>Niveles por debajo del borde del área de cobertura principal y secundaria</t>
+        </is>
+      </c>
+      <c r="AK43" s="22" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="28">

--- a/ReportesUnificados/zamora_ReporteUnificado.xlsx
+++ b/ReportesUnificados/zamora_ReporteUnificado.xlsx
@@ -810,7 +810,7 @@
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>FECHA PRESENTACIÓN: 02/09/2025</t>
+          <t>FECHA PRESENTACIÓN: 03/09/2025</t>
         </is>
       </c>
     </row>
@@ -2673,7 +2673,7 @@
     <row r="31">
       <c r="A31" s="1" t="inlineStr">
         <is>
-          <t>FECHA PRESENTACIÓN: 02/09/2025</t>
+          <t>FECHA PRESENTACIÓN: 03/09/2025</t>
         </is>
       </c>
     </row>
